--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -906,32 +906,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Simon Foster</t>
+          <t>Radu Calinescu</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>896.2966666666666</v>
+        <v>1280.13</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>445.0966666666667</v>
+        <v>186.43</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>276.2</v>
+        <v>918.7</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Practicals: 4 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 14.0h/teacher; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h; Grant ARISE: Accelerating ReIntroduction of EcoSystem-Engineering Ant Colonies with Embodied AI: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h; Grant MammoBot: Robotic Posture Assistance for Universal Breast Screening Access: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -953,42 +953,42 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Katrina Attwood</t>
+          <t>Yuchen Zhao</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1809.16</v>
+        <v>1203.65</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1093.56</v>
+        <v>766.35</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>212.2</v>
+        <v>180.2</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>503.4</v>
+        <v>257.1</v>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 5 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 17.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
+          <t>PhD supervision: 2x assessor (8h each) = 16.0h</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Director of Students: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -1000,37 +1000,37 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Felix Ulrich-Oltean</t>
+          <t>Carlo Ottaviani</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>810.63</v>
+        <v>1270.281666666667</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>423.43</v>
+        <v>662.8816666666667</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>212.2</v>
+        <v>268.2</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher</t>
+          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -1040,49 +1040,49 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Jacob Rigby</t>
+          <t>Stefano Pirandola</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1302.28</v>
+        <v>1752.515</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>716.78</v>
+        <v>810.8150000000001</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>246.3</v>
+        <v>520.4000000000001</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>339.2</v>
+        <v>421.3</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Projects (40cr): Standard (2.5x): 40.0h/teacher @ 2.5x = 100.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 39.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Practicals: 11 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 52.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Grant EPSRC: Addressing environmental injustices through transdisciplinary science and technology: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Integrated Quantum Networks (IQN) Hub: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Taught Project Coordinator: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -1094,37 +1094,37 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Pengcheng Liu</t>
+          <t>Nick Pears</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1400.88</v>
+        <v>1632.513333333333</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>229.3</v>
+        <v>372.5133333333333</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>996.5800000000002</v>
+        <v>428.2</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>175</v>
+        <v>831.8000000000001</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Intelligent Dependable Environment Control for Sustainable Aquaculture: 20% of 1642h = 328.4h; Grant Establishing a Safe AI Research Hub: York–UTM–UTB Twin-Lab Initiative: 9% of 1642h = 147.8h; Grant Establishment of Korea–UK Collaboration Platform for Convergent Research in Quantum Photonics and Artificial Intelligence - Yr2: 5% of 1642h = 82.1h; Grant SCHEME: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 264.0h</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Graduate School Board (GSB) Chair: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Head (Research): 40% of 1642h = 656.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -1141,42 +1141,42 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Nick Pears</t>
+          <t>Jo Iacovides</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1632.513333333333</v>
+        <v>1697.755</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>372.5133333333333</v>
+        <v>1010.355</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>428.2</v>
+        <v>348.2</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>831.8000000000001</v>
+        <v>339.2</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 264.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 184.0h</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Deputy Head (Research): 40% of 1642h = 656.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -1188,79 +1188,79 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Poonam Yadav</t>
+          <t>Soumya Banerjee</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2014.12</v>
+        <v>1461.04</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>562.12</v>
+        <v>1121.84</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1112.8</v>
+        <v>164.2</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>AURO (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h; Grant CHEDDAR Funding Apr-Sep 26- PSU296: 5% of 1642h = 82.1h; Grant REMOTE: Resilient and Secure Multi-Access Interoperable Communication Fabric for TinyEdge: 20% of 1642h = 328.4h; Grant Orchestrated mobile Network for Blackpool intelligent transport: 5% of 1642h = 82.1h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>James Walker</t>
+          <t>Claudio Guarnera</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1808.84</v>
+        <v>987.24</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>633.04</v>
+        <v>536.04</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1000.8</v>
+        <v>276.2</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h; Grant Smart Data Donation Service (SDDS): 10% of 1642h = 164.2h; Grant IGGI: 20% of 1642h = 328.4h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1329,42 +1329,42 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Joe Cutting</t>
+          <t>Kofi Appiah</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1424.235</v>
+        <v>1639.35</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1021.035</v>
+        <v>861.85</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>228.2</v>
+        <v>356.2</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>175</v>
+        <v>421.3</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>ECR rep: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Director of Admissions (UG Admissions): 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1376,42 +1376,42 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Kostas Barmpis</t>
+          <t>Alvaro Miyazawa</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1793.433333333333</v>
+        <v>1202.95</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1069.833333333333</v>
+        <v>595.55</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>548.6</v>
+        <v>268.2</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>PGR Training Officer: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1423,27 +1423,27 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Christopher Crispin-Bailey</t>
+          <t>Dawn H Wood</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1159.203333333333</v>
+        <v>1250.05</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>532.6533333333334</v>
+        <v>910.85</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>164.2</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>462.35</v>
+        <v>175</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>GTA Coordinator: 10% of 1642h = 164.2h; Union: 8% of 1642h = 123.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1463,49 +1463,49 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Jo Iacovides</t>
+          <t>Andrew Pomfret</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1697.755</v>
+        <v>1257.443333333334</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1010.355</v>
+        <v>836.1433333333334</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>348.2</v>
+        <v>164.2</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 184.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -1517,42 +1517,42 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Paul Cairns</t>
+          <t>Jacob Rigby</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2257.945</v>
+        <v>1302.28</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>906.145</v>
+        <v>716.78</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1012.6</v>
+        <v>246.3</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>339.2</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Projects (40cr): Standard (2.5x): 40.0h/teacher @ 2.5x = 100.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 39.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h; Grant BiB Centre for Social Change: 0% of 1642h = 0.0h; Grant IGGI: 20% of 1642h = 328.4h</t>
+          <t>Grant EPSRC: Addressing environmental injustices through transdisciplinary science and technology: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; REF Lead: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Taught Project Coordinator: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1564,42 +1564,42 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Dimitar Kazakov</t>
+          <t>Ian Gray</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1424.5</v>
+        <v>1769.61</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>629.3</v>
+        <v>425.41</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>620.2</v>
+        <v>348.2</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>175</v>
+        <v>996</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 5x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Ethics Committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Head of Department (On-campus teaching): 50% of 1642h = 821.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1611,37 +1611,37 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Siamak Shahandashti</t>
+          <t>Steven Wright</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1277.34</v>
+        <v>1167.91</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>459.84</v>
+        <v>540.71</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>478.3</v>
+        <v>452.2</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h; Grant Participatory Harm Auditing Workbenches &amp; Methodologies: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Chair of the Board of Examiners: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1658,84 +1658,84 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Dawn H Wood</t>
+          <t>William Smith</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1250.05</v>
+        <v>1992.76</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>910.85</v>
+        <v>1018.41</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>164.2</v>
+        <v>676.2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>175</v>
+        <v>298.15</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; DEEP (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Alena Denisova</t>
+          <t>Joe Cutting</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2006.015</v>
+        <v>1424.235</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1058.415</v>
+        <v>1021.035</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>444.2</v>
+        <v>228.2</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 4x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 280.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Ethics Committee Chair: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>ECR rep: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1752,42 +1752,42 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Peter Nightingale</t>
+          <t>Rob Alexander</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2230.43</v>
+        <v>789.1849999999999</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1591.03</v>
+        <v>215.885</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>300.2</v>
+        <v>398.3</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; ARIA (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 2 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 8.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>UG PL: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -1799,37 +1799,37 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Xinwei Fang</t>
+          <t>Paul Cairns</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1258.805</v>
+        <v>2257.945</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>757.505</v>
+        <v>906.145</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>244.2</v>
+        <v>1012.6</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Practicals: 4 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 14.0h/teacher; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h</t>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h; Grant BiB Centre for Social Change: 0% of 1642h = 0.0h; Grant IGGI: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; REF Lead: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1846,37 +1846,37 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Antonio Garcia-Dominguez</t>
+          <t>Jen Beeston</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1795.386666666667</v>
+        <v>1537</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>975.7866666666666</v>
+        <v>1029.8</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>644.6000000000001</v>
+        <v>332.2</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; ELLA (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 168.0h</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Chair of the Department Education Committee: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1886,81 +1886,81 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Da Li</t>
+          <t>Alena Denisova</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>750</v>
+        <v>2006.015</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>410.8</v>
+        <v>1058.415</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>164.2</v>
+        <v>444.2</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 4x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 280.0h</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Ethics Committee Chair: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Andrew Pomfret</t>
+          <t>Fang Yan</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1257.443333333334</v>
+        <v>800.6800000000001</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>836.1433333333334</v>
+        <v>461.48</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>164.2</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SOF2 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; THE3 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -1980,96 +1980,96 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Fang Yan</t>
+          <t>Kostas Barmpis</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>800.6800000000001</v>
+        <v>1793.433333333333</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>461.48</v>
+        <v>1069.833333333333</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>164.2</v>
+        <v>548.6</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>SOF2 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; THE3 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>PGR Training Officer: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>James Stovold</t>
+          <t>Steven Xiaotian Dai</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1600.34</v>
+        <v>1822.82</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1179.04</v>
+        <v>969.12</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>164.2</v>
+        <v>350.3</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>257.1</v>
+        <v>503.4</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>DEEP (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; LLMA (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h; Grant SCHEME: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Student Disability Representative: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -2081,84 +2081,84 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Colin Paterson</t>
+          <t>Mike Freeman</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>983.5599999999999</v>
+        <v>1278.443333333334</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>228.8</v>
+        <v>857.1433333333334</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>579.76</v>
+        <v>164.2</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>LPTC (20cr): Standard (2.5x): 10.0h/teacher @ 2.5x = 25.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
+          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 120.0h; Grant KTP with Advai (Industry): 3% of 1642h = 49.3h; Grant KTP with Advai: 5% of 1642h = 82.1h; Grant A STAR TO STEER BY: 5% of 1642h = 82.1h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Robbert Jongeling</t>
+          <t>Dimitar Kazakov</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1348.48</v>
+        <v>1424.5</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1009.28</v>
+        <v>629.3</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>164.2</v>
+        <v>620.2</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 2 students x 3h = 6.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 5x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Ethics Committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -2168,44 +2168,44 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Carlo Ottaviani</t>
+          <t>Siamak Shahandashti</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1270.281666666667</v>
+        <v>1277.34</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>662.8816666666667</v>
+        <v>459.84</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>268.2</v>
+        <v>478.3</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>339.2</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x assessor (8h each) = 104.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h; Grant Participatory Harm Auditing Workbenches &amp; Methodologies: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -2222,37 +2222,37 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ribeiro</t>
+          <t>Felix Ulrich-Oltean</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1986.063333333333</v>
+        <v>810.63</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1002.263333333333</v>
+        <v>423.43</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>644.6</v>
+        <v>212.2</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 20% of 1642h = 328.4h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -2262,49 +2262,49 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Frank Soboczenski</t>
+          <t>Peter Nightingale</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2515.32</v>
+        <v>2230.43</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>463.8</v>
+        <v>1591.03</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1794.42</v>
+        <v>300.2</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>LLMA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
+          <t>SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; ARIA (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 11% of 1642h = 180.6h; Grant Alan Turing AI Fellowship: 80% of 1642h = 1313.6h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>UG PL: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -2316,37 +2316,37 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Pourya Shamsolmoali</t>
+          <t>James Walker</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1538.465</v>
+        <v>1808.84</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1012.115</v>
+        <v>633.04</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>228.2</v>
+        <v>1000.8</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>298.15</v>
+        <v>175</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h; Grant Smart Data Donation Service (SDDS): 10% of 1642h = 164.2h; Grant IGGI: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Graduate School Board (Ordinary member): 2% of 1642h = 41.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -2356,44 +2356,44 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Miyazawa</t>
+          <t>Simon Foster</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1202.95</v>
+        <v>896.2966666666666</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>595.55</v>
+        <v>445.0966666666667</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>268.2</v>
+        <v>276.2</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -2403,44 +2403,44 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Steven Xiaotian Dai</t>
+          <t>Claire Ingram</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1822.82</v>
+        <v>649.1849999999999</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>969.12</v>
+        <v>227.885</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>350.3</v>
+        <v>164.2</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>503.4</v>
+        <v>257.1</v>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 2 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 8.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 1 students x 3h = 3.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h; Grant SCHEME: 5% of 1642h = 82.1h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Student Disability Representative: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Outreach and Extra-Curricular Activities: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -2457,27 +2457,27 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Soumya Banerjee</t>
+          <t>James Stovold</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1461.04</v>
+        <v>1600.34</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>1121.84</v>
+        <v>1179.04</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>164.2</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DEEP (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; LLMA (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2487,59 +2487,59 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Steven Wright</t>
+          <t>Katrina Attwood</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1167.91</v>
+        <v>1809.16</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>540.71</v>
+        <v>1093.56</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>452.2</v>
+        <v>212.2</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Chair of the Board of Examiners: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Director of Students: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -2551,37 +2551,37 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Radu Calinescu</t>
+          <t>Mike O'Dea</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1280.13</v>
+        <v>1263.375</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>186.43</v>
+        <v>842.075</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>918.7</v>
+        <v>164.2</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Practicals: 4 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 14.0h/teacher; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h; Grant ARISE: Accelerating ReIntroduction of EcoSystem-Engineering Ant Colonies with Embodied AI: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h; Grant MammoBot: Robotic Posture Assistance for Universal Breast Screening Access: 10% of 1642h = 164.2h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -2591,138 +2591,138 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Jen Beeston</t>
+          <t>Colin Paterson</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1537</v>
+        <v>983.5599999999999</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1029.8</v>
+        <v>228.8</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>332.2</v>
+        <v>579.76</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>LPTC (20cr): Standard (2.5x): 10.0h/teacher @ 2.5x = 25.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 168.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 120.0h; Grant KTP with Advai (Industry): 3% of 1642h = 49.3h; Grant KTP with Advai: 5% of 1642h = 82.1h; Grant A STAR TO STEER BY: 5% of 1642h = 82.1h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Chair of the Department Education Committee: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Vasileios Vasilakis</t>
+          <t>Robbert Jongeling</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1028.195</v>
+        <v>1348.48</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>332.795</v>
+        <v>1009.28</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>356.2</v>
+        <v>164.2</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 5 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 17.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>ENG1 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 2 students x 3h = 6.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Mike Freeman</t>
+          <t>Roberto Metere</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1278.443333333334</v>
+        <v>1522.941666666667</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>857.1433333333334</v>
+        <v>1079.741666666667</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>164.2</v>
+        <v>268.2</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -2739,84 +2739,84 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Adrian Bors</t>
+          <t>Yan Jia</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1346.6</v>
+        <v>1282.37</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>677.3</v>
+        <v>468.67</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>412.2</v>
+        <v>638.7</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
+          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x assessor (8h each) = 248.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10% of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Internationalisation and Visitors Coordinator: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Yuchen Zhao</t>
+          <t>Detlef Plump</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1203.65</v>
+        <v>1097.26</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>766.35</v>
+        <v>333.66</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>180.2</v>
+        <v>260.2</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>257.1</v>
+        <v>503.4</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 5 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 17.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x assessor (8h each) = 16.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>EC Officer (on-campus): 15% of 1642h = 246.3h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -2833,89 +2833,89 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Mike O'Dea</t>
+          <t>Dimitris Kolovos</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1263.375</v>
+        <v>1703.82</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>842.075</v>
+        <v>413.92</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>164.2</v>
+        <v>1114.9</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher</t>
+          <t>ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 376.0h; Grant Socially-Acceptable and Trustworthy Human-Robot Teaming for Agile Industries (SYMPHONY Resubmission): 5% of 1642h = 82.1h; Grant MOSAICO: 5% of 1642h = 82.1h; Grant SCHEME: 20% of 1642h = 328.4h; Grant Cavecore: Doctoral Network on Continuous, Automated Validation, and Evaluation of Cognitive Robots in Open-Ended Environments: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Tommy Yuan</t>
+          <t>Frank Soboczenski</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>2406.913333333333</v>
+        <v>2515.32</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>1703.513333333333</v>
+        <v>463.8</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>364.2</v>
+        <v>1794.42</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; ARIA (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>LLMA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 200.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 11% of 1642h = 180.6h; Grant Alan Turing AI Fellowship: 80% of 1642h = 1313.6h</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Deputy CBoEs: 10% of 1642h = 164.2h; StAMP committee members: 0% of 1642h = 0.0h; CSCSE SQA Partnership Leader: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -2927,37 +2927,37 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Kofi Appiah</t>
+          <t>Xinwei Fang</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1639.35</v>
+        <v>1258.805</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>861.85</v>
+        <v>757.505</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>356.2</v>
+        <v>244.2</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>421.3</v>
+        <v>257.1</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Practicals: 4 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 14.0h/teacher; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Deputy Director of Admissions (UG Admissions): 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -2974,89 +2974,89 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Claudio Guarnera</t>
+          <t>Tommy Yuan</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>987.24</v>
+        <v>2406.913333333333</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>536.04</v>
+        <v>1703.513333333333</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>276.2</v>
+        <v>364.2</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; ARIA (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 200.0h</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy CBoEs: 10% of 1642h = 164.2h; StAMP committee members: 0% of 1642h = 0.0h; CSCSE SQA Partnership Leader: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>William Smith</t>
+          <t>Pourya Shamsolmoali</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1992.76</v>
+        <v>1538.465</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>1018.41</v>
+        <v>1012.115</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>676.2</v>
+        <v>228.2</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>298.15</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; DEEP (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Graduate School Board (Ordinary member): 2% of 1642h = 41.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
@@ -3068,27 +3068,27 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Claire Ingram</t>
+          <t>Christopher Crispin-Bailey</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>649.1849999999999</v>
+        <v>1159.203333333333</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>227.885</v>
+        <v>532.6533333333334</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>164.2</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>257.1</v>
+        <v>462.35</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 2 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 8.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 1 students x 3h = 3.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
+          <t>SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>Outreach and Extra-Curricular Activities: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>GTA Coordinator: 10% of 1642h = 164.2h; Union: 8% of 1642h = 123.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
@@ -3115,37 +3115,37 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Roberto Metere</t>
+          <t>Da Li</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1522.941666666667</v>
+        <v>750</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>1079.741666666667</v>
+        <v>410.8</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>268.2</v>
+        <v>164.2</v>
       </c>
       <c r="F49" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS3 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
@@ -3155,138 +3155,138 @@
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Dimitris Kolovos</t>
+          <t>Vasileios Vasilakis</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1703.82</v>
+        <v>1028.195</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>413.92</v>
+        <v>332.795</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>1114.9</v>
+        <v>356.2</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher</t>
+          <t>NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 5 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 17.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 376.0h; Grant Socially-Acceptable and Trustworthy Human-Robot Teaming for Agile Industries (SYMPHONY Resubmission): 5% of 1642h = 82.1h; Grant MOSAICO: 5% of 1642h = 82.1h; Grant SCHEME: 20% of 1642h = 328.4h; Grant Cavecore: Doctoral Network on Continuous, Automated Validation, and Evaluation of Cognitive Robots in Open-Ended Environments: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Rob Alexander</t>
+          <t>Antonio Garcia-Dominguez</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>789.1849999999999</v>
+        <v>1795.386666666667</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>215.885</v>
+        <v>975.7866666666666</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>398.3</v>
+        <v>644.6000000000001</v>
       </c>
       <c r="F51" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 2 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 8.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; ELLA (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Detlef Plump</t>
+          <t>Pedro Ribeiro</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1097.26</v>
+        <v>1986.063333333333</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>333.66</v>
+        <v>1002.263333333333</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>260.2</v>
+        <v>644.6</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>503.4</v>
+        <v>339.2</v>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>EC Officer (on-campus): 15% of 1642h = 246.3h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
@@ -3303,37 +3303,37 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Ian Gray</t>
+          <t>Poonam Yadav</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>1769.61</v>
+        <v>2014.12</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>425.41</v>
+        <v>562.12</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>348.2</v>
+        <v>1112.8</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>996</v>
+        <v>339.2</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher</t>
+          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h; Grant CHEDDAR Funding Apr-Sep 26- PSU296: 5% of 1642h = 82.1h; Grant REMOTE: Resilient and Secure Multi-Access Interoperable Communication Fabric for TinyEdge: 20% of 1642h = 328.4h; Grant Orchestrated mobile Network for Blackpool intelligent transport: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Deputy Head of Department (On-campus teaching): 50% of 1642h = 821.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
@@ -3350,84 +3350,84 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Yan Jia</t>
+          <t>Adrian Bors</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1282.37</v>
+        <v>1346.6</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>468.67</v>
+        <v>677.3</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>638.7</v>
+        <v>412.2</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10% of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x assessor (8h each) = 248.0h</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Internationalisation and Visitors Coordinator: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Stefano Pirandola</t>
+          <t>Pengcheng Liu</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1752.515</v>
+        <v>1400.88</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>810.8150000000001</v>
+        <v>229.3</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>520.4000000000001</v>
+        <v>996.5800000000002</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>421.3</v>
+        <v>175</v>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Practicals: 11 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 52.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Integrated Quantum Networks (IQN) Hub: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Intelligent Dependable Environment Control for Sustainable Aquaculture: 20% of 1642h = 328.4h; Grant Establishing a Safe AI Research Hub: York–UTM–UTB Twin-Lab Initiative: 9% of 1642h = 147.8h; Grant Establishment of Korea–UK Collaboration Platform for Convergent Research in Quantum Photonics and Artificial Intelligence - Yr2: 5% of 1642h = 82.1h; Grant SCHEME: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Graduate School Board (GSB) Chair: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
@@ -3553,14 +3553,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Simon Foster</t>
+          <t>Radu Calinescu</t>
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>445.0966666666667</v>
+        <v>186.43</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>276.2</v>
+        <v>918.7</v>
       </c>
       <c r="D2" s="7" t="n">
         <v>175</v>
@@ -3573,17 +3573,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Katrina Attwood</t>
+          <t>Yuchen Zhao</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>1093.56</v>
+        <v>766.35</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>212.2</v>
+        <v>180.2</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>503.4</v>
+        <v>257.1</v>
       </c>
       <c r="E3" s="7">
         <f>SUM(B3:D3)</f>
@@ -3593,17 +3593,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Felix Ulrich-Oltean</t>
+          <t>Carlo Ottaviani</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>423.43</v>
+        <v>662.8816666666667</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>212.2</v>
+        <v>268.2</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E4" s="7">
         <f>SUM(B4:D4)</f>
@@ -3613,17 +3613,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jacob Rigby</t>
+          <t>Stefano Pirandola</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>716.78</v>
+        <v>810.8150000000001</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>246.3</v>
+        <v>520.4000000000001</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>339.2</v>
+        <v>421.3</v>
       </c>
       <c r="E5" s="7">
         <f>SUM(B5:D5)</f>
@@ -3633,17 +3633,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pengcheng Liu</t>
+          <t>Nick Pears</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>229.3</v>
+        <v>372.5133333333333</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>996.5800000000002</v>
+        <v>428.2</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>175</v>
+        <v>831.8000000000001</v>
       </c>
       <c r="E6" s="7">
         <f>SUM(B6:D6)</f>
@@ -3653,17 +3653,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nick Pears</t>
+          <t>Jo Iacovides</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>372.5133333333333</v>
+        <v>1010.355</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>428.2</v>
+        <v>348.2</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>831.8000000000001</v>
+        <v>339.2</v>
       </c>
       <c r="E7" s="7">
         <f>SUM(B7:D7)</f>
@@ -3673,17 +3673,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Poonam Yadav</t>
+          <t>Soumya Banerjee</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>562.12</v>
+        <v>1121.84</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>1112.8</v>
+        <v>164.2</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E8" s="7">
         <f>SUM(B8:D8)</f>
@@ -3693,14 +3693,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>James Walker</t>
+          <t>Claudio Guarnera</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>633.04</v>
+        <v>536.04</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>1000.8</v>
+        <v>276.2</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>175</v>
@@ -3733,17 +3733,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Joe Cutting</t>
+          <t>Kofi Appiah</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>1021.035</v>
+        <v>861.85</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>228.2</v>
+        <v>356.2</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>175</v>
+        <v>421.3</v>
       </c>
       <c r="E11" s="7">
         <f>SUM(B11:D11)</f>
@@ -3753,17 +3753,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kostas Barmpis</t>
+          <t>Alvaro Miyazawa</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>1069.833333333333</v>
+        <v>595.55</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>548.6</v>
+        <v>268.2</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E12" s="7">
         <f>SUM(B12:D12)</f>
@@ -3773,17 +3773,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Christopher Crispin-Bailey</t>
+          <t>Dawn H Wood</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>532.6533333333334</v>
+        <v>910.85</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>164.2</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>462.35</v>
+        <v>175</v>
       </c>
       <c r="E13" s="7">
         <f>SUM(B13:D13)</f>
@@ -3793,17 +3793,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jo Iacovides</t>
+          <t>Andrew Pomfret</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>1010.355</v>
+        <v>836.1433333333334</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>348.2</v>
+        <v>164.2</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="E14" s="7">
         <f>SUM(B14:D14)</f>
@@ -3813,14 +3813,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Paul Cairns</t>
+          <t>Jacob Rigby</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>906.145</v>
+        <v>716.78</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1012.6</v>
+        <v>246.3</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>339.2</v>
@@ -3833,17 +3833,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dimitar Kazakov</t>
+          <t>Ian Gray</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>629.3</v>
+        <v>425.41</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>620.2</v>
+        <v>348.2</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>175</v>
+        <v>996</v>
       </c>
       <c r="E16" s="7">
         <f>SUM(B16:D16)</f>
@@ -3853,17 +3853,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Siamak Shahandashti</t>
+          <t>Steven Wright</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>459.84</v>
+        <v>540.71</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>478.3</v>
+        <v>452.2</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E17" s="7">
         <f>SUM(B17:D17)</f>
@@ -3873,17 +3873,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dawn H Wood</t>
+          <t>William Smith</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>910.85</v>
+        <v>1018.41</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>164.2</v>
+        <v>676.2</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>175</v>
+        <v>298.15</v>
       </c>
       <c r="E18" s="7">
         <f>SUM(B18:D18)</f>
@@ -3893,17 +3893,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alena Denisova</t>
+          <t>Joe Cutting</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>1058.415</v>
+        <v>1021.035</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>444.2</v>
+        <v>228.2</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="E19" s="7">
         <f>SUM(B19:D19)</f>
@@ -3913,17 +3913,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Peter Nightingale</t>
+          <t>Rob Alexander</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>1591.03</v>
+        <v>215.885</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>300.2</v>
+        <v>398.3</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E20" s="7">
         <f>SUM(B20:D20)</f>
@@ -3933,17 +3933,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Xinwei Fang</t>
+          <t>Paul Cairns</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>757.505</v>
+        <v>906.145</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>244.2</v>
+        <v>1012.6</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="E21" s="7">
         <f>SUM(B21:D21)</f>
@@ -3953,14 +3953,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Antonio Garcia-Dominguez</t>
+          <t>Jen Beeston</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>975.7866666666666</v>
+        <v>1029.8</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>644.6000000000001</v>
+        <v>332.2</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>175</v>
@@ -3973,17 +3973,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Da Li</t>
+          <t>Alena Denisova</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>410.8</v>
+        <v>1058.415</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>164.2</v>
+        <v>444.2</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="E23" s="7">
         <f>SUM(B23:D23)</f>
@@ -3993,17 +3993,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Andrew Pomfret</t>
+          <t>Fang Yan</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>836.1433333333334</v>
+        <v>461.48</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>164.2</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="E24" s="7">
         <f>SUM(B24:D24)</f>
@@ -4013,14 +4013,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Fang Yan</t>
+          <t>Kostas Barmpis</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>461.48</v>
+        <v>1069.833333333333</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>164.2</v>
+        <v>548.6</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>175</v>
@@ -4033,17 +4033,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>James Stovold</t>
+          <t>Steven Xiaotian Dai</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>1179.04</v>
+        <v>969.12</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>164.2</v>
+        <v>350.3</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>257.1</v>
+        <v>503.4</v>
       </c>
       <c r="E26" s="7">
         <f>SUM(B26:D26)</f>
@@ -4053,17 +4053,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Colin Paterson</t>
+          <t>Mike Freeman</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>228.8</v>
+        <v>857.1433333333334</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>579.76</v>
+        <v>164.2</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(B27:D27)</f>
@@ -4073,14 +4073,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Robbert Jongeling</t>
+          <t>Dimitar Kazakov</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>1009.28</v>
+        <v>629.3</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>164.2</v>
+        <v>620.2</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>175</v>
@@ -4093,14 +4093,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Carlo Ottaviani</t>
+          <t>Siamak Shahandashti</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>662.8816666666667</v>
+        <v>459.84</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>268.2</v>
+        <v>478.3</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>339.2</v>
@@ -4113,17 +4113,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pedro Ribeiro</t>
+          <t>Felix Ulrich-Oltean</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>1002.263333333333</v>
+        <v>423.43</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>644.6</v>
+        <v>212.2</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E30" s="7">
         <f>SUM(B30:D30)</f>
@@ -4133,17 +4133,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Frank Soboczenski</t>
+          <t>Peter Nightingale</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>463.8</v>
+        <v>1591.03</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>1794.42</v>
+        <v>300.2</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="E31" s="7">
         <f>SUM(B31:D31)</f>
@@ -4153,17 +4153,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pourya Shamsolmoali</t>
+          <t>James Walker</t>
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>1012.115</v>
+        <v>633.04</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>228.2</v>
+        <v>1000.8</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>298.15</v>
+        <v>175</v>
       </c>
       <c r="E32" s="7">
         <f>SUM(B32:D32)</f>
@@ -4173,17 +4173,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alvaro Miyazawa</t>
+          <t>Simon Foster</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>595.55</v>
+        <v>445.0966666666667</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>268.2</v>
+        <v>276.2</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E33" s="7">
         <f>SUM(B33:D33)</f>
@@ -4193,17 +4193,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Steven Xiaotian Dai</t>
+          <t>Claire Ingram</t>
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>969.12</v>
+        <v>227.885</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>350.3</v>
+        <v>164.2</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>503.4</v>
+        <v>257.1</v>
       </c>
       <c r="E34" s="7">
         <f>SUM(B34:D34)</f>
@@ -4213,17 +4213,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Soumya Banerjee</t>
+          <t>James Stovold</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>1121.84</v>
+        <v>1179.04</v>
       </c>
       <c r="C35" s="7" t="n">
         <v>164.2</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E35" s="7">
         <f>SUM(B35:D35)</f>
@@ -4233,17 +4233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Steven Wright</t>
+          <t>Katrina Attwood</t>
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>540.71</v>
+        <v>1093.56</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>452.2</v>
+        <v>212.2</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="E36" s="7">
         <f>SUM(B36:D36)</f>
@@ -4253,17 +4253,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Radu Calinescu</t>
+          <t>Mike O'Dea</t>
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>186.43</v>
+        <v>842.075</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>918.7</v>
+        <v>164.2</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E37" s="7">
         <f>SUM(B37:D37)</f>
@@ -4273,14 +4273,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jen Beeston</t>
+          <t>Colin Paterson</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>1029.8</v>
+        <v>228.8</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>332.2</v>
+        <v>579.76</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>175</v>
@@ -4293,17 +4293,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Vasileios Vasilakis</t>
+          <t>Robbert Jongeling</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>332.795</v>
+        <v>1009.28</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>356.2</v>
+        <v>164.2</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E39" s="7">
         <f>SUM(B39:D39)</f>
@@ -4313,17 +4313,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mike Freeman</t>
+          <t>Roberto Metere</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>857.1433333333334</v>
+        <v>1079.741666666667</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>164.2</v>
+        <v>268.2</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="E40" s="7">
         <f>SUM(B40:D40)</f>
@@ -4333,17 +4333,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Adrian Bors</t>
+          <t>Yan Jia</t>
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>677.3</v>
+        <v>468.67</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>412.2</v>
+        <v>638.7</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="E41" s="7">
         <f>SUM(B41:D41)</f>
@@ -4353,17 +4353,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Yuchen Zhao</t>
+          <t>Detlef Plump</t>
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>766.35</v>
+        <v>333.66</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>180.2</v>
+        <v>260.2</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>257.1</v>
+        <v>503.4</v>
       </c>
       <c r="E42" s="7">
         <f>SUM(B42:D42)</f>
@@ -4373,17 +4373,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mike O'Dea</t>
+          <t>Dimitris Kolovos</t>
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>842.075</v>
+        <v>413.92</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>164.2</v>
+        <v>1114.9</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="E43" s="7">
         <f>SUM(B43:D43)</f>
@@ -4393,17 +4393,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tommy Yuan</t>
+          <t>Frank Soboczenski</t>
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>1703.513333333333</v>
+        <v>463.8</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>364.2</v>
+        <v>1794.42</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="E44" s="7">
         <f>SUM(B44:D44)</f>
@@ -4413,17 +4413,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kofi Appiah</t>
+          <t>Xinwei Fang</t>
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>861.85</v>
+        <v>757.505</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>356.2</v>
+        <v>244.2</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>421.3</v>
+        <v>257.1</v>
       </c>
       <c r="E45" s="7">
         <f>SUM(B45:D45)</f>
@@ -4433,17 +4433,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Claudio Guarnera</t>
+          <t>Tommy Yuan</t>
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>536.04</v>
+        <v>1703.513333333333</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>276.2</v>
+        <v>364.2</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E46" s="7">
         <f>SUM(B46:D46)</f>
@@ -4453,14 +4453,14 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>William Smith</t>
+          <t>Pourya Shamsolmoali</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>1018.41</v>
+        <v>1012.115</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>676.2</v>
+        <v>228.2</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>298.15</v>
@@ -4473,17 +4473,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Claire Ingram</t>
+          <t>Christopher Crispin-Bailey</t>
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>227.885</v>
+        <v>532.6533333333334</v>
       </c>
       <c r="C48" s="7" t="n">
         <v>164.2</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>257.1</v>
+        <v>462.35</v>
       </c>
       <c r="E48" s="7">
         <f>SUM(B48:D48)</f>
@@ -4493,14 +4493,14 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Roberto Metere</t>
+          <t>Da Li</t>
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>1079.741666666667</v>
+        <v>410.8</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>268.2</v>
+        <v>164.2</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>175</v>
@@ -4513,17 +4513,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Dimitris Kolovos</t>
+          <t>Vasileios Vasilakis</t>
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>413.92</v>
+        <v>332.795</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>1114.9</v>
+        <v>356.2</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E50" s="7">
         <f>SUM(B50:D50)</f>
@@ -4533,14 +4533,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Rob Alexander</t>
+          <t>Antonio Garcia-Dominguez</t>
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>215.885</v>
+        <v>975.7866666666666</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>398.3</v>
+        <v>644.6000000000001</v>
       </c>
       <c r="D51" s="7" t="n">
         <v>175</v>
@@ -4553,17 +4553,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Detlef Plump</t>
+          <t>Pedro Ribeiro</t>
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>333.66</v>
+        <v>1002.263333333333</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>260.2</v>
+        <v>644.6</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>503.4</v>
+        <v>339.2</v>
       </c>
       <c r="E52" s="7">
         <f>SUM(B52:D52)</f>
@@ -4573,17 +4573,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ian Gray</t>
+          <t>Poonam Yadav</t>
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>425.41</v>
+        <v>562.12</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>348.2</v>
+        <v>1112.8</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>996</v>
+        <v>339.2</v>
       </c>
       <c r="E53" s="7">
         <f>SUM(B53:D53)</f>
@@ -4593,17 +4593,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Yan Jia</t>
+          <t>Adrian Bors</t>
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>468.67</v>
+        <v>677.3</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>638.7</v>
+        <v>412.2</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E54" s="7">
         <f>SUM(B54:D54)</f>
@@ -4613,17 +4613,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Stefano Pirandola</t>
+          <t>Pengcheng Liu</t>
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>810.8150000000001</v>
+        <v>229.3</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>520.4000000000001</v>
+        <v>996.5800000000002</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>421.3</v>
+        <v>175</v>
       </c>
       <c r="E55" s="7">
         <f>SUM(B55:D55)</f>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -906,79 +906,79 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Radu Calinescu</t>
+          <t>Katrina Attwood</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1280.13</v>
+        <v>1809.16</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>186.43</v>
+        <v>1093.56</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>918.7</v>
+        <v>212.2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Practicals: 4 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 14.0h/teacher; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h; Grant ARISE: Accelerating ReIntroduction of EcoSystem-Engineering Ant Colonies with Embodied AI: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h; Grant MammoBot: Robotic Posture Assistance for Universal Breast Screening Access: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Director of Students: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Yuchen Zhao</t>
+          <t>Xinwei Fang</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1203.65</v>
+        <v>1258.805</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>766.35</v>
+        <v>757.505</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>180.2</v>
+        <v>244.2</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>257.1</v>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 5 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 17.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Practicals: 4 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 14.0h/teacher; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x assessor (8h each) = 16.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -1000,37 +1000,37 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Carlo Ottaviani</t>
+          <t>Andrew Pomfret</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1270.281666666667</v>
+        <v>1257.443333333334</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>662.8816666666667</v>
+        <v>836.1433333333334</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>268.2</v>
+        <v>164.2</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x assessor (8h each) = 104.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -1047,42 +1047,42 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Stefano Pirandola</t>
+          <t>Alena Denisova</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1752.515</v>
+        <v>2006.015</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>810.8150000000001</v>
+        <v>1058.415</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>520.4000000000001</v>
+        <v>444.2</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>421.3</v>
+        <v>503.4</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Practicals: 11 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 52.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Integrated Quantum Networks (IQN) Hub: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 4x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 280.0h</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Ethics Committee Chair: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -1094,37 +1094,37 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Nick Pears</t>
+          <t>Pourya Shamsolmoali</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1632.513333333333</v>
+        <v>1538.465</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>372.5133333333333</v>
+        <v>1012.115</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>428.2</v>
+        <v>228.2</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>831.8000000000001</v>
+        <v>298.15</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 264.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Deputy Head (Research): 40% of 1642h = 656.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Graduate School Board (Ordinary member): 2% of 1642h = 41.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -1141,131 +1141,131 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Jo Iacovides</t>
+          <t>Dawn H Wood</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1697.755</v>
+        <v>1250.05</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1010.355</v>
+        <v>910.85</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>348.2</v>
+        <v>164.2</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 184.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Soumya Banerjee</t>
+          <t>Poonam Yadav</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1461.04</v>
+        <v>2014.12</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1121.84</v>
+        <v>562.12</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>164.2</v>
+        <v>1112.8</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h; Grant CHEDDAR Funding Apr-Sep 26- PSU296: 5% of 1642h = 82.1h; Grant REMOTE: Resilient and Secure Multi-Access Interoperable Communication Fabric for TinyEdge: 20% of 1642h = 328.4h; Grant Orchestrated mobile Network for Blackpool intelligent transport: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Claudio Guarnera</t>
+          <t>Yuchen Zhao</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>987.24</v>
+        <v>1203.65</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>536.04</v>
+        <v>766.35</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>276.2</v>
+        <v>180.2</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 5 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 17.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
+          <t>PhD supervision: 2x assessor (8h each) = 16.0h</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -1275,44 +1275,44 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Sam Braunstein</t>
+          <t>Pengcheng Liu</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1151.591666666667</v>
+        <v>1400.88</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>812.3916666666668</v>
+        <v>229.3</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>164.2</v>
+        <v>996.5800000000002</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Practicals: 11 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 52.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Intelligent Dependable Environment Control for Sustainable Aquaculture: 20% of 1642h = 328.4h; Grant Establishing a Safe AI Research Hub: York–UTM–UTB Twin-Lab Initiative: 9% of 1642h = 147.8h; Grant Establishment of Korea–UK Collaboration Platform for Convergent Research in Quantum Photonics and Artificial Intelligence - Yr2: 5% of 1642h = 82.1h; Grant SCHEME: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Graduate School Board (GSB) Chair: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -1322,96 +1322,96 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Kofi Appiah</t>
+          <t>Antonio Garcia-Dominguez</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1639.35</v>
+        <v>1795.386666666667</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>861.85</v>
+        <v>975.7866666666666</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>356.2</v>
+        <v>644.6000000000001</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>421.3</v>
+        <v>175</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; ELLA (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Deputy Director of Admissions (UG Admissions): 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Miyazawa</t>
+          <t>Kostas Barmpis</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1202.95</v>
+        <v>1793.433333333333</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>595.55</v>
+        <v>1069.833333333333</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>268.2</v>
+        <v>548.6</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>PGR Training Officer: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1423,37 +1423,37 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Dawn H Wood</t>
+          <t>Siamak Shahandashti</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1250.05</v>
+        <v>1277.34</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>910.85</v>
+        <v>459.84</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>164.2</v>
+        <v>478.3</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h; Grant Participatory Harm Auditing Workbenches &amp; Methodologies: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1463,24 +1463,24 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Andrew Pomfret</t>
+          <t>Mike Freeman</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1257.443333333334</v>
+        <v>1278.443333333334</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>836.1433333333334</v>
+        <v>857.1433333333334</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>164.2</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1517,84 +1517,84 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Jacob Rigby</t>
+          <t>Simon Foster</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1302.28</v>
+        <v>896.2966666666666</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>716.78</v>
+        <v>445.0966666666667</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>246.3</v>
+        <v>276.2</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Projects (40cr): Standard (2.5x): 40.0h/teacher @ 2.5x = 100.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 39.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Grant EPSRC: Addressing environmental injustices through transdisciplinary science and technology: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Taught Project Coordinator: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Ian Gray</t>
+          <t>Da Li</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1769.61</v>
+        <v>750</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>425.41</v>
+        <v>410.8</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>348.2</v>
+        <v>164.2</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>996</v>
+        <v>175</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher</t>
+          <t>SYS3 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Deputy Head of Department (On-campus teaching): 50% of 1642h = 821.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1604,49 +1604,49 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Steven Wright</t>
+          <t>Frank Soboczenski</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1167.91</v>
+        <v>2515.32</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>540.71</v>
+        <v>463.8</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>452.2</v>
+        <v>1794.42</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>LLMA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 11% of 1642h = 180.6h; Grant Alan Turing AI Fellowship: 80% of 1642h = 1313.6h</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Chair of the Board of Examiners: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1658,42 +1658,42 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>William Smith</t>
+          <t>Paul Cairns</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1992.76</v>
+        <v>2257.945</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1018.41</v>
+        <v>906.145</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>676.2</v>
+        <v>1012.6</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>298.15</v>
+        <v>339.2</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; DEEP (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h</t>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h; Grant BiB Centre for Social Change: 0% of 1642h = 0.0h; Grant IGGI: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; REF Lead: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -1705,37 +1705,37 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Joe Cutting</t>
+          <t>Dimitris Kolovos</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1424.235</v>
+        <v>1703.82</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1021.035</v>
+        <v>413.92</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>228.2</v>
+        <v>1114.9</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 376.0h; Grant Socially-Acceptable and Trustworthy Human-Robot Teaming for Agile Industries (SYMPHONY Resubmission): 5% of 1642h = 82.1h; Grant MOSAICO: 5% of 1642h = 82.1h; Grant SCHEME: 20% of 1642h = 328.4h; Grant Cavecore: Doctoral Network on Continuous, Automated Validation, and Evaluation of Cognitive Robots in Open-Ended Environments: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>ECR rep: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1745,44 +1745,44 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Rob Alexander</t>
+          <t>Kofi Appiah</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>789.1849999999999</v>
+        <v>1639.35</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>215.885</v>
+        <v>861.85</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>398.3</v>
+        <v>356.2</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>175</v>
+        <v>421.3</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 2 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 8.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Director of Admissions (UG Admissions): 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -1799,37 +1799,37 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Paul Cairns</t>
+          <t>Felix Ulrich-Oltean</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>2257.945</v>
+        <v>810.63</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>906.145</v>
+        <v>423.43</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1012.6</v>
+        <v>212.2</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h; Grant BiB Centre for Social Change: 0% of 1642h = 0.0h; Grant IGGI: 20% of 1642h = 328.4h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; REF Lead: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1839,49 +1839,49 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Jen Beeston</t>
+          <t>Adrian Bors</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1537</v>
+        <v>1346.6</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1029.8</v>
+        <v>677.3</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>332.2</v>
+        <v>412.2</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 168.0h</t>
+          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x assessor (8h each) = 248.0h</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Chair of the Department Education Committee: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Internationalisation and Visitors Coordinator: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -1893,79 +1893,79 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Alena Denisova</t>
+          <t>Radu Calinescu</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2006.015</v>
+        <v>1280.13</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1058.415</v>
+        <v>186.43</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>444.2</v>
+        <v>918.7</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Practicals: 4 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 14.0h/teacher; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 4x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 280.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h; Grant ARISE: Accelerating ReIntroduction of EcoSystem-Engineering Ant Colonies with Embodied AI: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h; Grant MammoBot: Robotic Posture Assistance for Universal Breast Screening Access: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Ethics Committee Chair: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Fang Yan</t>
+          <t>Yan Jia</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>800.6800000000001</v>
+        <v>1282.37</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>461.48</v>
+        <v>468.67</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>164.2</v>
+        <v>638.7</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>SOF2 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; THE3 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Pastoral: 9 students x 3h = 27.0h; Also teaches: Foundations of Safe AI (Safe AI 1), Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10% of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -1987,42 +1987,42 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Kostas Barmpis</t>
+          <t>Detlef Plump</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1793.433333333333</v>
+        <v>1097.26</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1069.833333333333</v>
+        <v>333.66</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>548.6</v>
+        <v>260.2</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>PGR Training Officer: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>EC Officer (on-campus): 15% of 1642h = 246.3h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -2034,37 +2034,37 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Steven Xiaotian Dai</t>
+          <t>Ian Gray</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1822.82</v>
+        <v>1769.61</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>969.12</v>
+        <v>425.41</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>350.3</v>
+        <v>348.2</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>503.4</v>
+        <v>996</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h; Grant SCHEME: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Student Disability Representative: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Head of Department (On-campus teaching): 50% of 1642h = 821.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -2081,42 +2081,42 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Mike Freeman</t>
+          <t>Peter Nightingale</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1278.443333333334</v>
+        <v>2230.43</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>857.1433333333334</v>
+        <v>1591.03</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>164.2</v>
+        <v>300.2</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; ARIA (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>UG PL: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -2128,42 +2128,42 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Dimitar Kazakov</t>
+          <t>Alvaro Miyazawa</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1424.5</v>
+        <v>1202.95</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>629.3</v>
+        <v>595.55</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>620.2</v>
+        <v>268.2</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 5x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Ethics Committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -2175,42 +2175,42 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Siamak Shahandashti</t>
+          <t>James Stovold</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1277.34</v>
+        <v>1600.34</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>459.84</v>
+        <v>1179.04</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>478.3</v>
+        <v>164.2</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DEEP (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; LLMA (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h; Grant Participatory Harm Auditing Workbenches &amp; Methodologies: 5% of 1642h = 82.1h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -2222,32 +2222,32 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Felix Ulrich-Oltean</t>
+          <t>Claudio Guarnera</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>810.63</v>
+        <v>987.24</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>423.43</v>
+        <v>536.04</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>212.2</v>
+        <v>276.2</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher</t>
+          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -2269,84 +2269,84 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Peter Nightingale</t>
+          <t>James Walker</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2230.43</v>
+        <v>1808.84</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>1591.03</v>
+        <v>633.04</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>300.2</v>
+        <v>1000.8</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; ARIA (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h; Grant Smart Data Donation Service (SDDS): 10% of 1642h = 164.2h; Grant IGGI: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>UG PL: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>James Walker</t>
+          <t>Roberto Metere</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1808.84</v>
+        <v>1522.941666666667</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>633.04</v>
+        <v>1079.741666666667</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1000.8</v>
+        <v>268.2</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h; Grant Smart Data Donation Service (SDDS): 10% of 1642h = 164.2h; Grant IGGI: 20% of 1642h = 328.4h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -2356,71 +2356,71 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Simon Foster</t>
+          <t>Jen Beeston</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>896.2966666666666</v>
+        <v>1537</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>445.0966666666667</v>
+        <v>1029.8</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>276.2</v>
+        <v>332.2</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 168.0h</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Chair of the Department Education Committee: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Claire Ingram</t>
+          <t>Mike O'Dea</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>649.1849999999999</v>
+        <v>1263.375</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>227.885</v>
+        <v>842.075</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>164.2</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 2 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 8.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 1 students x 3h = 3.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
+          <t>CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Outreach and Extra-Curricular Activities: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -2457,42 +2457,42 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>James Stovold</t>
+          <t>Joe Cutting</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1600.34</v>
+        <v>1424.235</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>1179.04</v>
+        <v>1021.035</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>164.2</v>
+        <v>228.2</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>DEEP (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; LLMA (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>ECR rep: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2504,42 +2504,42 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Katrina Attwood</t>
+          <t>Christopher Crispin-Bailey</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1809.16</v>
+        <v>1159.203333333333</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1093.56</v>
+        <v>532.6533333333334</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>212.2</v>
+        <v>164.2</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>503.4</v>
+        <v>462.35</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Director of Students: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>GTA Coordinator: 10% of 1642h = 164.2h; Union: 8% of 1642h = 123.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -2551,42 +2551,42 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Mike O'Dea</t>
+          <t>Jacob Rigby</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1263.375</v>
+        <v>1302.28</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>842.075</v>
+        <v>716.78</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>164.2</v>
+        <v>246.3</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher</t>
+          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Projects (40cr): Standard (2.5x): 40.0h/teacher @ 2.5x = 100.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 39.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>Grant EPSRC: Addressing environmental injustices through transdisciplinary science and technology: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Taught Project Coordinator: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -2598,37 +2598,37 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Colin Paterson</t>
+          <t>Jo Iacovides</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>983.5599999999999</v>
+        <v>1697.755</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>228.8</v>
+        <v>1010.355</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>579.76</v>
+        <v>348.2</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>LPTC (20cr): Standard (2.5x): 10.0h/teacher @ 2.5x = 25.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
+          <t>QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 120.0h; Grant KTP with Advai (Industry): 3% of 1642h = 49.3h; Grant KTP with Advai: 5% of 1642h = 82.1h; Grant A STAR TO STEER BY: 5% of 1642h = 82.1h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 184.0h</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
@@ -2638,39 +2638,39 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Robbert Jongeling</t>
+          <t>Colin Paterson</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1348.48</v>
+        <v>983.5599999999999</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1009.28</v>
+        <v>228.8</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>164.2</v>
+        <v>579.76</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 2 students x 3h = 6.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>LPTC (20cr): Standard (2.5x): 10.0h/teacher @ 2.5x = 25.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 120.0h; Grant KTP with Advai (Industry): 3% of 1642h = 49.3h; Grant KTP with Advai: 5% of 1642h = 82.1h; Grant A STAR TO STEER BY: 5% of 1642h = 82.1h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2692,37 +2692,37 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Roberto Metere</t>
+          <t>Pedro Ribeiro</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1522.941666666667</v>
+        <v>1986.063333333333</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>1079.741666666667</v>
+        <v>1002.263333333333</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>268.2</v>
+        <v>644.6</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -2739,37 +2739,37 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Yan Jia</t>
+          <t>Steven Wright</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1282.37</v>
+        <v>1167.91</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>468.67</v>
+        <v>540.71</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>638.7</v>
+        <v>452.2</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10% of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Chair of the Board of Examiners: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -2779,44 +2779,44 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Detlef Plump</t>
+          <t>Claire Ingram</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1097.26</v>
+        <v>649.1849999999999</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>333.66</v>
+        <v>227.885</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>260.2</v>
+        <v>164.2</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>503.4</v>
+        <v>257.1</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 2 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 8.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 1 students x 3h = 3.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>EC Officer (on-campus): 15% of 1642h = 246.3h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Outreach and Extra-Curricular Activities: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -2833,37 +2833,37 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Dimitris Kolovos</t>
+          <t>Dimitar Kazakov</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1703.82</v>
+        <v>1424.5</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>413.92</v>
+        <v>629.3</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>1114.9</v>
+        <v>620.2</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher</t>
+          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 376.0h; Grant Socially-Acceptable and Trustworthy Human-Robot Teaming for Agile Industries (SYMPHONY Resubmission): 5% of 1642h = 82.1h; Grant MOSAICO: 5% of 1642h = 82.1h; Grant SCHEME: 20% of 1642h = 328.4h; Grant Cavecore: Doctoral Network on Continuous, Automated Validation, and Evaluation of Cognitive Robots in Open-Ended Environments: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 5x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Ethics Committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -2873,49 +2873,49 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Frank Soboczenski</t>
+          <t>Nick Pears</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>2515.32</v>
+        <v>1632.513333333333</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>463.8</v>
+        <v>372.5133333333333</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>1794.42</v>
+        <v>428.2</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>257.1</v>
+        <v>831.8000000000001</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>LLMA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
+          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 11% of 1642h = 180.6h; Grant Alan Turing AI Fellowship: 80% of 1642h = 1313.6h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 264.0h</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Head (Research): 40% of 1642h = 656.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -2927,37 +2927,37 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Xinwei Fang</t>
+          <t>Rob Alexander</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1258.805</v>
+        <v>789.1849999999999</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>757.505</v>
+        <v>215.885</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>244.2</v>
+        <v>398.3</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Practicals: 4 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 14.0h/teacher; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 2 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 8.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -2974,84 +2974,84 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Tommy Yuan</t>
+          <t>Fang Yan</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2406.913333333333</v>
+        <v>800.6800000000001</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>1703.513333333333</v>
+        <v>461.48</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>364.2</v>
+        <v>164.2</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; ARIA (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SOF2 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; THE3 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Foundations of Safe AI (Safe AI 1), Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 200.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Deputy CBoEs: 10% of 1642h = 164.2h; StAMP committee members: 0% of 1642h = 0.0h; CSCSE SQA Partnership Leader: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Pourya Shamsolmoali</t>
+          <t>Steven Xiaotian Dai</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1538.465</v>
+        <v>1822.82</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>1012.115</v>
+        <v>969.12</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>228.2</v>
+        <v>350.3</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>298.15</v>
+        <v>503.4</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h; Grant SCHEME: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Graduate School Board (Ordinary member): 2% of 1642h = 41.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Student Disability Representative: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
@@ -3068,37 +3068,37 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Christopher Crispin-Bailey</t>
+          <t>Carlo Ottaviani</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1159.203333333333</v>
+        <v>1270.281666666667</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>532.6533333333334</v>
+        <v>662.8816666666667</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>164.2</v>
+        <v>268.2</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>462.35</v>
+        <v>339.2</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>GTA Coordinator: 10% of 1642h = 164.2h; Union: 8% of 1642h = 123.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
@@ -3115,37 +3115,37 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Da Li</t>
+          <t>Stefano Pirandola</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>750</v>
+        <v>1752.515</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>410.8</v>
+        <v>810.8150000000001</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>164.2</v>
+        <v>520.4000000000001</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>175</v>
+        <v>421.3</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Practicals: 11 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 52.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Integrated Quantum Networks (IQN) Hub: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
@@ -3155,49 +3155,49 @@
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Vasileios Vasilakis</t>
+          <t>Tommy Yuan</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1028.195</v>
+        <v>2406.913333333333</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>332.795</v>
+        <v>1703.513333333333</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>356.2</v>
+        <v>364.2</v>
       </c>
       <c r="F50" s="3" t="n">
         <v>339.2</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 5 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 17.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; ARIA (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 200.0h</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy CBoEs: 10% of 1642h = 164.2h; StAMP committee members: 0% of 1642h = 0.0h; CSCSE SQA Partnership Leader: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -3209,84 +3209,84 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Antonio Garcia-Dominguez</t>
+          <t>William Smith</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1795.386666666667</v>
+        <v>1992.76</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>975.7866666666666</v>
+        <v>1018.41</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>644.6000000000001</v>
+        <v>676.2</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>175</v>
+        <v>298.15</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; ELLA (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; DEEP (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ribeiro</t>
+          <t>Sam Braunstein</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1986.063333333333</v>
+        <v>1151.591666666667</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>1002.263333333333</v>
+        <v>812.3916666666668</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>644.6</v>
+        <v>164.2</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Practicals: 11 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 52.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 20% of 1642h = 328.4h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
@@ -3296,44 +3296,44 @@
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Poonam Yadav</t>
+          <t>Vasileios Vasilakis</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>2014.12</v>
+        <v>1028.195</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>562.12</v>
+        <v>332.795</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>1112.8</v>
+        <v>356.2</v>
       </c>
       <c r="F53" s="3" t="n">
         <v>339.2</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 5 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 17.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h; Grant CHEDDAR Funding Apr-Sep 26- PSU296: 5% of 1642h = 82.1h; Grant REMOTE: Resilient and Secure Multi-Access Interoperable Communication Fabric for TinyEdge: 20% of 1642h = 328.4h; Grant Orchestrated mobile Network for Blackpool intelligent transport: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
@@ -3350,37 +3350,37 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Adrian Bors</t>
+          <t>Soumya Banerjee</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1346.6</v>
+        <v>1461.04</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>677.3</v>
+        <v>1121.84</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>412.2</v>
+        <v>164.2</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
+          <t>AURO (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x assessor (8h each) = 248.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>Internationalisation and Visitors Coordinator: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
@@ -3390,54 +3390,54 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Pengcheng Liu</t>
+          <t>Robbert Jongeling</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1400.88</v>
+        <v>1348.48</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>229.3</v>
+        <v>1009.28</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>996.5800000000002</v>
+        <v>164.2</v>
       </c>
       <c r="F55" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>ENG1 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 2 students x 3h = 6.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Intelligent Dependable Environment Control for Sustainable Aquaculture: 20% of 1642h = 328.4h; Grant Establishing a Safe AI Research Hub: York–UTM–UTB Twin-Lab Initiative: 9% of 1642h = 147.8h; Grant Establishment of Korea–UK Collaboration Platform for Convergent Research in Quantum Photonics and Artificial Intelligence - Yr2: 5% of 1642h = 82.1h; Grant SCHEME: 5% of 1642h = 82.1h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>Graduate School Board (GSB) Chair: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
@@ -3553,17 +3553,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Radu Calinescu</t>
+          <t>Katrina Attwood</t>
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>186.43</v>
+        <v>1093.56</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>918.7</v>
+        <v>212.2</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="E2" s="7">
         <f>SUM(B2:D2)</f>
@@ -3573,14 +3573,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Yuchen Zhao</t>
+          <t>Xinwei Fang</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>766.35</v>
+        <v>757.505</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>180.2</v>
+        <v>244.2</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>257.1</v>
@@ -3593,17 +3593,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Carlo Ottaviani</t>
+          <t>Andrew Pomfret</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>662.8816666666667</v>
+        <v>836.1433333333334</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>268.2</v>
+        <v>164.2</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="E4" s="7">
         <f>SUM(B4:D4)</f>
@@ -3613,17 +3613,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Stefano Pirandola</t>
+          <t>Alena Denisova</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>810.8150000000001</v>
+        <v>1058.415</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>520.4000000000001</v>
+        <v>444.2</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>421.3</v>
+        <v>503.4</v>
       </c>
       <c r="E5" s="7">
         <f>SUM(B5:D5)</f>
@@ -3633,17 +3633,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nick Pears</t>
+          <t>Pourya Shamsolmoali</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>372.5133333333333</v>
+        <v>1012.115</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>428.2</v>
+        <v>228.2</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>831.8000000000001</v>
+        <v>298.15</v>
       </c>
       <c r="E6" s="7">
         <f>SUM(B6:D6)</f>
@@ -3653,17 +3653,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jo Iacovides</t>
+          <t>Dawn H Wood</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1010.355</v>
+        <v>910.85</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>348.2</v>
+        <v>164.2</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E7" s="7">
         <f>SUM(B7:D7)</f>
@@ -3673,17 +3673,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Soumya Banerjee</t>
+          <t>Poonam Yadav</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>1121.84</v>
+        <v>562.12</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>164.2</v>
+        <v>1112.8</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E8" s="7">
         <f>SUM(B8:D8)</f>
@@ -3693,17 +3693,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Claudio Guarnera</t>
+          <t>Yuchen Zhao</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>536.04</v>
+        <v>766.35</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>276.2</v>
+        <v>180.2</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E9" s="7">
         <f>SUM(B9:D9)</f>
@@ -3713,14 +3713,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sam Braunstein</t>
+          <t>Pengcheng Liu</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>812.3916666666668</v>
+        <v>229.3</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>164.2</v>
+        <v>996.5800000000002</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>175</v>
@@ -3733,17 +3733,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kofi Appiah</t>
+          <t>Antonio Garcia-Dominguez</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>861.85</v>
+        <v>975.7866666666666</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>356.2</v>
+        <v>644.6000000000001</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>421.3</v>
+        <v>175</v>
       </c>
       <c r="E11" s="7">
         <f>SUM(B11:D11)</f>
@@ -3753,17 +3753,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alvaro Miyazawa</t>
+          <t>Kostas Barmpis</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>595.55</v>
+        <v>1069.833333333333</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>268.2</v>
+        <v>548.6</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E12" s="7">
         <f>SUM(B12:D12)</f>
@@ -3773,17 +3773,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dawn H Wood</t>
+          <t>Siamak Shahandashti</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>910.85</v>
+        <v>459.84</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>164.2</v>
+        <v>478.3</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E13" s="7">
         <f>SUM(B13:D13)</f>
@@ -3793,11 +3793,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Andrew Pomfret</t>
+          <t>Mike Freeman</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>836.1433333333334</v>
+        <v>857.1433333333334</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>164.2</v>
@@ -3813,17 +3813,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jacob Rigby</t>
+          <t>Simon Foster</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>716.78</v>
+        <v>445.0966666666667</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>246.3</v>
+        <v>276.2</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E15" s="7">
         <f>SUM(B15:D15)</f>
@@ -3833,17 +3833,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ian Gray</t>
+          <t>Da Li</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>425.41</v>
+        <v>410.8</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>348.2</v>
+        <v>164.2</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>996</v>
+        <v>175</v>
       </c>
       <c r="E16" s="7">
         <f>SUM(B16:D16)</f>
@@ -3853,17 +3853,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Steven Wright</t>
+          <t>Frank Soboczenski</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>540.71</v>
+        <v>463.8</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>452.2</v>
+        <v>1794.42</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E17" s="7">
         <f>SUM(B17:D17)</f>
@@ -3873,17 +3873,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>William Smith</t>
+          <t>Paul Cairns</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>1018.41</v>
+        <v>906.145</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>676.2</v>
+        <v>1012.6</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>298.15</v>
+        <v>339.2</v>
       </c>
       <c r="E18" s="7">
         <f>SUM(B18:D18)</f>
@@ -3893,14 +3893,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Joe Cutting</t>
+          <t>Dimitris Kolovos</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>1021.035</v>
+        <v>413.92</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>228.2</v>
+        <v>1114.9</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>175</v>
@@ -3913,17 +3913,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rob Alexander</t>
+          <t>Kofi Appiah</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>215.885</v>
+        <v>861.85</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>398.3</v>
+        <v>356.2</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>175</v>
+        <v>421.3</v>
       </c>
       <c r="E20" s="7">
         <f>SUM(B20:D20)</f>
@@ -3933,17 +3933,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Paul Cairns</t>
+          <t>Felix Ulrich-Oltean</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>906.145</v>
+        <v>423.43</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>1012.6</v>
+        <v>212.2</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E21" s="7">
         <f>SUM(B21:D21)</f>
@@ -3953,17 +3953,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jen Beeston</t>
+          <t>Adrian Bors</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>1029.8</v>
+        <v>677.3</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>332.2</v>
+        <v>412.2</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E22" s="7">
         <f>SUM(B22:D22)</f>
@@ -3973,17 +3973,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alena Denisova</t>
+          <t>Radu Calinescu</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>1058.415</v>
+        <v>186.43</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>444.2</v>
+        <v>918.7</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="E23" s="7">
         <f>SUM(B23:D23)</f>
@@ -3993,14 +3993,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fang Yan</t>
+          <t>Yan Jia</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>461.48</v>
+        <v>468.67</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>164.2</v>
+        <v>638.7</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>175</v>
@@ -4013,17 +4013,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kostas Barmpis</t>
+          <t>Detlef Plump</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>1069.833333333333</v>
+        <v>333.66</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>548.6</v>
+        <v>260.2</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="E25" s="7">
         <f>SUM(B25:D25)</f>
@@ -4033,17 +4033,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Steven Xiaotian Dai</t>
+          <t>Ian Gray</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>969.12</v>
+        <v>425.41</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>350.3</v>
+        <v>348.2</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>503.4</v>
+        <v>996</v>
       </c>
       <c r="E26" s="7">
         <f>SUM(B26:D26)</f>
@@ -4053,17 +4053,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mike Freeman</t>
+          <t>Peter Nightingale</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>857.1433333333334</v>
+        <v>1591.03</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>164.2</v>
+        <v>300.2</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(B27:D27)</f>
@@ -4073,17 +4073,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dimitar Kazakov</t>
+          <t>Alvaro Miyazawa</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>629.3</v>
+        <v>595.55</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>620.2</v>
+        <v>268.2</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E28" s="7">
         <f>SUM(B28:D28)</f>
@@ -4093,17 +4093,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Siamak Shahandashti</t>
+          <t>James Stovold</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>459.84</v>
+        <v>1179.04</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>478.3</v>
+        <v>164.2</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="E29" s="7">
         <f>SUM(B29:D29)</f>
@@ -4113,14 +4113,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Felix Ulrich-Oltean</t>
+          <t>Claudio Guarnera</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>423.43</v>
+        <v>536.04</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>212.2</v>
+        <v>276.2</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>175</v>
@@ -4133,17 +4133,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Peter Nightingale</t>
+          <t>James Walker</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>1591.03</v>
+        <v>633.04</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>300.2</v>
+        <v>1000.8</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E31" s="7">
         <f>SUM(B31:D31)</f>
@@ -4153,14 +4153,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>James Walker</t>
+          <t>Roberto Metere</t>
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>633.04</v>
+        <v>1079.741666666667</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>1000.8</v>
+        <v>268.2</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>175</v>
@@ -4173,14 +4173,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Simon Foster</t>
+          <t>Jen Beeston</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>445.0966666666667</v>
+        <v>1029.8</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>276.2</v>
+        <v>332.2</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>175</v>
@@ -4193,11 +4193,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Claire Ingram</t>
+          <t>Mike O'Dea</t>
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>227.885</v>
+        <v>842.075</v>
       </c>
       <c r="C34" s="7" t="n">
         <v>164.2</v>
@@ -4213,17 +4213,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>James Stovold</t>
+          <t>Joe Cutting</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>1179.04</v>
+        <v>1021.035</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>164.2</v>
+        <v>228.2</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="E35" s="7">
         <f>SUM(B35:D35)</f>
@@ -4233,17 +4233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Katrina Attwood</t>
+          <t>Christopher Crispin-Bailey</t>
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>1093.56</v>
+        <v>532.6533333333334</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>212.2</v>
+        <v>164.2</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>503.4</v>
+        <v>462.35</v>
       </c>
       <c r="E36" s="7">
         <f>SUM(B36:D36)</f>
@@ -4253,17 +4253,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mike O'Dea</t>
+          <t>Jacob Rigby</t>
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>842.075</v>
+        <v>716.78</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>164.2</v>
+        <v>246.3</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="E37" s="7">
         <f>SUM(B37:D37)</f>
@@ -4273,17 +4273,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Colin Paterson</t>
+          <t>Jo Iacovides</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>228.8</v>
+        <v>1010.355</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>579.76</v>
+        <v>348.2</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E38" s="7">
         <f>SUM(B38:D38)</f>
@@ -4293,14 +4293,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Robbert Jongeling</t>
+          <t>Colin Paterson</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>1009.28</v>
+        <v>228.8</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>164.2</v>
+        <v>579.76</v>
       </c>
       <c r="D39" s="7" t="n">
         <v>175</v>
@@ -4313,17 +4313,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Roberto Metere</t>
+          <t>Pedro Ribeiro</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>1079.741666666667</v>
+        <v>1002.263333333333</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>268.2</v>
+        <v>644.6</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E40" s="7">
         <f>SUM(B40:D40)</f>
@@ -4333,14 +4333,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Yan Jia</t>
+          <t>Steven Wright</t>
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>468.67</v>
+        <v>540.71</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>638.7</v>
+        <v>452.2</v>
       </c>
       <c r="D41" s="7" t="n">
         <v>175</v>
@@ -4353,17 +4353,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Detlef Plump</t>
+          <t>Claire Ingram</t>
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>333.66</v>
+        <v>227.885</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>260.2</v>
+        <v>164.2</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>503.4</v>
+        <v>257.1</v>
       </c>
       <c r="E42" s="7">
         <f>SUM(B42:D42)</f>
@@ -4373,14 +4373,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Dimitris Kolovos</t>
+          <t>Dimitar Kazakov</t>
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>413.92</v>
+        <v>629.3</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>1114.9</v>
+        <v>620.2</v>
       </c>
       <c r="D43" s="7" t="n">
         <v>175</v>
@@ -4393,17 +4393,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Frank Soboczenski</t>
+          <t>Nick Pears</t>
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>463.8</v>
+        <v>372.5133333333333</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>1794.42</v>
+        <v>428.2</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>257.1</v>
+        <v>831.8000000000001</v>
       </c>
       <c r="E44" s="7">
         <f>SUM(B44:D44)</f>
@@ -4413,17 +4413,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Xinwei Fang</t>
+          <t>Rob Alexander</t>
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>757.505</v>
+        <v>215.885</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>244.2</v>
+        <v>398.3</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="E45" s="7">
         <f>SUM(B45:D45)</f>
@@ -4433,17 +4433,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tommy Yuan</t>
+          <t>Fang Yan</t>
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>1703.513333333333</v>
+        <v>461.48</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>364.2</v>
+        <v>164.2</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E46" s="7">
         <f>SUM(B46:D46)</f>
@@ -4453,17 +4453,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pourya Shamsolmoali</t>
+          <t>Steven Xiaotian Dai</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>1012.115</v>
+        <v>969.12</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>228.2</v>
+        <v>350.3</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>298.15</v>
+        <v>503.4</v>
       </c>
       <c r="E47" s="7">
         <f>SUM(B47:D47)</f>
@@ -4473,17 +4473,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Christopher Crispin-Bailey</t>
+          <t>Carlo Ottaviani</t>
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>532.6533333333334</v>
+        <v>662.8816666666667</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>164.2</v>
+        <v>268.2</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>462.35</v>
+        <v>339.2</v>
       </c>
       <c r="E48" s="7">
         <f>SUM(B48:D48)</f>
@@ -4493,17 +4493,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Da Li</t>
+          <t>Stefano Pirandola</t>
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>410.8</v>
+        <v>810.8150000000001</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>164.2</v>
+        <v>520.4000000000001</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>175</v>
+        <v>421.3</v>
       </c>
       <c r="E49" s="7">
         <f>SUM(B49:D49)</f>
@@ -4513,14 +4513,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Vasileios Vasilakis</t>
+          <t>Tommy Yuan</t>
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>332.795</v>
+        <v>1703.513333333333</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>356.2</v>
+        <v>364.2</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>339.2</v>
@@ -4533,17 +4533,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Antonio Garcia-Dominguez</t>
+          <t>William Smith</t>
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>975.7866666666666</v>
+        <v>1018.41</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>644.6000000000001</v>
+        <v>676.2</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>175</v>
+        <v>298.15</v>
       </c>
       <c r="E51" s="7">
         <f>SUM(B51:D51)</f>
@@ -4553,17 +4553,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pedro Ribeiro</t>
+          <t>Sam Braunstein</t>
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>1002.263333333333</v>
+        <v>812.3916666666668</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>644.6</v>
+        <v>164.2</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E52" s="7">
         <f>SUM(B52:D52)</f>
@@ -4573,14 +4573,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Poonam Yadav</t>
+          <t>Vasileios Vasilakis</t>
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>562.12</v>
+        <v>332.795</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>1112.8</v>
+        <v>356.2</v>
       </c>
       <c r="D53" s="7" t="n">
         <v>339.2</v>
@@ -4593,17 +4593,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Adrian Bors</t>
+          <t>Soumya Banerjee</t>
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>677.3</v>
+        <v>1121.84</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>412.2</v>
+        <v>164.2</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="E54" s="7">
         <f>SUM(B54:D54)</f>
@@ -4613,14 +4613,14 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Pengcheng Liu</t>
+          <t>Robbert Jongeling</t>
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>229.3</v>
+        <v>1009.28</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>996.5800000000002</v>
+        <v>164.2</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>175</v>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -906,37 +906,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Katrina Attwood</t>
+          <t>Adrian Bors</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1809.16</v>
+        <v>1346.6</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1093.56</v>
+        <v>677.3</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>212.2</v>
+        <v>412.2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>503.4</v>
+        <v>257.1</v>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
+          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x assessor (8h each) = 248.0h</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Director of Students: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Internationalisation and Visitors Coordinator: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
@@ -953,42 +953,42 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Xinwei Fang</t>
+          <t>Alena Denisova</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1258.805</v>
+        <v>2006.015</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>757.505</v>
+        <v>1058.415</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>244.2</v>
+        <v>444.2</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>257.1</v>
+        <v>503.4</v>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Practicals: 4 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 14.0h/teacher; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 4x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 280.0h</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Ethics Committee Chair: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -1000,37 +1000,37 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Andrew Pomfret</t>
+          <t>Alvaro Miyazawa</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1257.443333333334</v>
+        <v>1202.95</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>836.1433333333334</v>
+        <v>595.55</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>164.2</v>
+        <v>268.2</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -1047,42 +1047,42 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Alena Denisova</t>
+          <t>Andrew Pomfret</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2006.015</v>
+        <v>1257.443333333334</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1058.415</v>
+        <v>836.1433333333334</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>444.2</v>
+        <v>164.2</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>503.4</v>
+        <v>257.1</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 4x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 280.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Ethics Committee Chair: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -1094,84 +1094,84 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Pourya Shamsolmoali</t>
+          <t>Antonio Garcia-Dominguez</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1538.465</v>
+        <v>1795.386666666667</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1012.115</v>
+        <v>975.7866666666666</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>228.2</v>
+        <v>644.6000000000001</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>298.15</v>
+        <v>175</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>ELLA (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Graduate School Board (Ordinary member): 2% of 1642h = 41.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Dawn H Wood</t>
+          <t>Carlo Ottaviani</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1250.05</v>
+        <v>1270.281666666667</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>910.85</v>
+        <v>662.8816666666667</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>164.2</v>
+        <v>268.2</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -1181,44 +1181,44 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Poonam Yadav</t>
+          <t>Christopher Crispin-Bailey</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2014.12</v>
+        <v>1159.203333333333</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>562.12</v>
+        <v>532.6533333333334</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1112.8</v>
+        <v>164.2</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>339.2</v>
+        <v>462.35</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h; Grant CHEDDAR Funding Apr-Sep 26- PSU296: 5% of 1642h = 82.1h; Grant REMOTE: Resilient and Secure Multi-Access Interoperable Communication Fabric for TinyEdge: 20% of 1642h = 328.4h; Grant Orchestrated mobile Network for Blackpool intelligent transport: 5% of 1642h = 82.1h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>GTA Coordinator: 10% of 1642h = 164.2h; Union: 8% of 1642h = 123.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -1235,37 +1235,37 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Yuchen Zhao</t>
+          <t>Claire Ingram</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1203.65</v>
+        <v>649.1849999999999</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>766.35</v>
+        <v>227.885</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>180.2</v>
+        <v>164.2</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>257.1</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 5 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 17.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 2 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 8.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 1 students x 3h = 3.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x assessor (8h each) = 16.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Outreach and Extra-Curricular Activities: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -1282,37 +1282,37 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Pengcheng Liu</t>
+          <t>Claudio Guarnera</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1400.88</v>
+        <v>987.24</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>229.3</v>
+        <v>536.04</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>996.5800000000002</v>
+        <v>276.2</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Intelligent Dependable Environment Control for Sustainable Aquaculture: 20% of 1642h = 328.4h; Grant Establishing a Safe AI Research Hub: York–UTM–UTB Twin-Lab Initiative: 9% of 1642h = 147.8h; Grant Establishment of Korea–UK Collaboration Platform for Convergent Research in Quantum Photonics and Artificial Intelligence - Yr2: 5% of 1642h = 82.1h; Grant SCHEME: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Graduate School Board (GSB) Chair: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -1322,39 +1322,39 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Antonio Garcia-Dominguez</t>
+          <t>Colin Paterson</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1795.386666666667</v>
+        <v>983.5599999999999</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>975.7866666666666</v>
+        <v>228.8</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>644.6000000000001</v>
+        <v>579.76</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; ELLA (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>LPTC (20cr): Standard (2.5x): 10.0h/teacher @ 2.5x = 25.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 120.0h; Grant KTP with Advai (Industry): 3% of 1642h = 49.3h; Grant KTP with Advai: 5% of 1642h = 82.1h; Grant A STAR TO STEER BY: 5% of 1642h = 82.1h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1376,84 +1376,84 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Kostas Barmpis</t>
+          <t>Da Li</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1793.433333333333</v>
+        <v>750</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1069.833333333333</v>
+        <v>410.8</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>548.6</v>
+        <v>164.2</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS3 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>PGR Training Officer: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Siamak Shahandashti</t>
+          <t>Dawn H Wood</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1277.34</v>
+        <v>1250.05</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>459.84</v>
+        <v>910.85</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>478.3</v>
+        <v>164.2</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h; Grant Participatory Harm Auditing Workbenches &amp; Methodologies: 5% of 1642h = 82.1h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1463,44 +1463,44 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Mike Freeman</t>
+          <t>Detlef Plump</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1278.443333333334</v>
+        <v>1097.26</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>857.1433333333334</v>
+        <v>333.66</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>164.2</v>
+        <v>260.2</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>257.1</v>
+        <v>503.4</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>EC Officer (on-campus): 15% of 1642h = 246.3h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1517,79 +1517,79 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Simon Foster</t>
+          <t>Dimitar Kazakov</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>896.2966666666666</v>
+        <v>1424.5</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>445.0966666666667</v>
+        <v>629.3</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>276.2</v>
+        <v>620.2</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
+          <t>PhD supervision: 5x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Ethics Committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Da Li</t>
+          <t>Dimitris Kolovos</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>750</v>
+        <v>1703.82</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>410.8</v>
+        <v>413.92</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>164.2</v>
+        <v>1114.9</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 376.0h; Grant Socially-Acceptable and Trustworthy Human-Robot Teaming for Agile Industries (SYMPHONY Resubmission): 5% of 1642h = 82.1h; Grant MOSAICO: 5% of 1642h = 82.1h; Grant SCHEME: 20% of 1642h = 328.4h; Grant Cavecore: Doctoral Network on Continuous, Automated Validation, and Evaluation of Cognitive Robots in Open-Ended Environments: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1611,84 +1611,84 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Frank Soboczenski</t>
+          <t>Fang Yan</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2515.32</v>
+        <v>800.6800000000001</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>463.8</v>
+        <v>461.48</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1794.42</v>
+        <v>164.2</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>LLMA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
+          <t>SOF2 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; THE3 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 11% of 1642h = 180.6h; Grant Alan Turing AI Fellowship: 80% of 1642h = 1313.6h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Paul Cairns</t>
+          <t>Felix Ulrich-Oltean</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>2257.945</v>
+        <v>810.63</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>906.145</v>
+        <v>423.43</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1012.6</v>
+        <v>212.2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h; Grant BiB Centre for Social Change: 0% of 1642h = 0.0h; Grant IGGI: 20% of 1642h = 328.4h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; REF Lead: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1698,44 +1698,44 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Dimitris Kolovos</t>
+          <t>Frank Soboczenski</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1703.82</v>
+        <v>2515.32</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>413.92</v>
+        <v>463.8</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1114.9</v>
+        <v>1794.42</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher</t>
+          <t>LLMA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 376.0h; Grant Socially-Acceptable and Trustworthy Human-Robot Teaming for Agile Industries (SYMPHONY Resubmission): 5% of 1642h = 82.1h; Grant MOSAICO: 5% of 1642h = 82.1h; Grant SCHEME: 20% of 1642h = 328.4h; Grant Cavecore: Doctoral Network on Continuous, Automated Validation, and Evaluation of Cognitive Robots in Open-Ended Environments: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 11% of 1642h = 180.6h; Grant Alan Turing AI Fellowship: 80% of 1642h = 1313.6h</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1745,44 +1745,44 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Kofi Appiah</t>
+          <t>Iain Bate</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1639.35</v>
+        <v>2435.6</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>861.85</v>
+        <v>30</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>356.2</v>
+        <v>588.6</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>421.3</v>
+        <v>1817</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>Minimum administrative teaching load (from workload_parameters.yaml): 30h</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h; Grant SCHEME: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Deputy Director of Admissions (UG Admissions): 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Head of Department: 100% of 1642h = 1642.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -1799,37 +1799,37 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Felix Ulrich-Oltean</t>
+          <t>Ian Gray</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>810.63</v>
+        <v>1769.61</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>423.43</v>
+        <v>425.41</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>212.2</v>
+        <v>348.2</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>175</v>
+        <v>996</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher</t>
+          <t>EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Head of Department (On-campus teaching): 50% of 1642h = 821.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1839,44 +1839,44 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Adrian Bors</t>
+          <t>Jacob Rigby</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1346.6</v>
+        <v>1302.28</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>677.3</v>
+        <v>716.78</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>412.2</v>
+        <v>246.3</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
+          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Projects (40cr): Standard (2.5x): 40.0h/teacher @ 2.5x = 100.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 39.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x assessor (8h each) = 248.0h</t>
+          <t>Grant EPSRC: Addressing environmental injustices through transdisciplinary science and technology: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Internationalisation and Visitors Coordinator: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Taught Project Coordinator: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1893,79 +1893,79 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Radu Calinescu</t>
+          <t>James Stovold</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1280.13</v>
+        <v>1600.34</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>186.43</v>
+        <v>1179.04</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>918.7</v>
+        <v>164.2</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Practicals: 4 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 14.0h/teacher; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>DEEP (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; LLMA (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h; Grant ARISE: Accelerating ReIntroduction of EcoSystem-Engineering Ant Colonies with Embodied AI: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h; Grant MammoBot: Robotic Posture Assistance for Universal Breast Screening Access: 10% of 1642h = 164.2h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Yan Jia</t>
+          <t>James Walker</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1282.37</v>
+        <v>1808.84</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>468.67</v>
+        <v>633.04</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>638.7</v>
+        <v>1000.8</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Pastoral: 9 students x 3h = 27.0h; Also teaches: Foundations of Safe AI (Safe AI 1), Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
+          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10% of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h; Grant Smart Data Donation Service (SDDS): 10% of 1642h = 164.2h; Grant IGGI: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -1987,42 +1987,42 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Detlef Plump</t>
+          <t>Jen Beeston</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1097.26</v>
+        <v>1537</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>333.66</v>
+        <v>1029.8</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>260.2</v>
+        <v>332.2</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 168.0h</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>EC Officer (on-campus): 15% of 1642h = 246.3h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Chair of the Department Education Committee: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -2034,42 +2034,42 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Ian Gray</t>
+          <t>Jo Iacovides</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1769.61</v>
+        <v>1697.755</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>425.41</v>
+        <v>1010.355</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>348.2</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>996</v>
+        <v>339.2</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher</t>
+          <t>PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 184.0h</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Deputy Head of Department (On-campus teaching): 50% of 1642h = 821.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -2081,42 +2081,42 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Peter Nightingale</t>
+          <t>Joe Cutting</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2230.43</v>
+        <v>1424.235</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1591.03</v>
+        <v>1021.035</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>300.2</v>
+        <v>228.2</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; ARIA (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>UG PL: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>ECR rep: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -2128,42 +2128,42 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Miyazawa</t>
+          <t>Katrina Attwood</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1202.95</v>
+        <v>1809.16</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>595.55</v>
+        <v>1093.56</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>268.2</v>
+        <v>212.2</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>339.2</v>
+        <v>503.4</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Director of Students: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -2175,42 +2175,42 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>James Stovold</t>
+          <t>Kofi Appiah</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1600.34</v>
+        <v>1639.35</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1179.04</v>
+        <v>861.85</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>164.2</v>
+        <v>356.2</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>257.1</v>
+        <v>421.3</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>DEEP (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; LLMA (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Director of Admissions (UG Admissions): 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -2222,84 +2222,84 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Claudio Guarnera</t>
+          <t>Kostas Barmpis</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>987.24</v>
+        <v>1793.433333333333</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>536.04</v>
+        <v>1069.833333333333</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>276.2</v>
+        <v>548.6</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>PGR Training Officer: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>James Walker</t>
+          <t>Mike Freeman</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1808.84</v>
+        <v>1278.443333333334</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>633.04</v>
+        <v>857.1433333333334</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1000.8</v>
+        <v>164.2</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h; Grant Smart Data Donation Service (SDDS): 10% of 1642h = 164.2h; Grant IGGI: 20% of 1642h = 328.4h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -2309,44 +2309,44 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Roberto Metere</t>
+          <t>Mike O'Dea</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1522.941666666667</v>
+        <v>1263.375</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1079.741666666667</v>
+        <v>842.075</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>268.2</v>
+        <v>164.2</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -2363,42 +2363,42 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Jen Beeston</t>
+          <t>Nick Pears</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1537</v>
+        <v>1632.513333333333</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>1029.8</v>
+        <v>372.5133333333333</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>332.2</v>
+        <v>428.2</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>175</v>
+        <v>831.8000000000001</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 168.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 264.0h</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Chair of the Department Education Committee: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Head (Research): 40% of 1642h = 656.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -2410,37 +2410,37 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Mike O'Dea</t>
+          <t>Paul Cairns</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1263.375</v>
+        <v>2257.945</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>842.075</v>
+        <v>906.145</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>164.2</v>
+        <v>1012.6</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher</t>
+          <t>GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher; HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h; Grant BiB Centre for Social Change: 0% of 1642h = 0.0h; Grant IGGI: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; REF Lead: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -2457,42 +2457,42 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Joe Cutting</t>
+          <t>Pedro Ribeiro</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1424.235</v>
+        <v>1986.063333333333</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>1021.035</v>
+        <v>1002.263333333333</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>228.2</v>
+        <v>644.6</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>ECR rep: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2504,37 +2504,37 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Christopher Crispin-Bailey</t>
+          <t>Pengcheng Liu</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1159.203333333333</v>
+        <v>1400.88</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>532.6533333333334</v>
+        <v>229.3</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>164.2</v>
+        <v>996.5800000000002</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>462.35</v>
+        <v>175</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Intelligent Dependable Environment Control for Sustainable Aquaculture: 20% of 1642h = 328.4h; Grant Establishing a Safe AI Research Hub: York–UTM–UTB Twin-Lab Initiative: 9% of 1642h = 147.8h; Grant Establishment of Korea–UK Collaboration Platform for Convergent Research in Quantum Photonics and Artificial Intelligence - Yr2: 5% of 1642h = 82.1h; Grant SCHEME: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>GTA Coordinator: 10% of 1642h = 164.2h; Union: 8% of 1642h = 123.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Graduate School Board (GSB) Chair: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -2551,42 +2551,42 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Jacob Rigby</t>
+          <t>Peter Nightingale</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1302.28</v>
+        <v>2230.43</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>716.78</v>
+        <v>1591.03</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>246.3</v>
+        <v>300.2</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>339.2</v>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Projects (40cr): Standard (2.5x): 40.0h/teacher @ 2.5x = 100.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 39.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>ARIA (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Grant EPSRC: Addressing environmental injustices through transdisciplinary science and technology: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Taught Project Coordinator: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>UG PL: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -2598,32 +2598,32 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Jo Iacovides</t>
+          <t>Poonam Yadav</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1697.755</v>
+        <v>2014.12</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1010.355</v>
+        <v>562.12</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>348.2</v>
+        <v>1112.8</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>339.2</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 184.0h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h; Grant CHEDDAR Funding Apr-Sep 26- PSU296: 5% of 1642h = 82.1h; Grant REMOTE: Resilient and Secure Multi-Access Interoperable Communication Fabric for TinyEdge: 20% of 1642h = 328.4h; Grant Orchestrated mobile Network for Blackpool intelligent transport: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -2645,84 +2645,84 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Colin Paterson</t>
+          <t>Pourya Shamsolmoali</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>983.5599999999999</v>
+        <v>1538.465</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>228.8</v>
+        <v>1012.115</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>579.76</v>
+        <v>228.2</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>175</v>
+        <v>298.15</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>LPTC (20cr): Standard (2.5x): 10.0h/teacher @ 2.5x = 25.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
+          <t>DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 120.0h; Grant KTP with Advai (Industry): 3% of 1642h = 49.3h; Grant KTP with Advai: 5% of 1642h = 82.1h; Grant A STAR TO STEER BY: 5% of 1642h = 82.1h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Graduate School Board (Ordinary member): 2% of 1642h = 41.1h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ribeiro</t>
+          <t>Radu Calinescu</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1986.063333333333</v>
+        <v>1280.13</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>1002.263333333333</v>
+        <v>186.43</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>644.6</v>
+        <v>918.7</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Practicals: 4 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 14.0h/teacher; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 20% of 1642h = 328.4h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h; Grant ARISE: Accelerating ReIntroduction of EcoSystem-Engineering Ant Colonies with Embodied AI: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h; Grant MammoBot: Robotic Posture Assistance for Universal Breast Screening Access: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -2732,44 +2732,44 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Steven Wright</t>
+          <t>Rob Alexander</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1167.91</v>
+        <v>789.1849999999999</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>540.71</v>
+        <v>215.885</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>452.2</v>
+        <v>398.3</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 2 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 8.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Chair of the Board of Examiners: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -2786,27 +2786,27 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Claire Ingram</t>
+          <t>Robbert Jongeling</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>649.1849999999999</v>
+        <v>1348.48</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>227.885</v>
+        <v>1009.28</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>164.2</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 2 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 8.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 1 students x 3h = 3.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
+          <t>ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; ENG1 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 2 students x 3h = 6.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -2816,59 +2816,59 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Outreach and Extra-Curricular Activities: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Dimitar Kazakov</t>
+          <t>Roberto Metere</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1424.5</v>
+        <v>1522.941666666667</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>629.3</v>
+        <v>1079.741666666667</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>620.2</v>
+        <v>268.2</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 5x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Ethics Committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
@@ -2880,37 +2880,37 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Nick Pears</t>
+          <t>Sam Braunstein</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1632.513333333333</v>
+        <v>1151.591666666667</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>372.5133333333333</v>
+        <v>812.3916666666668</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>428.2</v>
+        <v>164.2</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>831.8000000000001</v>
+        <v>175</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Practicals: 11 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 52.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 264.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Deputy Head (Research): 40% of 1642h = 656.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
@@ -2920,44 +2920,44 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Rob Alexander</t>
+          <t>Siamak Shahandashti</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>789.1849999999999</v>
+        <v>1277.34</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>215.885</v>
+        <v>459.84</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>398.3</v>
+        <v>478.3</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 2 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 8.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h; Grant Participatory Harm Auditing Workbenches &amp; Methodologies: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -2974,32 +2974,32 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Fang Yan</t>
+          <t>Simon Foster</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>800.6800000000001</v>
+        <v>896.2966666666666</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>461.48</v>
+        <v>445.0966666666667</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>164.2</v>
+        <v>276.2</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>SOF2 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; THE3 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Foundations of Safe AI (Safe AI 1), Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
+          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -3021,84 +3021,84 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Steven Xiaotian Dai</t>
+          <t>Soumya Banerjee</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1822.82</v>
+        <v>1461.04</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>969.12</v>
+        <v>1121.84</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>350.3</v>
+        <v>164.2</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>AURO (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h; Grant SCHEME: 5% of 1642h = 82.1h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>Student Disability Representative: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Carlo Ottaviani</t>
+          <t>Stefano Pirandola</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1270.281666666667</v>
+        <v>1752.515</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>662.8816666666667</v>
+        <v>810.8150000000001</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>268.2</v>
+        <v>520.4000000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>339.2</v>
+        <v>421.3</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Practicals: 11 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 52.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x assessor (8h each) = 104.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Integrated Quantum Networks (IQN) Hub: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
@@ -3115,37 +3115,37 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Stefano Pirandola</t>
+          <t>Steven Wright</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1752.515</v>
+        <v>1167.91</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>810.8150000000001</v>
+        <v>540.71</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>520.4000000000001</v>
+        <v>452.2</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>421.3</v>
+        <v>175</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Practicals: 11 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 52.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Integrated Quantum Networks (IQN) Hub: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Chair of the Board of Examiners: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
@@ -3162,42 +3162,42 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Tommy Yuan</t>
+          <t>Steven Xiaotian Dai</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>2406.913333333333</v>
+        <v>1822.82</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>1703.513333333333</v>
+        <v>969.12</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>364.2</v>
+        <v>350.3</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>339.2</v>
+        <v>503.4</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; ARIA (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher; HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 200.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h; Grant SCHEME: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>Deputy CBoEs: 10% of 1642h = 164.2h; StAMP committee members: 0% of 1642h = 0.0h; CSCSE SQA Partnership Leader: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Student Disability Representative: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -3209,42 +3209,42 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>William Smith</t>
+          <t>Tommy Yuan</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1992.76</v>
+        <v>2406.913333333333</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>1018.41</v>
+        <v>1703.513333333333</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>676.2</v>
+        <v>364.2</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>298.15</v>
+        <v>339.2</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; DEEP (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>ARIA (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 200.0h</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>CSCSE SQA Partnership Leader: 0% of 1642h = 0.0h; Deputy CBoEs: 10% of 1642h = 164.2h; StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -3256,37 +3256,37 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Sam Braunstein</t>
+          <t>Vasileios Vasilakis</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1151.591666666667</v>
+        <v>1028.195</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>812.3916666666668</v>
+        <v>332.795</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>164.2</v>
+        <v>356.2</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Practicals: 11 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 52.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 5 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 17.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
@@ -3296,49 +3296,49 @@
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Vasileios Vasilakis</t>
+          <t>William Smith</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>1028.195</v>
+        <v>1992.76</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>332.795</v>
+        <v>1018.41</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>356.2</v>
+        <v>676.2</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>339.2</v>
+        <v>298.15</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 5 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 17.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DEEP (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
@@ -3350,79 +3350,79 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Soumya Banerjee</t>
+          <t>Xinwei Fang</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1461.04</v>
+        <v>1258.805</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>1121.84</v>
+        <v>757.505</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>164.2</v>
+        <v>244.2</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Practicals: 4 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 14.0h/teacher; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Robbert Jongeling</t>
+          <t>Yan Jia</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1348.48</v>
+        <v>1282.37</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>1009.28</v>
+        <v>468.67</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>164.2</v>
+        <v>638.7</v>
       </c>
       <c r="F55" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 2 students x 3h = 6.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10% of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
@@ -3444,37 +3444,37 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Iain Bate</t>
+          <t>Yuchen Zhao</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>2435.6</v>
+        <v>1203.65</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>30</v>
+        <v>766.35</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>588.6</v>
+        <v>180.2</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1817</v>
+        <v>257.1</v>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>Minimum administrative teaching load (from workload_parameters.yaml): 30h</t>
+          <t>EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 5 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 17.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h; Grant SCHEME: 20% of 1642h = 328.4h</t>
+          <t>PhD supervision: 2x assessor (8h each) = 16.0h</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>Head of Department: 100% of 1642h = 1642.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
@@ -3553,17 +3553,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Katrina Attwood</t>
+          <t>Adrian Bors</t>
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>1093.56</v>
+        <v>677.3</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>212.2</v>
+        <v>412.2</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>503.4</v>
+        <v>257.1</v>
       </c>
       <c r="E2" s="7">
         <f>SUM(B2:D2)</f>
@@ -3573,17 +3573,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Xinwei Fang</t>
+          <t>Alena Denisova</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>757.505</v>
+        <v>1058.415</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>244.2</v>
+        <v>444.2</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>257.1</v>
+        <v>503.4</v>
       </c>
       <c r="E3" s="7">
         <f>SUM(B3:D3)</f>
@@ -3593,17 +3593,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Andrew Pomfret</t>
+          <t>Alvaro Miyazawa</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>836.1433333333334</v>
+        <v>595.55</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>164.2</v>
+        <v>268.2</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="E4" s="7">
         <f>SUM(B4:D4)</f>
@@ -3613,17 +3613,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alena Denisova</t>
+          <t>Andrew Pomfret</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1058.415</v>
+        <v>836.1433333333334</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>444.2</v>
+        <v>164.2</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>503.4</v>
+        <v>257.1</v>
       </c>
       <c r="E5" s="7">
         <f>SUM(B5:D5)</f>
@@ -3633,17 +3633,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pourya Shamsolmoali</t>
+          <t>Antonio Garcia-Dominguez</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1012.115</v>
+        <v>975.7866666666666</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>228.2</v>
+        <v>644.6000000000001</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>298.15</v>
+        <v>175</v>
       </c>
       <c r="E6" s="7">
         <f>SUM(B6:D6)</f>
@@ -3653,17 +3653,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dawn H Wood</t>
+          <t>Carlo Ottaviani</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>910.85</v>
+        <v>662.8816666666667</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>164.2</v>
+        <v>268.2</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E7" s="7">
         <f>SUM(B7:D7)</f>
@@ -3673,17 +3673,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Poonam Yadav</t>
+          <t>Christopher Crispin-Bailey</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>562.12</v>
+        <v>532.6533333333334</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>1112.8</v>
+        <v>164.2</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>339.2</v>
+        <v>462.35</v>
       </c>
       <c r="E8" s="7">
         <f>SUM(B8:D8)</f>
@@ -3693,14 +3693,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Yuchen Zhao</t>
+          <t>Claire Ingram</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>766.35</v>
+        <v>227.885</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>180.2</v>
+        <v>164.2</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>257.1</v>
@@ -3713,14 +3713,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pengcheng Liu</t>
+          <t>Claudio Guarnera</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>229.3</v>
+        <v>536.04</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>996.5800000000002</v>
+        <v>276.2</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>175</v>
@@ -3733,14 +3733,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Antonio Garcia-Dominguez</t>
+          <t>Colin Paterson</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>975.7866666666666</v>
+        <v>228.8</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>644.6000000000001</v>
+        <v>579.76</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>175</v>
@@ -3753,14 +3753,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kostas Barmpis</t>
+          <t>Da Li</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>1069.833333333333</v>
+        <v>410.8</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>548.6</v>
+        <v>164.2</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>175</v>
@@ -3773,17 +3773,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Siamak Shahandashti</t>
+          <t>Dawn H Wood</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>459.84</v>
+        <v>910.85</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>478.3</v>
+        <v>164.2</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E13" s="7">
         <f>SUM(B13:D13)</f>
@@ -3793,17 +3793,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mike Freeman</t>
+          <t>Detlef Plump</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>857.1433333333334</v>
+        <v>333.66</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>164.2</v>
+        <v>260.2</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>257.1</v>
+        <v>503.4</v>
       </c>
       <c r="E14" s="7">
         <f>SUM(B14:D14)</f>
@@ -3813,14 +3813,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Simon Foster</t>
+          <t>Dimitar Kazakov</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>445.0966666666667</v>
+        <v>629.3</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>276.2</v>
+        <v>620.2</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>175</v>
@@ -3833,14 +3833,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Da Li</t>
+          <t>Dimitris Kolovos</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>410.8</v>
+        <v>413.92</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>164.2</v>
+        <v>1114.9</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>175</v>
@@ -3853,17 +3853,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Frank Soboczenski</t>
+          <t>Fang Yan</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>463.8</v>
+        <v>461.48</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>1794.42</v>
+        <v>164.2</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="E17" s="7">
         <f>SUM(B17:D17)</f>
@@ -3873,17 +3873,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Paul Cairns</t>
+          <t>Felix Ulrich-Oltean</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>906.145</v>
+        <v>423.43</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>1012.6</v>
+        <v>212.2</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E18" s="7">
         <f>SUM(B18:D18)</f>
@@ -3893,17 +3893,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dimitris Kolovos</t>
+          <t>Frank Soboczenski</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>413.92</v>
+        <v>463.8</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>1114.9</v>
+        <v>1794.42</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E19" s="7">
         <f>SUM(B19:D19)</f>
@@ -3913,17 +3913,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kofi Appiah</t>
+          <t>Iain Bate</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>861.85</v>
+        <v>30</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>356.2</v>
+        <v>588.6</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>421.3</v>
+        <v>1817</v>
       </c>
       <c r="E20" s="7">
         <f>SUM(B20:D20)</f>
@@ -3933,17 +3933,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Felix Ulrich-Oltean</t>
+          <t>Ian Gray</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>423.43</v>
+        <v>425.41</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>212.2</v>
+        <v>348.2</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>175</v>
+        <v>996</v>
       </c>
       <c r="E21" s="7">
         <f>SUM(B21:D21)</f>
@@ -3953,17 +3953,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Adrian Bors</t>
+          <t>Jacob Rigby</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>677.3</v>
+        <v>716.78</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>412.2</v>
+        <v>246.3</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="E22" s="7">
         <f>SUM(B22:D22)</f>
@@ -3973,17 +3973,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Radu Calinescu</t>
+          <t>James Stovold</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>186.43</v>
+        <v>1179.04</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>918.7</v>
+        <v>164.2</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E23" s="7">
         <f>SUM(B23:D23)</f>
@@ -3993,14 +3993,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Yan Jia</t>
+          <t>James Walker</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>468.67</v>
+        <v>633.04</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>638.7</v>
+        <v>1000.8</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>175</v>
@@ -4013,17 +4013,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Detlef Plump</t>
+          <t>Jen Beeston</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>333.66</v>
+        <v>1029.8</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>260.2</v>
+        <v>332.2</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="E25" s="7">
         <f>SUM(B25:D25)</f>
@@ -4033,17 +4033,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ian Gray</t>
+          <t>Jo Iacovides</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>425.41</v>
+        <v>1010.355</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>348.2</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>996</v>
+        <v>339.2</v>
       </c>
       <c r="E26" s="7">
         <f>SUM(B26:D26)</f>
@@ -4053,17 +4053,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Peter Nightingale</t>
+          <t>Joe Cutting</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>1591.03</v>
+        <v>1021.035</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>300.2</v>
+        <v>228.2</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(B27:D27)</f>
@@ -4073,17 +4073,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alvaro Miyazawa</t>
+          <t>Katrina Attwood</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>595.55</v>
+        <v>1093.56</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>268.2</v>
+        <v>212.2</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>339.2</v>
+        <v>503.4</v>
       </c>
       <c r="E28" s="7">
         <f>SUM(B28:D28)</f>
@@ -4093,17 +4093,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>James Stovold</t>
+          <t>Kofi Appiah</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>1179.04</v>
+        <v>861.85</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>164.2</v>
+        <v>356.2</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>257.1</v>
+        <v>421.3</v>
       </c>
       <c r="E29" s="7">
         <f>SUM(B29:D29)</f>
@@ -4113,14 +4113,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Claudio Guarnera</t>
+          <t>Kostas Barmpis</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>536.04</v>
+        <v>1069.833333333333</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>276.2</v>
+        <v>548.6</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>175</v>
@@ -4133,17 +4133,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>James Walker</t>
+          <t>Mike Freeman</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>633.04</v>
+        <v>857.1433333333334</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>1000.8</v>
+        <v>164.2</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E31" s="7">
         <f>SUM(B31:D31)</f>
@@ -4153,17 +4153,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Roberto Metere</t>
+          <t>Mike O'Dea</t>
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>1079.741666666667</v>
+        <v>842.075</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>268.2</v>
+        <v>164.2</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E32" s="7">
         <f>SUM(B32:D32)</f>
@@ -4173,17 +4173,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jen Beeston</t>
+          <t>Nick Pears</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>1029.8</v>
+        <v>372.5133333333333</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>332.2</v>
+        <v>428.2</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>175</v>
+        <v>831.8000000000001</v>
       </c>
       <c r="E33" s="7">
         <f>SUM(B33:D33)</f>
@@ -4193,17 +4193,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mike O'Dea</t>
+          <t>Paul Cairns</t>
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>842.075</v>
+        <v>906.145</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>164.2</v>
+        <v>1012.6</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="E34" s="7">
         <f>SUM(B34:D34)</f>
@@ -4213,17 +4213,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Joe Cutting</t>
+          <t>Pedro Ribeiro</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>1021.035</v>
+        <v>1002.263333333333</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>228.2</v>
+        <v>644.6</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E35" s="7">
         <f>SUM(B35:D35)</f>
@@ -4233,17 +4233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Christopher Crispin-Bailey</t>
+          <t>Pengcheng Liu</t>
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>532.6533333333334</v>
+        <v>229.3</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>164.2</v>
+        <v>996.5800000000002</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>462.35</v>
+        <v>175</v>
       </c>
       <c r="E36" s="7">
         <f>SUM(B36:D36)</f>
@@ -4253,14 +4253,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jacob Rigby</t>
+          <t>Peter Nightingale</t>
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>716.78</v>
+        <v>1591.03</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>246.3</v>
+        <v>300.2</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>339.2</v>
@@ -4273,14 +4273,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jo Iacovides</t>
+          <t>Poonam Yadav</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>1010.355</v>
+        <v>562.12</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>348.2</v>
+        <v>1112.8</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>339.2</v>
@@ -4293,17 +4293,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Colin Paterson</t>
+          <t>Pourya Shamsolmoali</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>228.8</v>
+        <v>1012.115</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>579.76</v>
+        <v>228.2</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>175</v>
+        <v>298.15</v>
       </c>
       <c r="E39" s="7">
         <f>SUM(B39:D39)</f>
@@ -4313,17 +4313,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pedro Ribeiro</t>
+          <t>Radu Calinescu</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>1002.263333333333</v>
+        <v>186.43</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>644.6</v>
+        <v>918.7</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E40" s="7">
         <f>SUM(B40:D40)</f>
@@ -4333,14 +4333,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Steven Wright</t>
+          <t>Rob Alexander</t>
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>540.71</v>
+        <v>215.885</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>452.2</v>
+        <v>398.3</v>
       </c>
       <c r="D41" s="7" t="n">
         <v>175</v>
@@ -4353,17 +4353,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Claire Ingram</t>
+          <t>Robbert Jongeling</t>
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>227.885</v>
+        <v>1009.28</v>
       </c>
       <c r="C42" s="7" t="n">
         <v>164.2</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="E42" s="7">
         <f>SUM(B42:D42)</f>
@@ -4373,14 +4373,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Dimitar Kazakov</t>
+          <t>Roberto Metere</t>
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>629.3</v>
+        <v>1079.741666666667</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>620.2</v>
+        <v>268.2</v>
       </c>
       <c r="D43" s="7" t="n">
         <v>175</v>
@@ -4393,17 +4393,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nick Pears</t>
+          <t>Sam Braunstein</t>
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>372.5133333333333</v>
+        <v>812.3916666666668</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>428.2</v>
+        <v>164.2</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>831.8000000000001</v>
+        <v>175</v>
       </c>
       <c r="E44" s="7">
         <f>SUM(B44:D44)</f>
@@ -4413,17 +4413,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Rob Alexander</t>
+          <t>Siamak Shahandashti</t>
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>215.885</v>
+        <v>459.84</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>398.3</v>
+        <v>478.3</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E45" s="7">
         <f>SUM(B45:D45)</f>
@@ -4433,14 +4433,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Fang Yan</t>
+          <t>Simon Foster</t>
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>461.48</v>
+        <v>445.0966666666667</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>164.2</v>
+        <v>276.2</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>175</v>
@@ -4453,17 +4453,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Steven Xiaotian Dai</t>
+          <t>Soumya Banerjee</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>969.12</v>
+        <v>1121.84</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>350.3</v>
+        <v>164.2</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="E47" s="7">
         <f>SUM(B47:D47)</f>
@@ -4473,17 +4473,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Carlo Ottaviani</t>
+          <t>Stefano Pirandola</t>
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>662.8816666666667</v>
+        <v>810.8150000000001</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>268.2</v>
+        <v>520.4000000000001</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>339.2</v>
+        <v>421.3</v>
       </c>
       <c r="E48" s="7">
         <f>SUM(B48:D48)</f>
@@ -4493,17 +4493,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Stefano Pirandola</t>
+          <t>Steven Wright</t>
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>810.8150000000001</v>
+        <v>540.71</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>520.4000000000001</v>
+        <v>452.2</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>421.3</v>
+        <v>175</v>
       </c>
       <c r="E49" s="7">
         <f>SUM(B49:D49)</f>
@@ -4513,17 +4513,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tommy Yuan</t>
+          <t>Steven Xiaotian Dai</t>
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>1703.513333333333</v>
+        <v>969.12</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>364.2</v>
+        <v>350.3</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>339.2</v>
+        <v>503.4</v>
       </c>
       <c r="E50" s="7">
         <f>SUM(B50:D50)</f>
@@ -4533,17 +4533,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>William Smith</t>
+          <t>Tommy Yuan</t>
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>1018.41</v>
+        <v>1703.513333333333</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>676.2</v>
+        <v>364.2</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>298.15</v>
+        <v>339.2</v>
       </c>
       <c r="E51" s="7">
         <f>SUM(B51:D51)</f>
@@ -4553,17 +4553,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sam Braunstein</t>
+          <t>Vasileios Vasilakis</t>
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>812.3916666666668</v>
+        <v>332.795</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>164.2</v>
+        <v>356.2</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E52" s="7">
         <f>SUM(B52:D52)</f>
@@ -4573,17 +4573,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vasileios Vasilakis</t>
+          <t>William Smith</t>
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>332.795</v>
+        <v>1018.41</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>356.2</v>
+        <v>676.2</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>339.2</v>
+        <v>298.15</v>
       </c>
       <c r="E53" s="7">
         <f>SUM(B53:D53)</f>
@@ -4593,17 +4593,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Soumya Banerjee</t>
+          <t>Xinwei Fang</t>
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>1121.84</v>
+        <v>757.505</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>164.2</v>
+        <v>244.2</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E54" s="7">
         <f>SUM(B54:D54)</f>
@@ -4613,14 +4613,14 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Robbert Jongeling</t>
+          <t>Yan Jia</t>
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>1009.28</v>
+        <v>468.67</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>164.2</v>
+        <v>638.7</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>175</v>
@@ -4633,17 +4633,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Iain Bate</t>
+          <t>Yuchen Zhao</t>
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>30</v>
+        <v>766.35</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>588.6</v>
+        <v>180.2</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>1817</v>
+        <v>257.1</v>
       </c>
       <c r="E56" s="7">
         <f>SUM(B56:D56)</f>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -1631,7 +1631,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>SOF2 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; THE3 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>SOF2 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; THE3 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Foundations of Safe AI (Safe AI 1), Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Pastoral: 9 students x 3h = 27.0h; Also teaches: Foundations of Safe AI (Safe AI 1), Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -1631,7 +1631,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>SOF2 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; THE3 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Foundations of Safe AI (Safe AI 1), Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
+          <t>SOF2 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; THE3 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Pastoral: 9 students x 3h = 27.0h; Also teaches: Foundations of Safe AI (Safe AI 1), Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
+          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -913,10 +913,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1346.6</v>
+        <v>961.6</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>677.3</v>
+        <v>292.3</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>412.2</v>
@@ -926,7 +926,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
+          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -960,10 +960,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2006.015</v>
+        <v>1236.015</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1058.415</v>
+        <v>288.415</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>444.2</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1202.95</v>
+        <v>799.6166666666667</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>595.55</v>
+        <v>192.2166666666667</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>268.2</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -1054,10 +1054,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1257.443333333334</v>
+        <v>718.4433333333334</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>836.1433333333334</v>
+        <v>297.1433333333333</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>164.2</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -1101,10 +1101,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1795.386666666667</v>
+        <v>988.7200000000001</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>975.7866666666666</v>
+        <v>169.12</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>644.6000000000001</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>ELLA (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>ELLA (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -1148,10 +1148,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1270.281666666667</v>
+        <v>877.7816666666668</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>662.8816666666667</v>
+        <v>270.3816666666667</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>268.2</v>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -1195,10 +1195,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1159.203333333333</v>
+        <v>917.2033333333334</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>532.6533333333334</v>
+        <v>290.6533333333333</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>164.2</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1242,10 +1242,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>649.1849999999999</v>
+        <v>633.1849999999999</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>227.885</v>
+        <v>211.885</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>164.2</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 2 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 8.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 1 students x 3h = 3.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
+          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 1 students x 3h = 3.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1289,10 +1289,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>987.24</v>
+        <v>602.24</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>536.04</v>
+        <v>151.04</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>276.2</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1383,10 +1383,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>750</v>
+        <v>607</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>410.8</v>
+        <v>267.8</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>164.2</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS3 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1430,10 +1430,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1250.05</v>
+        <v>663.3833333333333</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>910.85</v>
+        <v>324.1833333333333</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>164.2</v>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1477,10 +1477,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1097.26</v>
+        <v>1078.26</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>333.66</v>
+        <v>314.66</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>260.2</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1524,20 +1524,20 @@
         <v>1</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1424.5</v>
+        <v>1203.7</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>629.3</v>
+        <v>244.3</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>620.2</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Ethics Committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Ethics Committee Member: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1571,10 +1571,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1703.82</v>
+        <v>1318.82</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>413.92</v>
+        <v>28.92</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>1114.9</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher</t>
+          <t>ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1618,10 +1618,10 @@
         <v>1</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>800.6800000000001</v>
+        <v>580.0133333333333</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>461.48</v>
+        <v>240.8133333333333</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>164.2</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>SOF2 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; THE3 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>SOF2 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; THE3 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1665,10 +1665,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>810.63</v>
+        <v>425.63</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>423.43</v>
+        <v>38.43</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>212.2</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher</t>
+          <t>SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1712,10 +1712,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2515.32</v>
+        <v>2102.82</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>463.8</v>
+        <v>51.3</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>1794.42</v>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>LLMA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
+          <t>LLMA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1806,10 +1806,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1769.61</v>
+        <v>1384.61</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>425.41</v>
+        <v>40.41</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>348.2</v>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher</t>
+          <t>EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1853,10 +1853,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1302.28</v>
+        <v>917.28</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>716.78</v>
+        <v>331.78</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>246.3</v>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Projects (40cr): Standard (2.5x): 40.0h/teacher @ 2.5x = 100.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 39.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Projects (40cr): Standard (2.5x): 40.0h/teacher @ 2.5x = 100.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 39.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1900,10 +1900,10 @@
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1600.34</v>
+        <v>775.34</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1179.04</v>
+        <v>354.04</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>164.2</v>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>DEEP (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; LLMA (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DEEP (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; LLMA (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1947,10 +1947,10 @@
         <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1808.84</v>
+        <v>1423.84</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>633.04</v>
+        <v>248.04</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>1000.8</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1994,10 +1994,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1537</v>
+        <v>767</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1029.8</v>
+        <v>259.8</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>332.2</v>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2041,10 +2041,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1697.755</v>
+        <v>927.7550000000001</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1010.355</v>
+        <v>240.355</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>348.2</v>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2088,10 +2088,10 @@
         <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1424.235</v>
+        <v>654.235</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1021.035</v>
+        <v>251.035</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>228.2</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2135,10 +2135,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1809.16</v>
+        <v>1039.16</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1093.56</v>
+        <v>323.56</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>212.2</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2182,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1639.35</v>
+        <v>1052.683333333333</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>861.85</v>
+        <v>275.1833333333333</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>356.2</v>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 18.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2229,10 +2229,10 @@
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1793.433333333333</v>
+        <v>1005.1</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1069.833333333333</v>
+        <v>281.5</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>548.6</v>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2276,10 +2276,10 @@
         <v>1</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1278.443333333334</v>
+        <v>739.4433333333334</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>857.1433333333334</v>
+        <v>318.1433333333333</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>164.2</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; &lt;strong&gt;Practicals:&lt;/strong&gt; 5 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 2 group(s) without first-session slots (0.7 group(s)/lecturer @ 1.5x);     Total: 14.0h/week = 154.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2323,10 +2323,10 @@
         <v>1</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1263.375</v>
+        <v>493.375</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>842.075</v>
+        <v>72.075</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>164.2</v>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher</t>
+          <t>CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2370,10 +2370,10 @@
         <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1632.513333333333</v>
+        <v>1440.013333333333</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>372.5133333333333</v>
+        <v>180.0133333333333</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>428.2</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2417,10 +2417,10 @@
         <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2257.945</v>
+        <v>1487.945</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>906.145</v>
+        <v>136.145</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1012.6</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher; HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher; HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2464,10 +2464,10 @@
         <v>1</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1986.063333333333</v>
+        <v>1197.73</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>1002.263333333333</v>
+        <v>213.93</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>644.6</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2511,10 +2511,10 @@
         <v>1</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1400.88</v>
+        <v>1312.88</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>229.3</v>
+        <v>141.3</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>996.5800000000002</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; &lt;strong&gt;Practicals:&lt;/strong&gt; 6 group(s) over 11 weeks; - First time delivery: 3 group(s) (one per lecturer). 2.0h x 2.5 multiplier per week.; Repeated sessions: 3 group(s) without first-session slots (1.0 group(s)/lecturer @ 1.5x);     Total: 13.0h/week = 143.0h total; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2558,10 +2558,10 @@
         <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2230.43</v>
+        <v>965.4300000000001</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1591.03</v>
+        <v>326.03</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>300.2</v>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>ARIA (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>ARIA (20cr): Existing lecturer + new content (5x): 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2605,10 +2605,10 @@
         <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>2014.12</v>
+        <v>1629.12</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>562.12</v>
+        <v>177.12</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>1112.8</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2652,10 +2652,10 @@
         <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1538.465</v>
+        <v>768.4649999999999</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1012.115</v>
+        <v>242.115</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>228.2</v>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2699,10 +2699,10 @@
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1280.13</v>
+        <v>1224.13</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>186.43</v>
+        <v>130.43</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>918.7</v>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Practicals: 4 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 14.0h/teacher; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2746,10 +2746,10 @@
         <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>789.1849999999999</v>
+        <v>773.1849999999999</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>215.885</v>
+        <v>199.885</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>398.3</v>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 2 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 8.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -2793,10 +2793,10 @@
         <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1348.48</v>
+        <v>523.48</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>1009.28</v>
+        <v>184.28</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>164.2</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; ENG1 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 2 students x 3h = 6.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; ENG1 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 2 students x 3h = 6.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -2840,10 +2840,10 @@
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1522.941666666667</v>
+        <v>745.4416666666666</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>1079.741666666667</v>
+        <v>302.2416666666667</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>268.2</v>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -2887,10 +2887,10 @@
         <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1151.591666666667</v>
+        <v>574.0916666666667</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>812.3916666666668</v>
+        <v>234.8916666666667</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>164.2</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Practicals: 11 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 52.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -2934,10 +2934,10 @@
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1277.34</v>
+        <v>1077.34</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>459.84</v>
+        <v>259.84</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>478.3</v>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Practicals: 1 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 7.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -2981,10 +2981,10 @@
         <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>896.2966666666666</v>
+        <v>684.7966666666666</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>445.0966666666667</v>
+        <v>233.5966666666667</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>276.2</v>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 11 weeks; Standard lecturers: 2.5h/week @ 2.5x; Repeats: 1.5h/week @ 1.5x; Total: 17.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Practicals: 3 weeks; New/new-content lecturers: 5.0h/week @ 5x; Repeats: 1.5h/week @ 1.5x; Standard lecturers: 2.5h/week @ 2.5x; Total: 6.3h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3028,10 +3028,10 @@
         <v>1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1461.04</v>
+        <v>636.04</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>1121.84</v>
+        <v>296.84</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>164.2</v>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 38.3h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>AURO (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3075,10 +3075,10 @@
         <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1752.515</v>
+        <v>1175.015</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>810.8150000000001</v>
+        <v>233.315</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>520.4000000000001</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Practicals: 11 weeks; Standard lecturers: 7.5h/week @ 2.5x; Repeats: 4.5h/week @ 1.5x; Total: 52.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3122,10 +3122,10 @@
         <v>1</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1167.91</v>
+        <v>782.91</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>540.71</v>
+        <v>155.71</v>
       </c>
       <c r="E49" s="3" t="n">
         <v>452.2</v>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3169,10 +3169,10 @@
         <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1822.82</v>
+        <v>1052.82</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>969.12</v>
+        <v>199.12</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>350.3</v>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher; HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher; HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -3216,10 +3216,10 @@
         <v>1</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2406.913333333333</v>
+        <v>1123.58</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>1703.513333333333</v>
+        <v>420.18</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>364.2</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>ARIA (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 36.7h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 40.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>ARIA (20cr): Existing lecturer + new content (5x): 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -3263,10 +3263,10 @@
         <v>1</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1028.195</v>
+        <v>943.1950000000001</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>332.795</v>
+        <v>247.795</v>
       </c>
       <c r="E52" s="3" t="n">
         <v>356.2</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 5 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 17.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -3310,10 +3310,10 @@
         <v>1</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>1992.76</v>
+        <v>1195.26</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>1018.41</v>
+        <v>220.91</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>676.2</v>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>DEEP (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; New/new-content lecturers: 10.0h/week @ 5x; Repeats: 3.0h/week @ 1.5x; Standard lecturers: 5.0h/week @ 2.5x; Total: 37.5h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>DEEP (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -3357,10 +3357,10 @@
         <v>1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1258.805</v>
+        <v>817.8049999999999</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>757.505</v>
+        <v>316.505</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>244.2</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Practicals: 4 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 14.0h/teacher; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -3404,10 +3404,10 @@
         <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1282.37</v>
+        <v>897.37</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>468.67</v>
+        <v>83.67</v>
       </c>
       <c r="E55" s="3" t="n">
         <v>638.7</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -3451,10 +3451,10 @@
         <v>1</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>1203.65</v>
+        <v>733.6500000000001</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>766.35</v>
+        <v>296.35</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>180.2</v>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 11 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 35.0h/teacher; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Practicals: 5 weeks; Standard lecturers: 5.0h/week @ 2.5x; Repeats: 3.0h/week @ 1.5x; Total: 17.0h/teacher; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>677.3</v>
+        <v>292.3</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>412.2</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>1058.415</v>
+        <v>288.415</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>444.2</v>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>595.55</v>
+        <v>192.2166666666667</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>268.2</v>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>836.1433333333334</v>
+        <v>297.1433333333333</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>164.2</v>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>975.7866666666666</v>
+        <v>169.12</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>644.6000000000001</v>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>662.8816666666667</v>
+        <v>270.3816666666667</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>268.2</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>532.6533333333334</v>
+        <v>290.6533333333333</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>164.2</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>227.885</v>
+        <v>211.885</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>164.2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>536.04</v>
+        <v>151.04</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>276.2</v>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>410.8</v>
+        <v>267.8</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>164.2</v>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>910.85</v>
+        <v>324.1833333333333</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>164.2</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>333.66</v>
+        <v>314.66</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>260.2</v>
@@ -3817,13 +3817,13 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>629.3</v>
+        <v>244.3</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>620.2</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E15" s="7">
         <f>SUM(B15:D15)</f>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>413.92</v>
+        <v>28.92</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>1114.9</v>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>461.48</v>
+        <v>240.8133333333333</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>164.2</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>423.43</v>
+        <v>38.43</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>212.2</v>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>463.8</v>
+        <v>51.3</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>1794.42</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>425.41</v>
+        <v>40.41</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>348.2</v>
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>716.78</v>
+        <v>331.78</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>246.3</v>
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>1179.04</v>
+        <v>354.04</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>164.2</v>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>633.04</v>
+        <v>248.04</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>1000.8</v>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>1029.8</v>
+        <v>259.8</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>332.2</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>1010.355</v>
+        <v>240.355</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>348.2</v>
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>1021.035</v>
+        <v>251.035</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>228.2</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>1093.56</v>
+        <v>323.56</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>212.2</v>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>861.85</v>
+        <v>275.1833333333333</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>356.2</v>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>1069.833333333333</v>
+        <v>281.5</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>548.6</v>
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>857.1433333333334</v>
+        <v>318.1433333333333</v>
       </c>
       <c r="C31" s="7" t="n">
         <v>164.2</v>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>842.075</v>
+        <v>72.075</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>164.2</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>372.5133333333333</v>
+        <v>180.0133333333333</v>
       </c>
       <c r="C33" s="7" t="n">
         <v>428.2</v>
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>906.145</v>
+        <v>136.145</v>
       </c>
       <c r="C34" s="7" t="n">
         <v>1012.6</v>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>1002.263333333333</v>
+        <v>213.93</v>
       </c>
       <c r="C35" s="7" t="n">
         <v>644.6</v>
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>229.3</v>
+        <v>141.3</v>
       </c>
       <c r="C36" s="7" t="n">
         <v>996.5800000000002</v>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>1591.03</v>
+        <v>326.03</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>300.2</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>562.12</v>
+        <v>177.12</v>
       </c>
       <c r="C38" s="7" t="n">
         <v>1112.8</v>
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>1012.115</v>
+        <v>242.115</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>228.2</v>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>186.43</v>
+        <v>130.43</v>
       </c>
       <c r="C40" s="7" t="n">
         <v>918.7</v>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>215.885</v>
+        <v>199.885</v>
       </c>
       <c r="C41" s="7" t="n">
         <v>398.3</v>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>1009.28</v>
+        <v>184.28</v>
       </c>
       <c r="C42" s="7" t="n">
         <v>164.2</v>
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>1079.741666666667</v>
+        <v>302.2416666666667</v>
       </c>
       <c r="C43" s="7" t="n">
         <v>268.2</v>
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>812.3916666666668</v>
+        <v>234.8916666666667</v>
       </c>
       <c r="C44" s="7" t="n">
         <v>164.2</v>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>459.84</v>
+        <v>259.84</v>
       </c>
       <c r="C45" s="7" t="n">
         <v>478.3</v>
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>445.0966666666667</v>
+        <v>233.5966666666667</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>276.2</v>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>1121.84</v>
+        <v>296.84</v>
       </c>
       <c r="C47" s="7" t="n">
         <v>164.2</v>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>810.8150000000001</v>
+        <v>233.315</v>
       </c>
       <c r="C48" s="7" t="n">
         <v>520.4000000000001</v>
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>540.71</v>
+        <v>155.71</v>
       </c>
       <c r="C49" s="7" t="n">
         <v>452.2</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>969.12</v>
+        <v>199.12</v>
       </c>
       <c r="C50" s="7" t="n">
         <v>350.3</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>1703.513333333333</v>
+        <v>420.18</v>
       </c>
       <c r="C51" s="7" t="n">
         <v>364.2</v>
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>332.795</v>
+        <v>247.795</v>
       </c>
       <c r="C52" s="7" t="n">
         <v>356.2</v>
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>1018.41</v>
+        <v>220.91</v>
       </c>
       <c r="C53" s="7" t="n">
         <v>676.2</v>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>757.505</v>
+        <v>316.505</v>
       </c>
       <c r="C54" s="7" t="n">
         <v>244.2</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>468.67</v>
+        <v>83.67</v>
       </c>
       <c r="C55" s="7" t="n">
         <v>638.7</v>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>766.35</v>
+        <v>296.35</v>
       </c>
       <c r="C56" s="7" t="n">
         <v>180.2</v>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -913,10 +913,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>961.6</v>
+        <v>1016.6</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>292.3</v>
+        <v>347.3</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>412.2</v>
@@ -960,10 +960,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1236.015</v>
+        <v>1346.015</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>288.415</v>
+        <v>398.415</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>444.2</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>799.6166666666667</v>
+        <v>854.6166666666667</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>192.2166666666667</v>
+        <v>247.2166666666667</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>268.2</v>
@@ -1054,10 +1054,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>718.4433333333334</v>
+        <v>949.4433333333333</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>297.1433333333333</v>
+        <v>528.1433333333333</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>164.2</v>
@@ -1101,10 +1101,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>988.7200000000001</v>
+        <v>1098.72</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>169.12</v>
+        <v>279.12</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>644.6000000000001</v>
@@ -1148,10 +1148,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>877.7816666666668</v>
+        <v>940.2816666666668</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>270.3816666666667</v>
+        <v>332.8816666666667</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>268.2</v>
@@ -1195,10 +1195,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>917.2033333333334</v>
+        <v>1159.203333333333</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>290.6533333333333</v>
+        <v>532.6533333333334</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>164.2</v>
@@ -1242,10 +1242,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>633.1849999999999</v>
+        <v>643.1849999999999</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>211.885</v>
+        <v>221.885</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>164.2</v>
@@ -1289,10 +1289,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>602.24</v>
+        <v>668.24</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>151.04</v>
+        <v>217.04</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>276.2</v>
@@ -1383,10 +1383,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>607</v>
+        <v>750</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>267.8</v>
+        <v>410.8</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>164.2</v>
@@ -1430,10 +1430,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>663.3833333333333</v>
+        <v>778.8833333333333</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>324.1833333333333</v>
+        <v>439.6833333333333</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>164.2</v>
@@ -1477,10 +1477,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1078.26</v>
+        <v>1088.76</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>314.66</v>
+        <v>325.16</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>260.2</v>
@@ -1524,10 +1524,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1203.7</v>
+        <v>1258.7</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>244.3</v>
+        <v>299.3</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>620.2</v>
@@ -1571,10 +1571,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1318.82</v>
+        <v>1373.82</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>28.92</v>
+        <v>83.92</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>1114.9</v>
@@ -1618,10 +1618,10 @@
         <v>1</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>580.0133333333333</v>
+        <v>664.0133333333333</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>240.8133333333333</v>
+        <v>324.8133333333333</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>164.2</v>
@@ -1665,10 +1665,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>425.63</v>
+        <v>480.63</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>38.43</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>212.2</v>
@@ -1712,10 +1712,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2102.82</v>
+        <v>2157.82</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>51.3</v>
+        <v>106.3</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>1794.42</v>
@@ -1806,10 +1806,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1384.61</v>
+        <v>1439.61</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>40.41</v>
+        <v>95.41</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>348.2</v>
@@ -1853,10 +1853,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>917.28</v>
+        <v>983.28</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>331.78</v>
+        <v>397.78</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>246.3</v>
@@ -1900,10 +1900,10 @@
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>775.34</v>
+        <v>1011.84</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>354.04</v>
+        <v>590.54</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>164.2</v>
@@ -1947,10 +1947,10 @@
         <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1423.84</v>
+        <v>1489.84</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>248.04</v>
+        <v>314.04</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>1000.8</v>
@@ -1994,10 +1994,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>767</v>
+        <v>877</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>259.8</v>
+        <v>369.8</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>332.2</v>
@@ -2041,10 +2041,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>927.7550000000001</v>
+        <v>1037.755</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>240.355</v>
+        <v>350.355</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>348.2</v>
@@ -2088,10 +2088,10 @@
         <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>654.235</v>
+        <v>764.235</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>251.035</v>
+        <v>361.035</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>228.2</v>
@@ -2135,10 +2135,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1039.16</v>
+        <v>1160.16</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>323.56</v>
+        <v>444.56</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>212.2</v>
@@ -2182,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1052.683333333333</v>
+        <v>1168.183333333333</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>275.1833333333333</v>
+        <v>390.6833333333333</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>356.2</v>
@@ -2229,10 +2229,10 @@
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1005.1</v>
+        <v>1126.1</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>281.5</v>
+        <v>402.5</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>548.6</v>
@@ -2276,10 +2276,10 @@
         <v>1</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>739.4433333333334</v>
+        <v>970.4433333333333</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>318.1433333333333</v>
+        <v>549.1433333333333</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>164.2</v>
@@ -2323,10 +2323,10 @@
         <v>1</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>493.375</v>
+        <v>619.875</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>72.075</v>
+        <v>198.575</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>164.2</v>
@@ -2370,10 +2370,10 @@
         <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1440.013333333333</v>
+        <v>1473.013333333333</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>180.0133333333333</v>
+        <v>213.0133333333333</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>428.2</v>
@@ -2417,10 +2417,10 @@
         <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1487.945</v>
+        <v>1608.945</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>136.145</v>
+        <v>257.145</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1012.6</v>
@@ -2464,10 +2464,10 @@
         <v>1</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1197.73</v>
+        <v>1329.73</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>213.93</v>
+        <v>345.93</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>644.6</v>
@@ -2511,10 +2511,10 @@
         <v>1</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1312.88</v>
+        <v>1400.88</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>141.3</v>
+        <v>229.3</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>996.5800000000002</v>
@@ -2558,10 +2558,10 @@
         <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>965.4300000000001</v>
+        <v>1240.43</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>326.03</v>
+        <v>601.03</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>300.2</v>
@@ -2605,10 +2605,10 @@
         <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1629.12</v>
+        <v>1706.12</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>177.12</v>
+        <v>254.12</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>1112.8</v>
@@ -2652,10 +2652,10 @@
         <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>768.4649999999999</v>
+        <v>922.465</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>242.115</v>
+        <v>396.115</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>228.2</v>
@@ -2699,10 +2699,10 @@
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1224.13</v>
+        <v>1244.13</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>130.43</v>
+        <v>150.43</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>918.7</v>
@@ -2746,10 +2746,10 @@
         <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>773.1849999999999</v>
+        <v>783.1849999999999</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>199.885</v>
+        <v>209.885</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>398.3</v>
@@ -2793,10 +2793,10 @@
         <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>523.48</v>
+        <v>754.48</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>184.28</v>
+        <v>415.28</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>164.2</v>
@@ -2840,10 +2840,10 @@
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>745.4416666666666</v>
+        <v>879.4416666666666</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>302.2416666666667</v>
+        <v>436.2416666666667</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>268.2</v>
@@ -2887,10 +2887,10 @@
         <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>574.0916666666667</v>
+        <v>656.5916666666667</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>234.8916666666667</v>
+        <v>317.3916666666667</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>164.2</v>
@@ -2934,10 +2934,10 @@
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1077.34</v>
+        <v>1117.84</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>259.84</v>
+        <v>300.34</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>478.3</v>
@@ -2981,10 +2981,10 @@
         <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>684.7966666666666</v>
+        <v>728.2966666666666</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>233.5966666666667</v>
+        <v>277.0966666666666</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>276.2</v>
@@ -3028,10 +3028,10 @@
         <v>1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>636.04</v>
+        <v>856.04</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>296.84</v>
+        <v>516.8399999999999</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>164.2</v>
@@ -3075,10 +3075,10 @@
         <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1175.015</v>
+        <v>1257.515</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>233.315</v>
+        <v>315.815</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>520.4000000000001</v>
@@ -3122,10 +3122,10 @@
         <v>1</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>782.91</v>
+        <v>854.41</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>155.71</v>
+        <v>227.21</v>
       </c>
       <c r="E49" s="3" t="n">
         <v>452.2</v>
@@ -3169,10 +3169,10 @@
         <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1052.82</v>
+        <v>1179.32</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>199.12</v>
+        <v>325.62</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>350.3</v>
@@ -3216,10 +3216,10 @@
         <v>1</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1123.58</v>
+        <v>1409.58</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>420.18</v>
+        <v>706.1800000000001</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>364.2</v>
@@ -3263,10 +3263,10 @@
         <v>1</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>943.1950000000001</v>
+        <v>968.1950000000001</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>247.795</v>
+        <v>272.795</v>
       </c>
       <c r="E52" s="3" t="n">
         <v>356.2</v>
@@ -3310,10 +3310,10 @@
         <v>1</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>1195.26</v>
+        <v>1321.76</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>220.91</v>
+        <v>347.41</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>676.2</v>
@@ -3357,10 +3357,10 @@
         <v>1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>817.8049999999999</v>
+        <v>925.8049999999999</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>316.505</v>
+        <v>424.505</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>244.2</v>
@@ -3404,10 +3404,10 @@
         <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>897.37</v>
+        <v>952.3700000000001</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>83.67</v>
+        <v>138.67</v>
       </c>
       <c r="E55" s="3" t="n">
         <v>638.7</v>
@@ -3451,10 +3451,10 @@
         <v>1</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>733.6500000000001</v>
+        <v>813.65</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>296.35</v>
+        <v>376.35</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>180.2</v>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>292.3</v>
+        <v>347.3</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>412.2</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>288.415</v>
+        <v>398.415</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>444.2</v>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>192.2166666666667</v>
+        <v>247.2166666666667</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>268.2</v>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>297.1433333333333</v>
+        <v>528.1433333333333</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>164.2</v>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>169.12</v>
+        <v>279.12</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>644.6000000000001</v>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>270.3816666666667</v>
+        <v>332.8816666666667</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>268.2</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>290.6533333333333</v>
+        <v>532.6533333333334</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>164.2</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>211.885</v>
+        <v>221.885</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>164.2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>151.04</v>
+        <v>217.04</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>276.2</v>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>267.8</v>
+        <v>410.8</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>164.2</v>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>324.1833333333333</v>
+        <v>439.6833333333333</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>164.2</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>314.66</v>
+        <v>325.16</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>260.2</v>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>244.3</v>
+        <v>299.3</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>620.2</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>28.92</v>
+        <v>83.92</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>1114.9</v>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>240.8133333333333</v>
+        <v>324.8133333333333</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>164.2</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>38.43</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>212.2</v>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>51.3</v>
+        <v>106.3</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>1794.42</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>40.41</v>
+        <v>95.41</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>348.2</v>
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>331.78</v>
+        <v>397.78</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>246.3</v>
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>354.04</v>
+        <v>590.54</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>164.2</v>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>248.04</v>
+        <v>314.04</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>1000.8</v>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>259.8</v>
+        <v>369.8</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>332.2</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>240.355</v>
+        <v>350.355</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>348.2</v>
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>251.035</v>
+        <v>361.035</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>228.2</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>323.56</v>
+        <v>444.56</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>212.2</v>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>275.1833333333333</v>
+        <v>390.6833333333333</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>356.2</v>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>281.5</v>
+        <v>402.5</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>548.6</v>
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>318.1433333333333</v>
+        <v>549.1433333333333</v>
       </c>
       <c r="C31" s="7" t="n">
         <v>164.2</v>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>72.075</v>
+        <v>198.575</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>164.2</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>180.0133333333333</v>
+        <v>213.0133333333333</v>
       </c>
       <c r="C33" s="7" t="n">
         <v>428.2</v>
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>136.145</v>
+        <v>257.145</v>
       </c>
       <c r="C34" s="7" t="n">
         <v>1012.6</v>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>213.93</v>
+        <v>345.93</v>
       </c>
       <c r="C35" s="7" t="n">
         <v>644.6</v>
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>141.3</v>
+        <v>229.3</v>
       </c>
       <c r="C36" s="7" t="n">
         <v>996.5800000000002</v>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>326.03</v>
+        <v>601.03</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>300.2</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>177.12</v>
+        <v>254.12</v>
       </c>
       <c r="C38" s="7" t="n">
         <v>1112.8</v>
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>242.115</v>
+        <v>396.115</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>228.2</v>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>130.43</v>
+        <v>150.43</v>
       </c>
       <c r="C40" s="7" t="n">
         <v>918.7</v>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>199.885</v>
+        <v>209.885</v>
       </c>
       <c r="C41" s="7" t="n">
         <v>398.3</v>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>184.28</v>
+        <v>415.28</v>
       </c>
       <c r="C42" s="7" t="n">
         <v>164.2</v>
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>302.2416666666667</v>
+        <v>436.2416666666667</v>
       </c>
       <c r="C43" s="7" t="n">
         <v>268.2</v>
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>234.8916666666667</v>
+        <v>317.3916666666667</v>
       </c>
       <c r="C44" s="7" t="n">
         <v>164.2</v>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>259.84</v>
+        <v>300.34</v>
       </c>
       <c r="C45" s="7" t="n">
         <v>478.3</v>
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>233.5966666666667</v>
+        <v>277.0966666666666</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>276.2</v>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>296.84</v>
+        <v>516.8399999999999</v>
       </c>
       <c r="C47" s="7" t="n">
         <v>164.2</v>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>233.315</v>
+        <v>315.815</v>
       </c>
       <c r="C48" s="7" t="n">
         <v>520.4000000000001</v>
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>155.71</v>
+        <v>227.21</v>
       </c>
       <c r="C49" s="7" t="n">
         <v>452.2</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>199.12</v>
+        <v>325.62</v>
       </c>
       <c r="C50" s="7" t="n">
         <v>350.3</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>420.18</v>
+        <v>706.1800000000001</v>
       </c>
       <c r="C51" s="7" t="n">
         <v>364.2</v>
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>247.795</v>
+        <v>272.795</v>
       </c>
       <c r="C52" s="7" t="n">
         <v>356.2</v>
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>220.91</v>
+        <v>347.41</v>
       </c>
       <c r="C53" s="7" t="n">
         <v>676.2</v>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>316.505</v>
+        <v>424.505</v>
       </c>
       <c r="C54" s="7" t="n">
         <v>244.2</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>83.67</v>
+        <v>138.67</v>
       </c>
       <c r="C55" s="7" t="n">
         <v>638.7</v>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>296.35</v>
+        <v>376.35</v>
       </c>
       <c r="C56" s="7" t="n">
         <v>180.2</v>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -913,10 +913,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1016.6</v>
+        <v>983.6</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>347.3</v>
+        <v>314.3</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>412.2</v>
@@ -926,7 +926,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
+          <t>NLPG (20cr): Adrian Bors: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -960,10 +960,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1346.015</v>
+        <v>1263.614</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>398.415</v>
+        <v>316.014</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>444.2</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IDEV (20cr): Alena Denisova: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PLEI (20cr): Alena Denisova: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>854.6166666666667</v>
+        <v>808.9373333333333</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>247.2166666666667</v>
+        <v>201.5373333333333</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>268.2</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>AURO (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; THE2 (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -1054,10 +1054,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>949.4433333333333</v>
+        <v>846.8866666666667</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>528.1433333333333</v>
+        <v>425.5866666666666</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>164.2</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SYS1 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -1101,10 +1101,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1098.72</v>
+        <v>1012.553333333334</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>279.12</v>
+        <v>192.9533333333333</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>644.6000000000001</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>ELLA (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>ELLA (20cr): Antonio Garcia-Dominguez: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ENG2 (20cr): Antonio Garcia-Dominguez: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -1148,10 +1148,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>940.2816666666668</v>
+        <v>921.9026666666666</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>332.8816666666667</v>
+        <v>314.5026666666666</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>268.2</v>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CTAP (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 3.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; PRAD (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -1195,10 +1195,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1159.203333333333</v>
+        <v>1066.247333333333</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>532.6533333333334</v>
+        <v>439.6973333333333</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>164.2</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS2 (20cr): Christopher Crispin-Bailey: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS3 (20cr): Christopher Crispin-Bailey: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1242,10 +1242,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>643.1849999999999</v>
+        <v>647.034</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>221.885</v>
+        <v>225.734</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>164.2</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 1 students x 3h = 3.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
+          <t>HINT (20cr): Claire Ingram: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 1 students x 3h = 3.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1289,10 +1289,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>668.24</v>
+        <v>631.6613333333333</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>217.04</v>
+        <v>180.4613333333333</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>276.2</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>IMLO (20cr): Claudio Guarnera: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>LPTC (20cr): Standard (2.5x): 10.0h/teacher @ 2.5x = 25.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
+          <t>LPTC (20cr): Colin Paterson: Standard (2.5x): 0.0h/teacher @ 2.5x; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1383,10 +1383,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>750</v>
+        <v>651</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>410.8</v>
+        <v>311.8</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>164.2</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS3 (20cr): Da Li: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1430,10 +1430,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>778.8833333333333</v>
+        <v>718.4933333333333</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>439.6833333333333</v>
+        <v>379.2933333333334</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>164.2</v>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SOF1 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1477,10 +1477,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1088.76</v>
+        <v>1096.725333333333</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>325.16</v>
+        <v>333.1253333333333</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>260.2</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>THE2 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1524,10 +1524,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1258.7</v>
+        <v>1225.7</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>299.3</v>
+        <v>266.3</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>620.2</v>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>NLPG (20cr): Dimitar Kazakov: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1571,10 +1571,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1373.82</v>
+        <v>1327.986666666667</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>83.92</v>
+        <v>38.08666666666667</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>1114.9</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher</t>
+          <t>ENG2 (20cr): Dimitris Kolovos: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1618,10 +1618,10 @@
         <v>1</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>664.0133333333333</v>
+        <v>616.8119999999999</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>324.8133333333333</v>
+        <v>277.612</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>164.2</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>SOF2 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; THE3 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>SOF2 (20cr): Fang Yan: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; THE3 (20cr): Fang Yan: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1665,10 +1665,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>480.63</v>
+        <v>439.38</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>93.43000000000001</v>
+        <v>52.18</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>212.2</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher</t>
+          <t>SAIL (20cr): Felix Ulrich-Oltean: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1712,10 +1712,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2157.82</v>
+        <v>2116.57</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>106.3</v>
+        <v>65.05</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>1794.42</v>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>LLMA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
+          <t>LLMA (20cr): Frank Soboczenski: Standard (2.5x): 0.0h/teacher @ 2.5x; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -1806,10 +1806,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1439.61</v>
+        <v>1406.61</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>95.41</v>
+        <v>62.41</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>348.2</v>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher</t>
+          <t>EMBS (20cr): Ian Gray: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1853,10 +1853,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>983.28</v>
+        <v>946.6573333333333</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>397.78</v>
+        <v>361.1573333333333</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>246.3</v>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Projects (40cr): Standard (2.5x): 40.0h/teacher @ 2.5x = 100.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 39.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>HCIN (20cr): Jacob Rigby: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Projects (40cr): Jacob Rigby: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -1900,10 +1900,10 @@
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1011.84</v>
+        <v>822.09</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>590.54</v>
+        <v>400.79</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>164.2</v>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>DEEP (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; LLMA (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DEEP (20cr): James Stovold: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; LLMA (20cr): James Stovold: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -1947,10 +1947,10 @@
         <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1489.84</v>
+        <v>1453.261333333333</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>314.04</v>
+        <v>277.4613333333333</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>1000.8</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IMLO (20cr): James Walker: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1994,10 +1994,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>877</v>
+        <v>802.75</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>369.8</v>
+        <v>295.55</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>332.2</v>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>QUAL (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; TECC (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -2041,10 +2041,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1037.755</v>
+        <v>955.354</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>350.355</v>
+        <v>267.954</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>348.2</v>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>PLEI (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; QUAL (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -2088,10 +2088,10 @@
         <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>764.235</v>
+        <v>690.018</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>361.035</v>
+        <v>286.818</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>228.2</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IDEV (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PRAD (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -2135,10 +2135,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1160.16</v>
+        <v>1090.537333333333</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>444.56</v>
+        <v>374.9373333333333</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>212.2</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>HCIN (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; TECC (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -2182,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1168.183333333333</v>
+        <v>1107.793333333333</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>390.6833333333333</v>
+        <v>330.2933333333334</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>356.2</v>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>SOF1 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2229,20 +2229,20 @@
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1126.1</v>
+        <v>1125.7</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>402.5</v>
+        <v>320</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>548.6</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>ENG1 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; ENG2 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>PGR Training Officer: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>PhD Training Officer: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -2276,10 +2276,10 @@
         <v>1</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>970.4433333333333</v>
+        <v>867.8866666666667</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>549.1433333333333</v>
+        <v>446.5866666666666</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>164.2</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SYS1 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2323,10 +2323,10 @@
         <v>1</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>619.875</v>
+        <v>548.606</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>198.575</v>
+        <v>127.306</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>164.2</v>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher</t>
+          <t>CBDA (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; GODS (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2370,10 +2370,10 @@
         <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1473.013333333333</v>
+        <v>1454.724</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>213.0133333333333</v>
+        <v>194.724</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>428.2</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>THE1 (20cr): Nick Pears: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2417,10 +2417,10 @@
         <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1608.945</v>
+        <v>1539.421333333333</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>257.145</v>
+        <v>187.6213333333333</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1012.6</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher; HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>GODS (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HCIN (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2464,10 +2464,10 @@
         <v>1</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1329.73</v>
+        <v>1243.717333333333</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>345.93</v>
+        <v>259.9173333333333</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>644.6</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>AURO (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS1 (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2511,10 +2511,10 @@
         <v>1</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1400.88</v>
+        <v>1356.88</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>229.3</v>
+        <v>185.3</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>996.5800000000002</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>SYS3 (20cr): Pengcheng Liu: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2558,10 +2558,10 @@
         <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1240.43</v>
+        <v>1006.68</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>601.03</v>
+        <v>367.28</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>300.2</v>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>ARIA (20cr): Existing lecturer + new content (5x): 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>ARIA (20cr): Peter Nightingale: Existing lecturer + new content (5.0x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; FOAM (20cr): Peter Nightingale: Existing lecturer + new content (5.0x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SAIL (20cr): Peter Nightingale: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -2605,10 +2605,10 @@
         <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1706.12</v>
+        <v>1665.830666666667</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>254.12</v>
+        <v>213.8306666666667</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>1112.8</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>SOF1 (20cr): Poonam Yadav: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2652,10 +2652,10 @@
         <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>922.465</v>
+        <v>841.9193333333334</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>396.115</v>
+        <v>315.5693333333334</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>228.2</v>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>DATA (20cr): Pourya Shamsolmoali: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; IMLO (20cr): Pourya Shamsolmoali: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2699,10 +2699,10 @@
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1244.13</v>
+        <v>1237.88</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>150.43</v>
+        <v>144.18</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>918.7</v>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>GPIG (40cr): Radu Calinescu: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2746,10 +2746,10 @@
         <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>783.1849999999999</v>
+        <v>787.034</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>209.885</v>
+        <v>213.734</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>398.3</v>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HINT (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -2793,10 +2793,10 @@
         <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>754.48</v>
+        <v>567.48</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>415.28</v>
+        <v>228.28</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>164.2</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; ENG1 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 2 students x 3h = 6.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>ELLA (20cr): Robbert Jongeling: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ENG1 (20cr): Robbert Jongeling: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Project setting (fixed): 6.0h; Pastoral: 2 students x 3h = 6.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
@@ -2840,10 +2840,10 @@
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>879.4416666666666</v>
+        <v>845.1946666666666</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>436.2416666666667</v>
+        <v>401.9946666666667</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>268.2</v>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CBDA (20cr): Roberto Metere: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; CTAP (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 3.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; EHAC (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -2887,10 +2887,10 @@
         <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>656.5916666666667</v>
+        <v>587.9406666666666</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>317.3916666666667</v>
+        <v>248.7406666666667</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>164.2</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>QUCO (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; THE2 (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Project setting (fixed): 6.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -2934,10 +2934,10 @@
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1117.84</v>
+        <v>1114.138666666667</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>300.34</v>
+        <v>296.6386666666667</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>478.3</v>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CTAP (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 3.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE1 (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -2981,10 +2981,10 @@
         <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>728.2966666666666</v>
+        <v>733.74</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>277.0966666666666</v>
+        <v>282.54</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>276.2</v>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>THE1 (20cr): Simon Foster: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Simon Foster: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3028,10 +3028,10 @@
         <v>1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>856.04</v>
+        <v>659.9613333333333</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>516.8399999999999</v>
+        <v>320.7613333333333</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>164.2</v>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>AURO (20cr): Soumya Banerjee: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ELLA (20cr): Soumya Banerjee: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
@@ -3075,10 +3075,10 @@
         <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1257.515</v>
+        <v>1188.798</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>315.815</v>
+        <v>247.098</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>520.4000000000001</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>QUCO (20cr): Stefano Pirandola: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3122,10 +3122,10 @@
         <v>1</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>854.41</v>
+        <v>815.976</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>227.21</v>
+        <v>188.776</v>
       </c>
       <c r="E49" s="3" t="n">
         <v>452.2</v>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>HIPC (20cr): Steven Wright: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3169,10 +3169,10 @@
         <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1179.32</v>
+        <v>1107.886</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>325.62</v>
+        <v>254.186</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>350.3</v>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher; HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>EMBS (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HIPC (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -3216,10 +3216,10 @@
         <v>1</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1409.58</v>
+        <v>1180.413333333333</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>706.1800000000001</v>
+        <v>477.0133333333333</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>364.2</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>ARIA (20cr): Existing lecturer + new content (5x): 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>ARIA (20cr): Tommy Yuan: Existing lecturer + new content (5.0x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ENG1 (20cr): Tommy Yuan: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; FOAM (20cr): Tommy Yuan: Existing lecturer + new content (5.0x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -3263,10 +3263,10 @@
         <v>1</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>968.1950000000001</v>
+        <v>965.2940000000001</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>272.795</v>
+        <v>269.894</v>
       </c>
       <c r="E52" s="3" t="n">
         <v>356.2</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>NETS (20cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -3310,10 +3310,10 @@
         <v>1</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>1321.76</v>
+        <v>1250.326</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>347.41</v>
+        <v>275.976</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>676.2</v>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>DEEP (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>DEEP (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; ROCS (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
@@ -3357,10 +3357,10 @@
         <v>1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>925.8049999999999</v>
+        <v>875.5880000000001</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>424.505</v>
+        <v>374.288</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>244.2</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DATA (20cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; GPIG (40cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -3404,10 +3404,10 @@
         <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>952.3700000000001</v>
+        <v>919.436</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>138.67</v>
+        <v>105.736</v>
       </c>
       <c r="E55" s="3" t="n">
         <v>638.7</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>ROCS (20cr): Yan Jia: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -3451,10 +3451,10 @@
         <v>1</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>813.65</v>
+        <v>777.782</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>376.35</v>
+        <v>340.482</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>180.2</v>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>EHAC (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; NETS (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>347.3</v>
+        <v>314.3</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>412.2</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>398.415</v>
+        <v>316.014</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>444.2</v>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>247.2166666666667</v>
+        <v>201.5373333333333</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>268.2</v>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>528.1433333333333</v>
+        <v>425.5866666666666</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>164.2</v>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>279.12</v>
+        <v>192.9533333333333</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>644.6000000000001</v>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>332.8816666666667</v>
+        <v>314.5026666666666</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>268.2</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>532.6533333333334</v>
+        <v>439.6973333333333</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>164.2</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>221.885</v>
+        <v>225.734</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>164.2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>217.04</v>
+        <v>180.4613333333333</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>276.2</v>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>410.8</v>
+        <v>311.8</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>164.2</v>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>439.6833333333333</v>
+        <v>379.2933333333334</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>164.2</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>325.16</v>
+        <v>333.1253333333333</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>260.2</v>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>299.3</v>
+        <v>266.3</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>620.2</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>83.92</v>
+        <v>38.08666666666667</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>1114.9</v>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>324.8133333333333</v>
+        <v>277.612</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>164.2</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>93.43000000000001</v>
+        <v>52.18</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>212.2</v>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>106.3</v>
+        <v>65.05</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>1794.42</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>95.41</v>
+        <v>62.41</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>348.2</v>
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>397.78</v>
+        <v>361.1573333333333</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>246.3</v>
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>590.54</v>
+        <v>400.79</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>164.2</v>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>314.04</v>
+        <v>277.4613333333333</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>1000.8</v>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>369.8</v>
+        <v>295.55</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>332.2</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>350.355</v>
+        <v>267.954</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>348.2</v>
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>361.035</v>
+        <v>286.818</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>228.2</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>444.56</v>
+        <v>374.9373333333333</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>212.2</v>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>390.6833333333333</v>
+        <v>330.2933333333334</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>356.2</v>
@@ -4117,13 +4117,13 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>402.5</v>
+        <v>320</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>548.6</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E30" s="7">
         <f>SUM(B30:D30)</f>
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>549.1433333333333</v>
+        <v>446.5866666666666</v>
       </c>
       <c r="C31" s="7" t="n">
         <v>164.2</v>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>198.575</v>
+        <v>127.306</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>164.2</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>213.0133333333333</v>
+        <v>194.724</v>
       </c>
       <c r="C33" s="7" t="n">
         <v>428.2</v>
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>257.145</v>
+        <v>187.6213333333333</v>
       </c>
       <c r="C34" s="7" t="n">
         <v>1012.6</v>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>345.93</v>
+        <v>259.9173333333333</v>
       </c>
       <c r="C35" s="7" t="n">
         <v>644.6</v>
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>229.3</v>
+        <v>185.3</v>
       </c>
       <c r="C36" s="7" t="n">
         <v>996.5800000000002</v>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>601.03</v>
+        <v>367.28</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>300.2</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>254.12</v>
+        <v>213.8306666666667</v>
       </c>
       <c r="C38" s="7" t="n">
         <v>1112.8</v>
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>396.115</v>
+        <v>315.5693333333334</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>228.2</v>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>150.43</v>
+        <v>144.18</v>
       </c>
       <c r="C40" s="7" t="n">
         <v>918.7</v>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>209.885</v>
+        <v>213.734</v>
       </c>
       <c r="C41" s="7" t="n">
         <v>398.3</v>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>415.28</v>
+        <v>228.28</v>
       </c>
       <c r="C42" s="7" t="n">
         <v>164.2</v>
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>436.2416666666667</v>
+        <v>401.9946666666667</v>
       </c>
       <c r="C43" s="7" t="n">
         <v>268.2</v>
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>317.3916666666667</v>
+        <v>248.7406666666667</v>
       </c>
       <c r="C44" s="7" t="n">
         <v>164.2</v>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>300.34</v>
+        <v>296.6386666666667</v>
       </c>
       <c r="C45" s="7" t="n">
         <v>478.3</v>
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>277.0966666666666</v>
+        <v>282.54</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>276.2</v>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>516.8399999999999</v>
+        <v>320.7613333333333</v>
       </c>
       <c r="C47" s="7" t="n">
         <v>164.2</v>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>315.815</v>
+        <v>247.098</v>
       </c>
       <c r="C48" s="7" t="n">
         <v>520.4000000000001</v>
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>227.21</v>
+        <v>188.776</v>
       </c>
       <c r="C49" s="7" t="n">
         <v>452.2</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>325.62</v>
+        <v>254.186</v>
       </c>
       <c r="C50" s="7" t="n">
         <v>350.3</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>706.1800000000001</v>
+        <v>477.0133333333333</v>
       </c>
       <c r="C51" s="7" t="n">
         <v>364.2</v>
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>272.795</v>
+        <v>269.894</v>
       </c>
       <c r="C52" s="7" t="n">
         <v>356.2</v>
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>347.41</v>
+        <v>275.976</v>
       </c>
       <c r="C53" s="7" t="n">
         <v>676.2</v>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>424.505</v>
+        <v>374.288</v>
       </c>
       <c r="C54" s="7" t="n">
         <v>244.2</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>138.67</v>
+        <v>105.736</v>
       </c>
       <c r="C55" s="7" t="n">
         <v>638.7</v>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>376.35</v>
+        <v>340.482</v>
       </c>
       <c r="C56" s="7" t="n">
         <v>180.2</v>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -195,12 +195,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Staff Workload'!$A$2:$A$56</f>
+              <f>'Staff Workload'!$A$2:$A$57</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Staff Workload'!$D$2:$D$56</f>
+              <f>'Staff Workload'!$D$2:$D$57</f>
             </numRef>
           </val>
         </ser>
@@ -219,12 +219,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Staff Workload'!$A$2:$A$56</f>
+              <f>'Staff Workload'!$A$2:$A$57</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Staff Workload'!$E$2:$E$56</f>
+              <f>'Staff Workload'!$E$2:$E$57</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +243,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Staff Workload'!$A$2:$A$56</f>
+              <f>'Staff Workload'!$A$2:$A$57</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Staff Workload'!$F$2:$F$56</f>
+              <f>'Staff Workload'!$F$2:$F$57</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Detailed Breakdown'!$A$2:$A$56</f>
+              <f>'Detailed Breakdown'!$A$2:$A$57</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Detailed Breakdown'!$B$2:$B$56</f>
+              <f>'Detailed Breakdown'!$B$2:$B$57</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Detailed Breakdown'!$A$2:$A$56</f>
+              <f>'Detailed Breakdown'!$A$2:$A$57</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Detailed Breakdown'!$C$2:$C$56</f>
+              <f>'Detailed Breakdown'!$C$2:$C$57</f>
             </numRef>
           </val>
         </ser>
@@ -408,12 +408,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Detailed Breakdown'!$A$2:$A$56</f>
+              <f>'Detailed Breakdown'!$A$2:$A$57</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Detailed Breakdown'!$D$2:$D$56</f>
+              <f>'Detailed Breakdown'!$D$2:$D$57</f>
             </numRef>
           </val>
         </ser>
@@ -830,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -913,10 +913,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>983.6</v>
+        <v>1014.1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>314.3</v>
+        <v>344.8</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>412.2</v>
@@ -926,7 +926,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Adrian Bors: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
+          <t>NLPG (20cr): Adrian Bors: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -960,10 +960,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1263.614</v>
+        <v>1289.114</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>316.014</v>
+        <v>341.514</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>444.2</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Alena Denisova: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PLEI (20cr): Alena Denisova: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IDEV (20cr): Alena Denisova: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PLEI (20cr): Alena Denisova: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>808.9373333333333</v>
+        <v>815.104</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>201.5373333333333</v>
+        <v>207.704</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>268.2</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; THE2 (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>AURO (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; THE2 (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -1054,10 +1054,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>846.8866666666667</v>
+        <v>872.8866666666667</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>425.5866666666666</v>
+        <v>451.5866666666667</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>164.2</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SYS1 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 11 students x 3h = 33.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -1101,10 +1101,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1012.553333333334</v>
+        <v>1060.72</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>192.9533333333333</v>
+        <v>241.12</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>644.6000000000001</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>ELLA (20cr): Antonio Garcia-Dominguez: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ENG2 (20cr): Antonio Garcia-Dominguez: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>ELLA (20cr): Antonio Garcia-Dominguez: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Robbert Jongeling: 5x, Antonio Garcia-Dominguez: 2.5x, Soumya Banerjee: 5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ENG2 (20cr): Antonio Garcia-Dominguez: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -1148,10 +1148,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>921.9026666666666</v>
+        <v>1016.069333333333</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>314.5026666666666</v>
+        <v>408.6693333333333</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>268.2</v>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 3.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; PRAD (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CTAP (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; PRAD (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -1195,10 +1195,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1066.247333333333</v>
+        <v>1155.914</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>439.6973333333333</v>
+        <v>529.364</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>164.2</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>SYS2 (20cr): Christopher Crispin-Bailey: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS3 (20cr): Christopher Crispin-Bailey: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS2 (20cr): Christopher Crispin-Bailey: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS3 (20cr): Christopher Crispin-Bailey: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Pengcheng Liu: 2.5x, Christopher Crispin-Bailey: 2.5x, Da Li: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1242,10 +1242,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>647.034</v>
+        <v>658.284</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>225.734</v>
+        <v>236.984</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>164.2</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Claire Ingram: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 1 students x 3h = 3.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
+          <t>HINT (20cr): Claire Ingram: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 1 students x 3h = 3.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1289,10 +1289,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>631.6613333333333</v>
+        <v>663.6613333333333</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>180.4613333333333</v>
+        <v>212.4613333333333</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>276.2</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Claudio Guarnera: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>IMLO (20cr): Claudio Guarnera: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1336,10 +1336,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>983.5599999999999</v>
+        <v>978.5599999999999</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>228.8</v>
+        <v>223.8</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>579.76</v>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>LPTC (20cr): Colin Paterson: Standard (2.5x): 0.0h/teacher @ 2.5x; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
+          <t>LPTC (20cr): Colin Paterson: Standard (2.5x): 0.0h/teacher @ 2.5x; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1383,10 +1383,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>651</v>
+        <v>749.6666666666667</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>311.8</v>
+        <v>410.4666666666667</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>164.2</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): Da Li: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS3 (20cr): Da Li: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Pengcheng Liu: 2.5x, Christopher Crispin-Bailey: 2.5x, Da Li: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1430,10 +1430,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>718.4933333333333</v>
+        <v>775.8266666666666</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>379.2933333333334</v>
+        <v>436.6266666666667</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>164.2</v>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SOF1 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1477,10 +1477,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1096.725333333333</v>
+        <v>1112.058666666667</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>333.1253333333333</v>
+        <v>348.4586666666667</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>260.2</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>THE2 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>THE2 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Detlef Plump: 2.5x, Simon Foster: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1524,10 +1524,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1225.7</v>
+        <v>1256.2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>266.3</v>
+        <v>296.8</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>620.2</v>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Dimitar Kazakov: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>NLPG (20cr): Dimitar Kazakov: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1571,10 +1571,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1327.986666666667</v>
+        <v>1339.486666666667</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>38.08666666666667</v>
+        <v>49.58666666666667</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>1114.9</v>
@@ -1618,10 +1618,10 @@
         <v>1</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>616.8119999999999</v>
+        <v>712.1453333333334</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>277.612</v>
+        <v>372.9453333333333</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>164.2</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>SOF2 (20cr): Fang Yan: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; THE3 (20cr): Fang Yan: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>SOF2 (20cr): Fang Yan: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; THE3 (20cr): Fang Yan: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Detlef Plump: 2.5x, Simon Foster: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1665,10 +1665,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>439.38</v>
+        <v>456.63</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>52.18</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>212.2</v>
@@ -1712,10 +1712,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2116.57</v>
+        <v>2133.82</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>65.05</v>
+        <v>82.3</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>1794.42</v>
@@ -1806,10 +1806,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1406.61</v>
+        <v>1443.11</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>62.41</v>
+        <v>98.91</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>348.2</v>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>EMBS (20cr): Ian Gray: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
+          <t>EMBS (20cr): Ian Gray: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1853,10 +1853,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>946.6573333333333</v>
+        <v>930.6573333333333</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>361.1573333333333</v>
+        <v>345.1573333333333</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>246.3</v>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Jacob Rigby: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Projects (40cr): Jacob Rigby: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>HCIN (20cr): Jacob Rigby: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Projects (40cr): Jacob Rigby: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1900,10 +1900,10 @@
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>822.09</v>
+        <v>967.84</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>400.79</v>
+        <v>546.54</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>164.2</v>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>DEEP (20cr): James Stovold: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; LLMA (20cr): James Stovold: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DEEP (20cr): James Stovold: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, James Stovold: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; LLMA (20cr): James Stovold: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1947,10 +1947,10 @@
         <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1453.261333333333</v>
+        <v>1485.261333333333</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>277.4613333333333</v>
+        <v>309.4613333333333</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>1000.8</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): James Walker: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IMLO (20cr): James Walker: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1994,10 +1994,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>802.75</v>
+        <v>850.5</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>295.55</v>
+        <v>343.3</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>332.2</v>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>QUAL (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; TECC (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>QUAL (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; TECC (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2041,10 +2041,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>955.354</v>
+        <v>982.354</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>267.954</v>
+        <v>294.954</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>348.2</v>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>PLEI (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; QUAL (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>PLEI (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; QUAL (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2088,10 +2088,10 @@
         <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>690.018</v>
+        <v>736.268</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>286.818</v>
+        <v>333.068</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>228.2</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PRAD (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IDEV (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PRAD (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2135,10 +2135,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1090.537333333333</v>
+        <v>1159.037333333333</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>374.9373333333333</v>
+        <v>443.4373333333333</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>212.2</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; TECC (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>HCIN (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; TECC (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2182,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1107.793333333333</v>
+        <v>1165.126666666667</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>330.2933333333334</v>
+        <v>387.6266666666667</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>356.2</v>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>SOF1 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2229,10 +2229,10 @@
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1125.7</v>
+        <v>1169.2</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>320</v>
+        <v>363.5</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>548.6</v>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; ENG2 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>ENG1 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Kostas Barmpis: 2.5x, Robbert Jongeling: 5x, Tommy Yuan: 2.5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; ENG2 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2276,10 +2276,10 @@
         <v>1</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>867.8866666666667</v>
+        <v>893.8866666666667</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>446.5866666666666</v>
+        <v>472.5866666666667</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>164.2</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 2 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SYS1 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2323,10 +2323,10 @@
         <v>1</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>548.606</v>
+        <v>627.106</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>127.306</v>
+        <v>205.806</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>164.2</v>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; GODS (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
+          <t>CBDA (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; GODS (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2370,10 +2370,10 @@
         <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1454.724</v>
+        <v>1468.557333333333</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>194.724</v>
+        <v>208.5573333333333</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>428.2</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Nick Pears: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>THE1 (20cr): Nick Pears: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2417,10 +2417,10 @@
         <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1539.421333333333</v>
+        <v>1607.921333333333</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>187.6213333333333</v>
+        <v>256.1213333333333</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1012.6</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>GODS (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HCIN (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>GODS (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HCIN (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2464,10 +2464,10 @@
         <v>1</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1243.717333333333</v>
+        <v>1291.884</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>259.9173333333333</v>
+        <v>308.084</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>644.6</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS1 (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>AURO (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS1 (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2511,10 +2511,10 @@
         <v>1</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1356.88</v>
+        <v>1397.213333333334</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>185.3</v>
+        <v>225.6333333333333</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>996.5800000000002</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): Pengcheng Liu: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>SYS3 (20cr): Pengcheng Liu: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Pengcheng Liu: 2.5x, Christopher Crispin-Bailey: 2.5x, Da Li: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2558,10 +2558,10 @@
         <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1006.68</v>
+        <v>1117.43</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>367.28</v>
+        <v>478.03</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>300.2</v>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>ARIA (20cr): Peter Nightingale: Existing lecturer + new content (5.0x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; FOAM (20cr): Peter Nightingale: Existing lecturer + new content (5.0x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SAIL (20cr): Peter Nightingale: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>ARIA (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; FOAM (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SAIL (20cr): Peter Nightingale: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2598,37 +2598,33 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Poonam Yadav</t>
+          <t>Phoebe</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1665.830666666667</v>
+        <v>339.2</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>213.8306666666667</v>
+        <v>0</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1112.8</v>
+        <v>164.2</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>339.2</v>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>SOF1 (20cr): Poonam Yadav: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
-        </is>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="G38" s="4" t="inlineStr"/>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h; Grant CHEDDAR Funding Apr-Sep 26- PSU296: 5% of 1642h = 82.1h; Grant REMOTE: Resilient and Secure Multi-Access Interoperable Communication Fabric for TinyEdge: 20% of 1642h = 328.4h; Grant Orchestrated mobile Network for Blackpool intelligent transport: 5% of 1642h = 82.1h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
@@ -2638,44 +2634,44 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Pourya Shamsolmoali</t>
+          <t>Poonam Yadav</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>841.9193333333334</v>
+        <v>1702.497333333333</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>315.5693333333334</v>
+        <v>250.4973333333333</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>228.2</v>
+        <v>1112.8</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>298.15</v>
+        <v>339.2</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Pourya Shamsolmoali: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; IMLO (20cr): Pourya Shamsolmoali: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>SOF1 (20cr): Poonam Yadav: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h; Grant CHEDDAR Funding Apr-Sep 26- PSU296: 5% of 1642h = 82.1h; Grant REMOTE: Resilient and Secure Multi-Access Interoperable Communication Fabric for TinyEdge: 20% of 1642h = 328.4h; Grant Orchestrated mobile Network for Blackpool intelligent transport: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Graduate School Board (Ordinary member): 2% of 1642h = 41.1h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -2692,37 +2688,37 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Radu Calinescu</t>
+          <t>Pourya Shamsolmoali</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1237.88</v>
+        <v>921.4193333333334</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>144.18</v>
+        <v>395.0693333333334</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>918.7</v>
+        <v>228.2</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>175</v>
+        <v>298.15</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>GPIG (40cr): Radu Calinescu: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>DATA (20cr): Pourya Shamsolmoali: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; IMLO (20cr): Pourya Shamsolmoali: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h; Grant ARISE: Accelerating ReIntroduction of EcoSystem-Engineering Ant Colonies with Embodied AI: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h; Grant MammoBot: Robotic Posture Assistance for Universal Breast Screening Access: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Graduate School Board (Ordinary member): 2% of 1642h = 41.1h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -2732,44 +2728,44 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Rob Alexander</t>
+          <t>Radu Calinescu</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>787.034</v>
+        <v>1221.13</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>213.734</v>
+        <v>127.43</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>398.3</v>
+        <v>918.7</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>GPIG (40cr): Radu Calinescu: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h; Grant ARISE: Accelerating ReIntroduction of EcoSystem-Engineering Ant Colonies with Embodied AI: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h; Grant MammoBot: Robotic Posture Assistance for Universal Breast Screening Access: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -2779,44 +2775,44 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Robbert Jongeling</t>
+          <t>Rob Alexander</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>567.48</v>
+        <v>798.284</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>228.28</v>
+        <v>224.984</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>164.2</v>
+        <v>398.3</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>ELLA (20cr): Robbert Jongeling: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ENG1 (20cr): Robbert Jongeling: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Project setting (fixed): 6.0h; Pastoral: 2 students x 3h = 6.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>HINT (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -2826,44 +2822,44 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Roberto Metere</t>
+          <t>Robbert Jongeling</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>845.1946666666666</v>
+        <v>758.8133333333333</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>401.9946666666667</v>
+        <v>419.6133333333333</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>268.2</v>
+        <v>164.2</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Roberto Metere: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; CTAP (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 3.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; EHAC (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>ELLA (20cr): Robbert Jongeling: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Robbert Jongeling: 5x, Antonio Garcia-Dominguez: 2.5x, Soumya Banerjee: 5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ENG1 (20cr): Robbert Jongeling: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Kostas Barmpis: 2.5x, Robbert Jongeling: 5x, Tommy Yuan: 2.5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 2 students x 3h = 6.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -2873,44 +2869,44 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Sam Braunstein</t>
+          <t>Roberto Metere</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>587.9406666666666</v>
+        <v>1039.861333333333</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>248.7406666666667</v>
+        <v>596.6613333333333</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>164.2</v>
+        <v>268.2</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; THE2 (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Project setting (fixed): 6.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CBDA (20cr): Roberto Metere: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; CTAP (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; EHAC (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
@@ -2920,44 +2916,44 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Siamak Shahandashti</t>
+          <t>Sam Braunstein</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1114.138666666667</v>
+        <v>614.8573333333334</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>296.6386666666667</v>
+        <v>275.6573333333333</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>478.3</v>
+        <v>164.2</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 3.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE1 (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>QUCO (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; THE2 (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h; Grant Participatory Harm Auditing Workbenches &amp; Methodologies: 5% of 1642h = 82.1h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -2967,44 +2963,44 @@
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Simon Foster</t>
+          <t>Siamak Shahandashti</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>733.74</v>
+        <v>1191.638666666667</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>282.54</v>
+        <v>374.1386666666667</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>276.2</v>
+        <v>478.3</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Simon Foster: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Simon Foster: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 1.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>CTAP (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE1 (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h; Grant Participatory Harm Auditing Workbenches &amp; Methodologies: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
@@ -3014,39 +3010,39 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Soumya Banerjee</t>
+          <t>Simon Foster</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>659.9613333333333</v>
+        <v>798.24</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>320.7613333333333</v>
+        <v>347.04</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>164.2</v>
+        <v>276.2</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): Soumya Banerjee: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ELLA (20cr): Soumya Banerjee: New lecturer (5.0x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>THE1 (20cr): Simon Foster: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Simon Foster: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Detlef Plump: 2.5x, Simon Foster: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -3068,37 +3064,37 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Stefano Pirandola</t>
+          <t>Soumya Banerjee</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1188.798</v>
+        <v>788.1279999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>247.098</v>
+        <v>448.928</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>520.4000000000001</v>
+        <v>164.2</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>421.3</v>
+        <v>175</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Stefano Pirandola: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>AURO (20cr): Soumya Banerjee: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ELLA (20cr): Soumya Banerjee: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Robbert Jongeling: 5x, Antonio Garcia-Dominguez: 2.5x, Soumya Banerjee: 5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Integrated Quantum Networks (IQN) Hub: 10% of 1642h = 164.2h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
@@ -3108,44 +3104,44 @@
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Steven Wright</t>
+          <t>Stefano Pirandola</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>815.976</v>
+        <v>1215.048</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>188.776</v>
+        <v>273.348</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>452.2</v>
+        <v>520.4000000000001</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>175</v>
+        <v>421.3</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>HIPC (20cr): Steven Wright: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>QUCO (20cr): Stefano Pirandola: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Integrated Quantum Networks (IQN) Hub: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>Chair of the Board of Examiners: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
@@ -3162,37 +3158,37 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Steven Xiaotian Dai</t>
+          <t>Steven Wright</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1107.886</v>
+        <v>851.976</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>254.186</v>
+        <v>224.776</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>350.3</v>
+        <v>452.2</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>EMBS (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HIPC (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>HIPC (20cr): Steven Wright: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h; Grant SCHEME: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>Student Disability Representative: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Chair of the Board of Examiners: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
@@ -3209,37 +3205,37 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Tommy Yuan</t>
+          <t>Steven Xiaotian Dai</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1180.413333333333</v>
+        <v>1180.386</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>477.0133333333333</v>
+        <v>326.686</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>364.2</v>
+        <v>350.3</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>339.2</v>
+        <v>503.4</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>ARIA (20cr): Tommy Yuan: Existing lecturer + new content (5.0x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ENG1 (20cr): Tommy Yuan: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; FOAM (20cr): Tommy Yuan: Existing lecturer + new content (5.0x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>EMBS (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HIPC (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 200.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h; Grant SCHEME: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>CSCSE SQA Partnership Leader: 0% of 1642h = 0.0h; Deputy CBoEs: 10% of 1642h = 164.2h; StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Student Disability Representative: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
@@ -3256,37 +3252,37 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Vasileios Vasilakis</t>
+          <t>Tommy Yuan</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>965.2940000000001</v>
+        <v>1311.913333333333</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>269.894</v>
+        <v>608.5133333333333</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>356.2</v>
+        <v>364.2</v>
       </c>
       <c r="F52" s="3" t="n">
         <v>339.2</v>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>NETS (20cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>ARIA (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ENG1 (20cr): Tommy Yuan: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Kostas Barmpis: 2.5x, Robbert Jongeling: 5x, Tommy Yuan: 2.5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; FOAM (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 200.0h</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>CSCSE SQA Partnership Leader: 0% of 1642h = 0.0h; Deputy CBoEs: 10% of 1642h = 164.2h; StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
@@ -3303,37 +3299,37 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>William Smith</t>
+          <t>Vasileios Vasilakis</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>1250.326</v>
+        <v>995.7940000000001</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>275.976</v>
+        <v>300.394</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>676.2</v>
+        <v>356.2</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>298.15</v>
+        <v>339.2</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>DEEP (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; ROCS (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>NETS (20cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
@@ -3350,37 +3346,37 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Xinwei Fang</t>
+          <t>William Smith</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>875.5880000000001</v>
+        <v>1321.326</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>374.288</v>
+        <v>346.976</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>244.2</v>
+        <v>676.2</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>257.1</v>
+        <v>298.15</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; GPIG (40cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DEEP (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, James Stovold: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; ROCS (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h</t>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
@@ -3397,37 +3393,37 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Yan Jia</t>
+          <t>Xinwei Fang</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>919.436</v>
+        <v>906.3380000000001</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>105.736</v>
+        <v>405.038</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>638.7</v>
+        <v>244.2</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>ROCS (20cr): Yan Jia: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>DATA (20cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; GPIG (40cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10% of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
@@ -3437,52 +3433,99 @@
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>Yan Jia</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>954.436</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>140.736</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>638.7</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>ROCS (20cr): Yan Jia: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10% of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>No administrative roles assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
           <t>Yuchen Zhao</t>
         </is>
       </c>
-      <c r="B56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" s="3" t="n">
-        <v>777.782</v>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>340.482</v>
-      </c>
-      <c r="E56" s="3" t="n">
+      <c r="B57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>843.282</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>405.982</v>
+      </c>
+      <c r="E57" s="3" t="n">
         <v>180.2</v>
       </c>
-      <c r="F56" s="3" t="n">
+      <c r="F57" s="3" t="n">
         <v>257.1</v>
       </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>EHAC (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; NETS (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; First time delivery: 1 sessions/week @ 2.0h each; - Standard lecturers: 2.5x first session (standard), 1.5x repeats; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>EHAC (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; NETS (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
         <is>
           <t>PhD supervision: 2x assessor (8h each) = 16.0h</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr">
+      <c r="I57" s="4" t="inlineStr">
         <is>
           <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3513,7 +3556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3557,7 +3600,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>314.3</v>
+        <v>344.8</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>412.2</v>
@@ -3577,7 +3620,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>316.014</v>
+        <v>341.514</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>444.2</v>
@@ -3597,7 +3640,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>201.5373333333333</v>
+        <v>207.704</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>268.2</v>
@@ -3617,7 +3660,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>425.5866666666666</v>
+        <v>451.5866666666667</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>164.2</v>
@@ -3637,7 +3680,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>192.9533333333333</v>
+        <v>241.12</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>644.6000000000001</v>
@@ -3657,7 +3700,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>314.5026666666666</v>
+        <v>408.6693333333333</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>268.2</v>
@@ -3677,7 +3720,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>439.6973333333333</v>
+        <v>529.364</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>164.2</v>
@@ -3697,7 +3740,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>225.734</v>
+        <v>236.984</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>164.2</v>
@@ -3717,7 +3760,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>180.4613333333333</v>
+        <v>212.4613333333333</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>276.2</v>
@@ -3737,7 +3780,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>228.8</v>
+        <v>223.8</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>579.76</v>
@@ -3757,7 +3800,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>311.8</v>
+        <v>410.4666666666667</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>164.2</v>
@@ -3777,7 +3820,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>379.2933333333334</v>
+        <v>436.6266666666667</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>164.2</v>
@@ -3797,7 +3840,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>333.1253333333333</v>
+        <v>348.4586666666667</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>260.2</v>
@@ -3817,7 +3860,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>266.3</v>
+        <v>296.8</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>620.2</v>
@@ -3837,7 +3880,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>38.08666666666667</v>
+        <v>49.58666666666667</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>1114.9</v>
@@ -3857,7 +3900,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>277.612</v>
+        <v>372.9453333333333</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>164.2</v>
@@ -3877,7 +3920,7 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>52.18</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>212.2</v>
@@ -3897,7 +3940,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>65.05</v>
+        <v>82.3</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>1794.42</v>
@@ -3937,7 +3980,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>62.41</v>
+        <v>98.91</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>348.2</v>
@@ -3957,7 +4000,7 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>361.1573333333333</v>
+        <v>345.1573333333333</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>246.3</v>
@@ -3977,7 +4020,7 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>400.79</v>
+        <v>546.54</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>164.2</v>
@@ -3997,7 +4040,7 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>277.4613333333333</v>
+        <v>309.4613333333333</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>1000.8</v>
@@ -4017,7 +4060,7 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>295.55</v>
+        <v>343.3</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>332.2</v>
@@ -4037,7 +4080,7 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>267.954</v>
+        <v>294.954</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>348.2</v>
@@ -4057,7 +4100,7 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>286.818</v>
+        <v>333.068</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>228.2</v>
@@ -4077,7 +4120,7 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>374.9373333333333</v>
+        <v>443.4373333333333</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>212.2</v>
@@ -4097,7 +4140,7 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>330.2933333333334</v>
+        <v>387.6266666666667</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>356.2</v>
@@ -4117,7 +4160,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>320</v>
+        <v>363.5</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>548.6</v>
@@ -4137,7 +4180,7 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>446.5866666666666</v>
+        <v>472.5866666666667</v>
       </c>
       <c r="C31" s="7" t="n">
         <v>164.2</v>
@@ -4157,7 +4200,7 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>127.306</v>
+        <v>205.806</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>164.2</v>
@@ -4177,7 +4220,7 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>194.724</v>
+        <v>208.5573333333333</v>
       </c>
       <c r="C33" s="7" t="n">
         <v>428.2</v>
@@ -4197,7 +4240,7 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>187.6213333333333</v>
+        <v>256.1213333333333</v>
       </c>
       <c r="C34" s="7" t="n">
         <v>1012.6</v>
@@ -4217,7 +4260,7 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>259.9173333333333</v>
+        <v>308.084</v>
       </c>
       <c r="C35" s="7" t="n">
         <v>644.6</v>
@@ -4237,7 +4280,7 @@
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>185.3</v>
+        <v>225.6333333333333</v>
       </c>
       <c r="C36" s="7" t="n">
         <v>996.5800000000002</v>
@@ -4257,7 +4300,7 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>367.28</v>
+        <v>478.03</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>300.2</v>
@@ -4273,17 +4316,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poonam Yadav</t>
+          <t>Phoebe</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>213.8306666666667</v>
+        <v>0</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>1112.8</v>
+        <v>164.2</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E38" s="7">
         <f>SUM(B38:D38)</f>
@@ -4293,17 +4336,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pourya Shamsolmoali</t>
+          <t>Poonam Yadav</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>315.5693333333334</v>
+        <v>250.4973333333333</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>228.2</v>
+        <v>1112.8</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>298.15</v>
+        <v>339.2</v>
       </c>
       <c r="E39" s="7">
         <f>SUM(B39:D39)</f>
@@ -4313,17 +4356,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Radu Calinescu</t>
+          <t>Pourya Shamsolmoali</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>144.18</v>
+        <v>395.0693333333334</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>918.7</v>
+        <v>228.2</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>175</v>
+        <v>298.15</v>
       </c>
       <c r="E40" s="7">
         <f>SUM(B40:D40)</f>
@@ -4333,14 +4376,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Rob Alexander</t>
+          <t>Radu Calinescu</t>
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>213.734</v>
+        <v>127.43</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>398.3</v>
+        <v>918.7</v>
       </c>
       <c r="D41" s="7" t="n">
         <v>175</v>
@@ -4353,14 +4396,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Robbert Jongeling</t>
+          <t>Rob Alexander</t>
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>228.28</v>
+        <v>224.984</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>164.2</v>
+        <v>398.3</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>175</v>
@@ -4373,14 +4416,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Roberto Metere</t>
+          <t>Robbert Jongeling</t>
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>401.9946666666667</v>
+        <v>419.6133333333333</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>268.2</v>
+        <v>164.2</v>
       </c>
       <c r="D43" s="7" t="n">
         <v>175</v>
@@ -4393,14 +4436,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sam Braunstein</t>
+          <t>Roberto Metere</t>
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>248.7406666666667</v>
+        <v>596.6613333333333</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>164.2</v>
+        <v>268.2</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>175</v>
@@ -4413,17 +4456,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Siamak Shahandashti</t>
+          <t>Sam Braunstein</t>
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>296.6386666666667</v>
+        <v>275.6573333333333</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>478.3</v>
+        <v>164.2</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E45" s="7">
         <f>SUM(B45:D45)</f>
@@ -4433,17 +4476,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Simon Foster</t>
+          <t>Siamak Shahandashti</t>
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>282.54</v>
+        <v>374.1386666666667</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>276.2</v>
+        <v>478.3</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E46" s="7">
         <f>SUM(B46:D46)</f>
@@ -4453,14 +4496,14 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Soumya Banerjee</t>
+          <t>Simon Foster</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>320.7613333333333</v>
+        <v>347.04</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>164.2</v>
+        <v>276.2</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>175</v>
@@ -4473,17 +4516,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Stefano Pirandola</t>
+          <t>Soumya Banerjee</t>
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>247.098</v>
+        <v>448.928</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>520.4000000000001</v>
+        <v>164.2</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>421.3</v>
+        <v>175</v>
       </c>
       <c r="E48" s="7">
         <f>SUM(B48:D48)</f>
@@ -4493,17 +4536,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Steven Wright</t>
+          <t>Stefano Pirandola</t>
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>188.776</v>
+        <v>273.348</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>452.2</v>
+        <v>520.4000000000001</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>175</v>
+        <v>421.3</v>
       </c>
       <c r="E49" s="7">
         <f>SUM(B49:D49)</f>
@@ -4513,17 +4556,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Steven Xiaotian Dai</t>
+          <t>Steven Wright</t>
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>254.186</v>
+        <v>224.776</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>350.3</v>
+        <v>452.2</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="E50" s="7">
         <f>SUM(B50:D50)</f>
@@ -4533,17 +4576,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Tommy Yuan</t>
+          <t>Steven Xiaotian Dai</t>
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>477.0133333333333</v>
+        <v>326.686</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>364.2</v>
+        <v>350.3</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>339.2</v>
+        <v>503.4</v>
       </c>
       <c r="E51" s="7">
         <f>SUM(B51:D51)</f>
@@ -4553,14 +4596,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Vasileios Vasilakis</t>
+          <t>Tommy Yuan</t>
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>269.894</v>
+        <v>608.5133333333333</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>356.2</v>
+        <v>364.2</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>339.2</v>
@@ -4573,17 +4616,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>William Smith</t>
+          <t>Vasileios Vasilakis</t>
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>275.976</v>
+        <v>300.394</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>676.2</v>
+        <v>356.2</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>298.15</v>
+        <v>339.2</v>
       </c>
       <c r="E53" s="7">
         <f>SUM(B53:D53)</f>
@@ -4593,17 +4636,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Xinwei Fang</t>
+          <t>William Smith</t>
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>374.288</v>
+        <v>346.976</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>244.2</v>
+        <v>676.2</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>257.1</v>
+        <v>298.15</v>
       </c>
       <c r="E54" s="7">
         <f>SUM(B54:D54)</f>
@@ -4613,17 +4656,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Yan Jia</t>
+          <t>Xinwei Fang</t>
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>105.736</v>
+        <v>405.038</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>638.7</v>
+        <v>244.2</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E55" s="7">
         <f>SUM(B55:D55)</f>
@@ -4633,20 +4676,40 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Yuchen Zhao</t>
+          <t>Yan Jia</t>
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>340.482</v>
+        <v>140.736</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>180.2</v>
+        <v>638.7</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="E56" s="7">
         <f>SUM(B56:D56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Yuchen Zhao</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>405.982</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>257.1</v>
+      </c>
+      <c r="E57" s="7">
+        <f>SUM(B57:D57)</f>
         <v/>
       </c>
     </row>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -960,10 +960,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1289.114</v>
+        <v>1291.256</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>341.514</v>
+        <v>343.656</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>444.2</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>815.104</v>
+        <v>811.76</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>207.704</v>
+        <v>204.36</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>268.2</v>
@@ -1101,10 +1101,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1060.72</v>
+        <v>1061.264</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>241.12</v>
+        <v>241.664</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>644.6000000000001</v>
@@ -1148,10 +1148,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1016.069333333333</v>
+        <v>1023.549333333333</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>408.6693333333333</v>
+        <v>416.1493333333333</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>268.2</v>
@@ -1242,10 +1242,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>658.284</v>
+        <v>659.9159999999999</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>236.984</v>
+        <v>238.616</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>164.2</v>
@@ -1571,10 +1571,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1339.486666666667</v>
+        <v>1340.030666666667</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>49.58666666666667</v>
+        <v>50.13066666666666</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>1114.9</v>
@@ -1665,10 +1665,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>456.63</v>
+        <v>458.16</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>69.43000000000001</v>
+        <v>70.96000000000001</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>212.2</v>
@@ -1806,10 +1806,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1443.11</v>
+        <v>1443.926</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>98.91</v>
+        <v>99.726</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>348.2</v>
@@ -1900,10 +1900,10 @@
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>967.84</v>
+        <v>972.532</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>546.54</v>
+        <v>551.232</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>164.2</v>
@@ -1994,10 +1994,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>850.5</v>
+        <v>855.498</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>343.3</v>
+        <v>348.298</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>332.2</v>
@@ -2041,10 +2041,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>982.354</v>
+        <v>985.0060000000001</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>294.954</v>
+        <v>297.606</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>348.2</v>
@@ -2088,10 +2088,10 @@
         <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>736.268</v>
+        <v>743</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>333.068</v>
+        <v>339.8</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>228.2</v>
@@ -2135,10 +2135,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1159.037333333333</v>
+        <v>1162.505333333333</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>443.4373333333333</v>
+        <v>446.9053333333333</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>212.2</v>
@@ -2229,10 +2229,10 @@
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1169.2</v>
+        <v>1169.744</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>363.5</v>
+        <v>364.044</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>548.6</v>
@@ -2323,10 +2323,10 @@
         <v>1</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>627.106</v>
+        <v>631.9000000000001</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>205.806</v>
+        <v>210.6</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>164.2</v>
@@ -2417,10 +2417,10 @@
         <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1607.921333333333</v>
+        <v>1609.757333333333</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>256.1213333333333</v>
+        <v>257.9573333333333</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1012.6</v>
@@ -2464,10 +2464,10 @@
         <v>1</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1291.884</v>
+        <v>1288.54</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>308.084</v>
+        <v>304.74</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>644.6</v>
@@ -2558,10 +2558,10 @@
         <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1117.43</v>
+        <v>1118.96</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>478.03</v>
+        <v>479.5600000000001</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>300.2</v>
@@ -2742,10 +2742,10 @@
         <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1221.13</v>
+        <v>1224.7</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>127.43</v>
+        <v>131</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>918.7</v>
@@ -2789,10 +2789,10 @@
         <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>798.284</v>
+        <v>799.9159999999999</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>224.984</v>
+        <v>226.616</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>398.3</v>
@@ -2883,10 +2883,10 @@
         <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1039.861333333333</v>
+        <v>1047.239333333333</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>596.6613333333333</v>
+        <v>604.0393333333334</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>268.2</v>
@@ -2930,10 +2930,10 @@
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>614.8573333333334</v>
+        <v>615.9793333333333</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>275.6573333333333</v>
+        <v>276.7793333333333</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>164.2</v>
@@ -2977,10 +2977,10 @@
         <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1191.638666666667</v>
+        <v>1193.406666666667</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>374.1386666666667</v>
+        <v>375.9066666666666</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>478.3</v>
@@ -3071,10 +3071,10 @@
         <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>788.1279999999999</v>
+        <v>784.7839999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>448.928</v>
+        <v>445.5839999999999</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>164.2</v>
@@ -3118,10 +3118,10 @@
         <v>1</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1215.048</v>
+        <v>1216.17</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>273.348</v>
+        <v>274.47</v>
       </c>
       <c r="E49" s="3" t="n">
         <v>520.4000000000001</v>
@@ -3165,10 +3165,10 @@
         <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>851.976</v>
+        <v>853.812</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>224.776</v>
+        <v>226.612</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>452.2</v>
@@ -3212,10 +3212,10 @@
         <v>1</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1180.386</v>
+        <v>1183.038</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>326.686</v>
+        <v>329.338</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>350.3</v>
@@ -3306,10 +3306,10 @@
         <v>1</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>995.7940000000001</v>
+        <v>998.854</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>300.394</v>
+        <v>303.454</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>356.2</v>
@@ -3353,10 +3353,10 @@
         <v>1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1321.326</v>
+        <v>1333.362</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>346.976</v>
+        <v>359.012</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>676.2</v>
@@ -3400,10 +3400,10 @@
         <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>906.3380000000001</v>
+        <v>909.908</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>405.038</v>
+        <v>408.608</v>
       </c>
       <c r="E55" s="3" t="n">
         <v>244.2</v>
@@ -3447,10 +3447,10 @@
         <v>1</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>954.436</v>
+        <v>961.78</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>140.736</v>
+        <v>148.08</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>638.7</v>
@@ -3494,10 +3494,10 @@
         <v>1</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>843.282</v>
+        <v>848.994</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>405.982</v>
+        <v>411.694</v>
       </c>
       <c r="E57" s="3" t="n">
         <v>180.2</v>
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>341.514</v>
+        <v>343.656</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>444.2</v>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>207.704</v>
+        <v>204.36</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>268.2</v>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>241.12</v>
+        <v>241.664</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>644.6000000000001</v>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>408.6693333333333</v>
+        <v>416.1493333333333</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>268.2</v>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>236.984</v>
+        <v>238.616</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>164.2</v>
@@ -3880,7 +3880,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>49.58666666666667</v>
+        <v>50.13066666666666</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>1114.9</v>
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>69.43000000000001</v>
+        <v>70.96000000000001</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>212.2</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>98.91</v>
+        <v>99.726</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>348.2</v>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>546.54</v>
+        <v>551.232</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>164.2</v>
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>343.3</v>
+        <v>348.298</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>332.2</v>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>294.954</v>
+        <v>297.606</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>348.2</v>
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>333.068</v>
+        <v>339.8</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>228.2</v>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>443.4373333333333</v>
+        <v>446.9053333333333</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>212.2</v>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>363.5</v>
+        <v>364.044</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>548.6</v>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>205.806</v>
+        <v>210.6</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>164.2</v>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>256.1213333333333</v>
+        <v>257.9573333333333</v>
       </c>
       <c r="C34" s="7" t="n">
         <v>1012.6</v>
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>308.084</v>
+        <v>304.74</v>
       </c>
       <c r="C35" s="7" t="n">
         <v>644.6</v>
@@ -4300,7 +4300,7 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>478.03</v>
+        <v>479.5600000000001</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>300.2</v>
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>127.43</v>
+        <v>131</v>
       </c>
       <c r="C41" s="7" t="n">
         <v>918.7</v>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>224.984</v>
+        <v>226.616</v>
       </c>
       <c r="C42" s="7" t="n">
         <v>398.3</v>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>596.6613333333333</v>
+        <v>604.0393333333334</v>
       </c>
       <c r="C44" s="7" t="n">
         <v>268.2</v>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>275.6573333333333</v>
+        <v>276.7793333333333</v>
       </c>
       <c r="C45" s="7" t="n">
         <v>164.2</v>
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>374.1386666666667</v>
+        <v>375.9066666666666</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>478.3</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>448.928</v>
+        <v>445.5839999999999</v>
       </c>
       <c r="C48" s="7" t="n">
         <v>164.2</v>
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>273.348</v>
+        <v>274.47</v>
       </c>
       <c r="C49" s="7" t="n">
         <v>520.4000000000001</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>224.776</v>
+        <v>226.612</v>
       </c>
       <c r="C50" s="7" t="n">
         <v>452.2</v>
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>326.686</v>
+        <v>329.338</v>
       </c>
       <c r="C51" s="7" t="n">
         <v>350.3</v>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>300.394</v>
+        <v>303.454</v>
       </c>
       <c r="C53" s="7" t="n">
         <v>356.2</v>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>346.976</v>
+        <v>359.012</v>
       </c>
       <c r="C54" s="7" t="n">
         <v>676.2</v>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>405.038</v>
+        <v>408.608</v>
       </c>
       <c r="C55" s="7" t="n">
         <v>244.2</v>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>140.736</v>
+        <v>148.08</v>
       </c>
       <c r="C56" s="7" t="n">
         <v>638.7</v>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>405.982</v>
+        <v>411.694</v>
       </c>
       <c r="C57" s="7" t="n">
         <v>180.2</v>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -913,10 +913,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1014.1</v>
+        <v>1014.3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>344.8</v>
+        <v>345</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>412.2</v>
@@ -960,10 +960,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1291.256</v>
+        <v>1291.3</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>343.656</v>
+        <v>343.7</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>444.2</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>811.76</v>
+        <v>812.2666666666667</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>204.36</v>
+        <v>204.8666666666667</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>268.2</v>
@@ -1054,10 +1054,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>872.8866666666667</v>
+        <v>873.6333333333333</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>451.5866666666667</v>
+        <v>452.3333333333333</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>164.2</v>
@@ -1101,10 +1101,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1061.264</v>
+        <v>1061.466666666667</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>241.664</v>
+        <v>241.8666666666666</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>644.6000000000001</v>
@@ -1148,10 +1148,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1023.549333333333</v>
+        <v>1023.633333333333</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>416.1493333333333</v>
+        <v>416.2333333333333</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>268.2</v>
@@ -1195,10 +1195,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1155.914</v>
+        <v>1156.65</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>529.364</v>
+        <v>530.1</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>164.2</v>
@@ -1242,10 +1242,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>659.9159999999999</v>
+        <v>660</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>238.616</v>
+        <v>238.7</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>164.2</v>
@@ -1289,10 +1289,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>663.6613333333333</v>
+        <v>664.0666666666666</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>212.4613333333333</v>
+        <v>212.8666666666667</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>276.2</v>
@@ -1336,10 +1336,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>978.5599999999999</v>
+        <v>978.76</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>223.8</v>
+        <v>224</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>579.76</v>
@@ -1383,10 +1383,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>749.6666666666667</v>
+        <v>750.0333333333333</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>410.4666666666667</v>
+        <v>410.8333333333333</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>164.2</v>
@@ -1430,10 +1430,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>775.8266666666666</v>
+        <v>776.7</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>436.6266666666667</v>
+        <v>437.5</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>164.2</v>
@@ -1477,10 +1477,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1112.058666666667</v>
+        <v>1112.9</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>348.4586666666667</v>
+        <v>349.3</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>260.2</v>
@@ -1524,10 +1524,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1256.2</v>
+        <v>1256.4</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>296.8</v>
+        <v>297</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>620.2</v>
@@ -1571,10 +1571,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1340.030666666667</v>
+        <v>1340.1</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>50.13066666666666</v>
+        <v>50.2</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>1114.9</v>
@@ -1618,10 +1618,10 @@
         <v>1</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>712.1453333333334</v>
+        <v>713</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>372.9453333333333</v>
+        <v>373.8</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>164.2</v>
@@ -1665,10 +1665,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>458.16</v>
+        <v>458.2</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>70.96000000000001</v>
+        <v>71</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>212.2</v>
@@ -1712,10 +1712,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2133.82</v>
+        <v>2134.02</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>82.3</v>
+        <v>82.5</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>1794.42</v>
@@ -1806,10 +1806,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1443.926</v>
+        <v>1444</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>99.726</v>
+        <v>99.8</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>348.2</v>
@@ -1853,10 +1853,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>930.6573333333333</v>
+        <v>931.4333333333334</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>345.1573333333333</v>
+        <v>345.9333333333333</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>246.3</v>
@@ -1900,10 +1900,10 @@
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>972.532</v>
+        <v>972.9</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>551.232</v>
+        <v>551.6</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>164.2</v>
@@ -1947,10 +1947,10 @@
         <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1485.261333333333</v>
+        <v>1485.666666666667</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>309.4613333333333</v>
+        <v>309.8666666666667</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>1000.8</v>
@@ -1994,10 +1994,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>855.498</v>
+        <v>855.5999999999999</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>348.298</v>
+        <v>348.4</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>332.2</v>
@@ -2041,10 +2041,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>985.0060000000001</v>
+        <v>985.1</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>297.606</v>
+        <v>297.7</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>348.2</v>
@@ -2135,10 +2135,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1162.505333333333</v>
+        <v>1162.933333333333</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>446.9053333333333</v>
+        <v>447.3333333333334</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>212.2</v>
@@ -2182,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1165.126666666667</v>
+        <v>1166</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>387.6266666666667</v>
+        <v>388.5</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>356.2</v>
@@ -2229,10 +2229,10 @@
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1169.744</v>
+        <v>1170.233333333333</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>364.044</v>
+        <v>364.5333333333333</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>548.6</v>
@@ -2276,10 +2276,10 @@
         <v>1</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>893.8866666666667</v>
+        <v>894.6333333333333</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>472.5866666666667</v>
+        <v>473.3333333333333</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>164.2</v>
@@ -2370,10 +2370,10 @@
         <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1468.557333333333</v>
+        <v>1468.933333333333</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>208.5573333333333</v>
+        <v>208.9333333333333</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>428.2</v>
@@ -2417,10 +2417,10 @@
         <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1609.757333333333</v>
+        <v>1610.133333333333</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>257.9573333333333</v>
+        <v>258.3333333333334</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1012.6</v>
@@ -2464,10 +2464,10 @@
         <v>1</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1288.54</v>
+        <v>1289</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>304.74</v>
+        <v>305.2</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>644.6</v>
@@ -2511,10 +2511,10 @@
         <v>1</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1397.213333333334</v>
+        <v>1397.58</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>225.6333333333333</v>
+        <v>226</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>996.5800000000002</v>
@@ -2558,10 +2558,10 @@
         <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1118.96</v>
+        <v>1119.4</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>479.5600000000001</v>
+        <v>480</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>300.2</v>
@@ -2648,10 +2648,10 @@
         <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1702.497333333333</v>
+        <v>1702.933333333333</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>250.4973333333333</v>
+        <v>250.9333333333333</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>1112.8</v>
@@ -2695,10 +2695,10 @@
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>921.4193333333334</v>
+        <v>922.4166666666666</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>395.0693333333334</v>
+        <v>396.0666666666667</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>228.2</v>
@@ -2789,10 +2789,10 @@
         <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>799.9159999999999</v>
+        <v>800</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>226.616</v>
+        <v>226.7</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>398.3</v>
@@ -2836,10 +2836,10 @@
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>758.8133333333333</v>
+        <v>759.3666666666666</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>419.6133333333333</v>
+        <v>420.1666666666666</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>164.2</v>
@@ -2883,10 +2883,10 @@
         <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1047.239333333333</v>
+        <v>1047.383333333333</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>604.0393333333334</v>
+        <v>604.1833333333334</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>268.2</v>
@@ -2930,10 +2930,10 @@
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>615.9793333333333</v>
+        <v>616.4833333333333</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>276.7793333333333</v>
+        <v>277.2833333333333</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>164.2</v>
@@ -2977,10 +2977,10 @@
         <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1193.406666666667</v>
+        <v>1193.866666666667</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>375.9066666666666</v>
+        <v>376.3666666666667</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>478.3</v>
@@ -3024,10 +3024,10 @@
         <v>1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>798.24</v>
+        <v>799.0333333333333</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>347.04</v>
+        <v>347.8333333333333</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>276.2</v>
@@ -3071,10 +3071,10 @@
         <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>784.7839999999999</v>
+        <v>785</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>445.5839999999999</v>
+        <v>445.8</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>164.2</v>
@@ -3118,10 +3118,10 @@
         <v>1</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1216.17</v>
+        <v>1216.25</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>274.47</v>
+        <v>274.55</v>
       </c>
       <c r="E49" s="3" t="n">
         <v>520.4000000000001</v>
@@ -3165,10 +3165,10 @@
         <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>853.812</v>
+        <v>853.9</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>226.612</v>
+        <v>226.7</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>452.2</v>
@@ -3212,10 +3212,10 @@
         <v>1</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1183.038</v>
+        <v>1183.2</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>329.338</v>
+        <v>329.5</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>350.3</v>
@@ -3259,10 +3259,10 @@
         <v>1</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1311.913333333333</v>
+        <v>1312.733333333333</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>608.5133333333333</v>
+        <v>609.3333333333333</v>
       </c>
       <c r="E52" s="3" t="n">
         <v>364.2</v>
@@ -3306,10 +3306,10 @@
         <v>1</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>998.854</v>
+        <v>999</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>303.454</v>
+        <v>303.6</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>356.2</v>
@@ -3353,10 +3353,10 @@
         <v>1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1333.362</v>
+        <v>1333.55</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>359.012</v>
+        <v>359.2</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>676.2</v>
@@ -3400,10 +3400,10 @@
         <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>909.908</v>
+        <v>910.5</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>408.608</v>
+        <v>409.2</v>
       </c>
       <c r="E55" s="3" t="n">
         <v>244.2</v>
@@ -3447,10 +3447,10 @@
         <v>1</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>961.78</v>
+        <v>961.8000000000001</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>148.08</v>
+        <v>148.1</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>638.7</v>
@@ -3494,10 +3494,10 @@
         <v>1</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>848.994</v>
+        <v>849.1999999999999</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>411.694</v>
+        <v>411.9</v>
       </c>
       <c r="E57" s="3" t="n">
         <v>180.2</v>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>344.8</v>
+        <v>345</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>412.2</v>
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>343.656</v>
+        <v>343.7</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>444.2</v>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>204.36</v>
+        <v>204.8666666666667</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>268.2</v>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>451.5866666666667</v>
+        <v>452.3333333333333</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>164.2</v>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>241.664</v>
+        <v>241.8666666666666</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>644.6000000000001</v>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>416.1493333333333</v>
+        <v>416.2333333333333</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>268.2</v>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>529.364</v>
+        <v>530.1</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>164.2</v>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>238.616</v>
+        <v>238.7</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>164.2</v>
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>212.4613333333333</v>
+        <v>212.8666666666667</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>276.2</v>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>223.8</v>
+        <v>224</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>579.76</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>410.4666666666667</v>
+        <v>410.8333333333333</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>164.2</v>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>436.6266666666667</v>
+        <v>437.5</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>164.2</v>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>348.4586666666667</v>
+        <v>349.3</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>260.2</v>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>296.8</v>
+        <v>297</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>620.2</v>
@@ -3880,7 +3880,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>50.13066666666666</v>
+        <v>50.2</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>1114.9</v>
@@ -3900,7 +3900,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>372.9453333333333</v>
+        <v>373.8</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>164.2</v>
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>70.96000000000001</v>
+        <v>71</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>212.2</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>82.3</v>
+        <v>82.5</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>1794.42</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>99.726</v>
+        <v>99.8</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>348.2</v>
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>345.1573333333333</v>
+        <v>345.9333333333333</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>246.3</v>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>551.232</v>
+        <v>551.6</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>164.2</v>
@@ -4040,7 +4040,7 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>309.4613333333333</v>
+        <v>309.8666666666667</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>1000.8</v>
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>348.298</v>
+        <v>348.4</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>332.2</v>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>297.606</v>
+        <v>297.7</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>348.2</v>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>446.9053333333333</v>
+        <v>447.3333333333334</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>212.2</v>
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>387.6266666666667</v>
+        <v>388.5</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>356.2</v>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>364.044</v>
+        <v>364.5333333333333</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>548.6</v>
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>472.5866666666667</v>
+        <v>473.3333333333333</v>
       </c>
       <c r="C31" s="7" t="n">
         <v>164.2</v>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>208.5573333333333</v>
+        <v>208.9333333333333</v>
       </c>
       <c r="C33" s="7" t="n">
         <v>428.2</v>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>257.9573333333333</v>
+        <v>258.3333333333334</v>
       </c>
       <c r="C34" s="7" t="n">
         <v>1012.6</v>
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>304.74</v>
+        <v>305.2</v>
       </c>
       <c r="C35" s="7" t="n">
         <v>644.6</v>
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>225.6333333333333</v>
+        <v>226</v>
       </c>
       <c r="C36" s="7" t="n">
         <v>996.5800000000002</v>
@@ -4300,7 +4300,7 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>479.5600000000001</v>
+        <v>480</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>300.2</v>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>250.4973333333333</v>
+        <v>250.9333333333333</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>1112.8</v>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>395.0693333333334</v>
+        <v>396.0666666666667</v>
       </c>
       <c r="C40" s="7" t="n">
         <v>228.2</v>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>226.616</v>
+        <v>226.7</v>
       </c>
       <c r="C42" s="7" t="n">
         <v>398.3</v>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>419.6133333333333</v>
+        <v>420.1666666666666</v>
       </c>
       <c r="C43" s="7" t="n">
         <v>164.2</v>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>604.0393333333334</v>
+        <v>604.1833333333334</v>
       </c>
       <c r="C44" s="7" t="n">
         <v>268.2</v>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>276.7793333333333</v>
+        <v>277.2833333333333</v>
       </c>
       <c r="C45" s="7" t="n">
         <v>164.2</v>
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>375.9066666666666</v>
+        <v>376.3666666666667</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>478.3</v>
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>347.04</v>
+        <v>347.8333333333333</v>
       </c>
       <c r="C47" s="7" t="n">
         <v>276.2</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>445.5839999999999</v>
+        <v>445.8</v>
       </c>
       <c r="C48" s="7" t="n">
         <v>164.2</v>
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>274.47</v>
+        <v>274.55</v>
       </c>
       <c r="C49" s="7" t="n">
         <v>520.4000000000001</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>226.612</v>
+        <v>226.7</v>
       </c>
       <c r="C50" s="7" t="n">
         <v>452.2</v>
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>329.338</v>
+        <v>329.5</v>
       </c>
       <c r="C51" s="7" t="n">
         <v>350.3</v>
@@ -4600,7 +4600,7 @@
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>608.5133333333333</v>
+        <v>609.3333333333333</v>
       </c>
       <c r="C52" s="7" t="n">
         <v>364.2</v>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>303.454</v>
+        <v>303.6</v>
       </c>
       <c r="C53" s="7" t="n">
         <v>356.2</v>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>359.012</v>
+        <v>359.2</v>
       </c>
       <c r="C54" s="7" t="n">
         <v>676.2</v>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>408.608</v>
+        <v>409.2</v>
       </c>
       <c r="C55" s="7" t="n">
         <v>244.2</v>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>148.08</v>
+        <v>148.1</v>
       </c>
       <c r="C56" s="7" t="n">
         <v>638.7</v>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>411.694</v>
+        <v>411.9</v>
       </c>
       <c r="C57" s="7" t="n">
         <v>180.2</v>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -1524,7 +1524,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1256.4</v>
+        <v>1420.6</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>297</v>
@@ -1533,7 +1533,7 @@
         <v>620.2</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>339.2</v>
+        <v>503.4</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Ethics Committee Member: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Ethics Committee Member: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -3866,7 +3866,7 @@
         <v>620.2</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>339.2</v>
+        <v>503.4</v>
       </c>
       <c r="E15" s="7">
         <f>SUM(B15:D15)</f>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -2111,7 +2111,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>ECR rep: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>ECR representative: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -1759,10 +1759,10 @@
         <v>1</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2435.6</v>
+        <v>2405.6</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>588.6</v>
@@ -1770,11 +1770,7 @@
       <c r="F20" s="3" t="n">
         <v>1817</v>
       </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Minimum administrative teaching load (from workload_parameters.yaml): 30h</t>
-        </is>
-      </c>
+      <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
           <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h; Grant SCHEME: 20% of 1642h = 328.4h</t>
@@ -3960,7 +3956,7 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C20" s="7" t="n">
         <v>588.6</v>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -2413,10 +2413,10 @@
         <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1610.133333333333</v>
+        <v>1626.133333333333</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>258.3333333333334</v>
+        <v>274.3333333333334</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1012.6</v>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>GODS (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HCIN (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>GODS (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HCIN (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>258.3333333333334</v>
+        <v>274.3333333333334</v>
       </c>
       <c r="C34" s="7" t="n">
         <v>1012.6</v>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -1849,10 +1849,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>931.4333333333334</v>
+        <v>821.4333333333334</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>345.9333333333333</v>
+        <v>235.9333333333333</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>246.3</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Jacob Rigby: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Projects (40cr): Jacob Rigby: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>HCIN (20cr): Jacob Rigby: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2554,10 +2554,10 @@
         <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1119.4</v>
+        <v>1108.4</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>300.2</v>
@@ -3255,10 +3255,10 @@
         <v>1</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1312.733333333333</v>
+        <v>1301.733333333333</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>609.3333333333333</v>
+        <v>598.3333333333333</v>
       </c>
       <c r="E52" s="3" t="n">
         <v>364.2</v>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>345.9333333333333</v>
+        <v>235.9333333333333</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>246.3</v>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>300.2</v>
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>609.3333333333333</v>
+        <v>598.3333333333333</v>
       </c>
       <c r="C52" s="7" t="n">
         <v>364.2</v>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -946,7 +946,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NLPG: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>No administrative roles assigned; ELLA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>No administrative roles assigned; LPTC: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NLPG: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>LLMA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>LLMA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ARIA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>No administrative roles assigned; ELLA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>No administrative roles assigned; ELLA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ARIA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
     </row>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -830,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -844,6 +844,7 @@
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,6 +903,11 @@
           <t>Missing Data</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Manual Adjustments</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -949,6 +955,11 @@
           <t>NLPG: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -996,6 +1007,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1043,6 +1059,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1090,6 +1111,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1137,6 +1163,11 @@
           <t>No administrative roles assigned; ELLA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1184,6 +1215,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1231,6 +1267,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1278,6 +1319,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1325,6 +1371,11 @@
           <t>No administrative roles assigned</t>
         </is>
       </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1372,6 +1423,11 @@
           <t>No administrative roles assigned; LPTC: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1419,6 +1475,11 @@
           <t>No administrative roles assigned</t>
         </is>
       </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1466,6 +1527,11 @@
           <t>No administrative roles assigned</t>
         </is>
       </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1513,6 +1579,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1560,6 +1631,11 @@
           <t>NLPG: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1607,6 +1683,11 @@
           <t>No administrative roles assigned</t>
         </is>
       </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1654,6 +1735,11 @@
           <t>No administrative roles assigned</t>
         </is>
       </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1701,6 +1787,11 @@
           <t>No administrative roles assigned</t>
         </is>
       </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1748,6 +1839,11 @@
           <t>LLMA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1791,6 +1887,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1838,6 +1939,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1885,6 +1991,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1932,6 +2043,11 @@
           <t>LLMA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1979,6 +2095,11 @@
           <t>No administrative roles assigned</t>
         </is>
       </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2026,6 +2147,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2073,6 +2199,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2120,6 +2251,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2167,6 +2303,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2214,6 +2355,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2261,6 +2407,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2308,6 +2459,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2355,6 +2511,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2402,6 +2563,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2449,6 +2615,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2496,6 +2667,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2543,6 +2719,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2590,6 +2771,11 @@
           <t>ARIA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2633,6 +2819,11 @@
           <t>No administrative roles assigned</t>
         </is>
       </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2680,6 +2871,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2727,6 +2923,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2774,6 +2975,11 @@
           <t>No administrative roles assigned</t>
         </is>
       </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2821,6 +3027,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2868,6 +3079,11 @@
           <t>No administrative roles assigned; ELLA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2915,6 +3131,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2962,6 +3183,11 @@
           <t>No administrative roles assigned</t>
         </is>
       </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3009,6 +3235,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3056,6 +3287,11 @@
           <t>No administrative roles assigned</t>
         </is>
       </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3103,6 +3339,11 @@
           <t>No administrative roles assigned; ELLA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3150,6 +3391,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3197,6 +3443,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3244,6 +3495,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3291,6 +3547,11 @@
           <t>ARIA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3338,6 +3599,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3385,6 +3651,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3432,6 +3703,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3479,6 +3755,11 @@
           <t>No administrative roles assigned</t>
         </is>
       </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3522,6 +3803,11 @@
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -919,10 +919,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1014.3</v>
+        <v>1096.8</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>345</v>
+        <v>427.5</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>412.2</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Adrian Bors: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
+          <t>NLPG (20cr): Adrian Bors: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - 5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -1127,10 +1127,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1061.466666666667</v>
+        <v>1134.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>241.8666666666666</v>
+        <v>315.2</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>644.6000000000001</v>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>ELLA (20cr): Antonio Garcia-Dominguez: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Robbert Jongeling: 5x, Antonio Garcia-Dominguez: 2.5x, Soumya Banerjee: 5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ENG2 (20cr): Antonio Garcia-Dominguez: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>ELLA (20cr): Antonio Garcia-Dominguez: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Robbert Jongeling: 7.5x, Antonio Garcia-Dominguez: 5x, Soumya Banerjee: 7.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ENG2 (20cr): Antonio Garcia-Dominguez: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -1595,10 +1595,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1420.6</v>
+        <v>1503.1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>297</v>
+        <v>379.5</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>620.2</v>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Dimitar Kazakov: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>NLPG (20cr): Dimitar Kazakov: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - 5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1803,10 +1803,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2134.02</v>
+        <v>2189.02</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>82.5</v>
+        <v>137.5</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>1794.42</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>LLMA (20cr): Frank Soboczenski: Standard (2.5x): 0.0h/teacher @ 2.5x; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
+          <t>LLMA (20cr): Frank Soboczenski: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -2007,10 +2007,10 @@
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>972.9</v>
+        <v>1027.9</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>551.6</v>
+        <v>606.6</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>164.2</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>DEEP (20cr): James Stovold: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, James Stovold: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; LLMA (20cr): James Stovold: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DEEP (20cr): James Stovold: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, James Stovold: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; LLMA (20cr): James Stovold: New lecturer + new content (7.5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -3043,10 +3043,10 @@
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>759.3666666666666</v>
+        <v>832.7</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>420.1666666666666</v>
+        <v>493.5</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>164.2</v>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>ELLA (20cr): Robbert Jongeling: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Robbert Jongeling: 5x, Antonio Garcia-Dominguez: 2.5x, Soumya Banerjee: 5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ENG1 (20cr): Robbert Jongeling: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Kostas Barmpis: 2.5x, Robbert Jongeling: 5x, Tommy Yuan: 2.5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 2 students x 3h = 6.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>ELLA (20cr): Robbert Jongeling: New lecturer + new content (7.5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Robbert Jongeling: 7.5x, Antonio Garcia-Dominguez: 5x, Soumya Banerjee: 7.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ENG1 (20cr): Robbert Jongeling: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Kostas Barmpis: 2.5x, Robbert Jongeling: 5x, Tommy Yuan: 2.5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 2 students x 3h = 6.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3303,10 +3303,10 @@
         <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>785</v>
+        <v>858.3333333333333</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>445.8</v>
+        <v>519.1333333333333</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>164.2</v>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): Soumya Banerjee: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ELLA (20cr): Soumya Banerjee: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Robbert Jongeling: 5x, Antonio Garcia-Dominguez: 2.5x, Soumya Banerjee: 5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>AURO (20cr): Soumya Banerjee: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ELLA (20cr): Soumya Banerjee: New lecturer + new content (7.5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Robbert Jongeling: 7.5x, Antonio Garcia-Dominguez: 5x, Soumya Banerjee: 7.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>345</v>
+        <v>427.5</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>412.2</v>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>241.8666666666666</v>
+        <v>315.2</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>644.6000000000001</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>297</v>
+        <v>379.5</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>620.2</v>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>82.5</v>
+        <v>137.5</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>1794.42</v>
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>551.6</v>
+        <v>606.6</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>164.2</v>
@@ -4702,7 +4702,7 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>420.1666666666666</v>
+        <v>493.5</v>
       </c>
       <c r="C43" s="7" t="n">
         <v>164.2</v>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>445.8</v>
+        <v>519.1333333333333</v>
       </c>
       <c r="C48" s="7" t="n">
         <v>164.2</v>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -195,12 +195,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Staff Workload'!$A$2:$A$57</f>
+              <f>'Staff Workload'!$A$2:$A$66</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Staff Workload'!$D$2:$D$57</f>
+              <f>'Staff Workload'!$D$2:$D$66</f>
             </numRef>
           </val>
         </ser>
@@ -219,12 +219,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Staff Workload'!$A$2:$A$57</f>
+              <f>'Staff Workload'!$A$2:$A$66</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Staff Workload'!$E$2:$E$57</f>
+              <f>'Staff Workload'!$E$2:$E$66</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +243,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Staff Workload'!$A$2:$A$57</f>
+              <f>'Staff Workload'!$A$2:$A$66</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Staff Workload'!$F$2:$F$57</f>
+              <f>'Staff Workload'!$F$2:$F$66</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Detailed Breakdown'!$A$2:$A$57</f>
+              <f>'Detailed Breakdown'!$A$2:$A$66</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Detailed Breakdown'!$B$2:$B$57</f>
+              <f>'Detailed Breakdown'!$B$2:$B$66</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Detailed Breakdown'!$A$2:$A$57</f>
+              <f>'Detailed Breakdown'!$A$2:$A$66</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Detailed Breakdown'!$C$2:$C$57</f>
+              <f>'Detailed Breakdown'!$C$2:$C$66</f>
             </numRef>
           </val>
         </ser>
@@ -408,12 +408,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Detailed Breakdown'!$A$2:$A$57</f>
+              <f>'Detailed Breakdown'!$A$2:$A$66</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Detailed Breakdown'!$D$2:$D$57</f>
+              <f>'Detailed Breakdown'!$D$2:$D$66</f>
             </numRef>
           </val>
         </ser>
@@ -830,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -971,10 +971,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1291.3</v>
+        <v>1298.6</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>343.7</v>
+        <v>351</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>444.2</v>
@@ -1023,10 +1023,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>812.2666666666667</v>
+        <v>911.2333333333333</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>204.8666666666667</v>
+        <v>303.8333333333333</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>268.2</v>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; THE2 (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>ARIA (20cr): Alvaro Miyazawa: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; AURO (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; THE2 (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ARIA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -1068,42 +1068,38 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Andrew Pomfret</t>
+          <t>Ana Cavalcanti</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>873.6333333333333</v>
+        <v>887.4000000000001</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>452.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>164.2</v>
+        <v>548.2</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>257.1</v>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>SYS1 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 11 students x 3h = 33.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
-        </is>
-      </c>
+        <v>339.2</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 8x part-time PhD student × 48h/FTE = 384.0h</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Invalid FTE value for grant: '?'; Invalid FTE value for grant: '?'</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -1120,37 +1116,37 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Antonio Garcia-Dominguez</t>
+          <t>Andrew Pomfret</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1134.8</v>
+        <v>880.9333333333333</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>315.2</v>
+        <v>459.6333333333333</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>644.6000000000001</v>
+        <v>164.2</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>ELLA (20cr): Antonio Garcia-Dominguez: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Robbert Jongeling: 7.5x, Antonio Garcia-Dominguez: 5x, Soumya Banerjee: 7.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ENG2 (20cr): Antonio Garcia-Dominguez: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>SYS1 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 11 students x 3h = 33.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -1160,7 +1156,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned; ELLA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -1172,37 +1168,37 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Carlo Ottaviani</t>
+          <t>Antonio Garcia-Dominguez</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1023.633333333333</v>
+        <v>1176.9</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>416.2333333333333</v>
+        <v>357.3</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>268.2</v>
+        <v>644.6000000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; PRAD (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>ELLA (20cr): Antonio Garcia-Dominguez: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Antonio Garcia-Dominguez: 5x, &lt;new hire&gt;: 7.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; ENG2 (20cr): Antonio Garcia-Dominguez: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x assessor (8h each) = 104.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -1212,7 +1208,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned; ELLA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
@@ -1224,37 +1220,37 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Christopher Crispin-Bailey</t>
+          <t>Carlo Ottaviani</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1156.65</v>
+        <v>1030.933333333333</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>530.1</v>
+        <v>423.5333333333333</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>164.2</v>
+        <v>268.2</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>462.35</v>
+        <v>339.2</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>SYS2 (20cr): Christopher Crispin-Bailey: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS3 (20cr): Christopher Crispin-Bailey: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Pengcheng Liu: 2.5x, Christopher Crispin-Bailey: 2.5x, Da Li: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CTAP (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; PRAD (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>GTA Coordinator: 10% of 1642h = 164.2h; Union: 8% of 1642h = 123.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -1276,27 +1272,27 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Claire Ingram</t>
+          <t>Christopher Crispin-Bailey</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>660</v>
+        <v>1219.65</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>238.7</v>
+        <v>593.1</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>164.2</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>257.1</v>
+        <v>462.35</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Claire Ingram: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 1 students x 3h = 3.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
+          <t>SYS2 (20cr): Christopher Crispin-Bailey: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS3 (20cr): Christopher Crispin-Bailey: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1306,7 +1302,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Outreach and Extra-Curricular Activities: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>GTA Coordinator: 10% of 1642h = 164.2h; Union: 8% of 1642h = 123.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -1328,37 +1324,37 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Claudio Guarnera</t>
+          <t>Claire Ingram</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>664.0666666666666</v>
+        <v>820.9</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>212.8666666666667</v>
+        <v>399.6</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>276.2</v>
+        <v>164.2</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Claudio Guarnera: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>HINT (20cr): Claire Ingram: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; REMS (20cr): Claire Ingram: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 1 students x 3h = 3.0h; Projects: 10 projects x MSc (24h) = 240.0h</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Outreach and Extra-Curricular Activities: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -1368,7 +1364,7 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
@@ -1380,37 +1376,37 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Colin Paterson</t>
+          <t>Claudio Guarnera</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>978.76</v>
+        <v>460.5466666666667</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>224</v>
+        <v>212.8666666666667</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>579.76</v>
+        <v>177.68</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>175</v>
+        <v>70</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>LPTC (20cr): Colin Paterson: Standard (2.5x): 0.0h/teacher @ 2.5x; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
+          <t>IMLO (20cr): Claudio Guarnera: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 120.0h; Grant KTP with Advai (Industry): 3% of 1642h = 49.3h; Grant KTP with Advai: 5% of 1642h = 82.1h; Grant A STAR TO STEER BY: 5% of 1642h = 82.1h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 40.0h; Personal development: 30.0h (FTE: 0.40)</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1420,7 +1416,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned; LPTC: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
@@ -1432,32 +1428,32 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Da Li</t>
+          <t>Colin Paterson</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>750.0333333333333</v>
+        <v>1156.16</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>410.8333333333333</v>
+        <v>401.4</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>164.2</v>
+        <v>579.76</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): Da Li: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Pengcheng Liu: 2.5x, Christopher Crispin-Bailey: 2.5x, Da Li: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>LPTC (20cr): Colin Paterson: Standard (2.5x): 0.0h/teacher @ 2.5x; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ROCS (20cr): Colin Paterson: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 120.0h; Grant KTP with Advai (Industry): 3% of 1642h = 49.3h; Grant KTP with Advai: 5% of 1642h = 82.1h; Grant A STAR TO STEER BY: 5% of 1642h = 82.1h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1472,7 +1468,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>No administrative roles assigned; LPTC: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
@@ -1484,17 +1480,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Dawn H Wood</t>
+          <t>Da Li</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>776.7</v>
+        <v>657.0333333333333</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>437.5</v>
+        <v>317.8333333333334</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>164.2</v>
@@ -1504,7 +1500,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>LLMA (20cr): Da Li: New lecturer + new content (7.5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1524,7 +1520,7 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>No administrative roles assigned; LLMA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
@@ -1536,37 +1532,37 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Detlef Plump</t>
+          <t>David Pumfrey</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1112.9</v>
+        <v>265.7</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>349.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>260.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>503.4</v>
+        <v>87.5</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>THE2 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Detlef Plump: 2.5x, Simon Foster: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HRAS (10cr): David Pumfrey: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; HUFS (10cr): David Pumfrey: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>EC Officer (on-campus): 15% of 1642h = 246.3h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 50.0h; Personal development: 37.5h (FTE: 0.50)</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1576,7 +1572,7 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -1588,37 +1584,37 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Dimitar Kazakov</t>
+          <t>Dawn H Wood</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1503.1</v>
+        <v>784</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>379.5</v>
+        <v>444.8</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>620.2</v>
+        <v>164.2</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Dimitar Kazakov: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - 5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SOF1 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 5x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Ethics Committee Member: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1628,7 +1624,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>NLPG: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -1640,37 +1636,37 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Dimitris Kolovos</t>
+          <t>Detlef Plump</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1340.1</v>
+        <v>1168.983333333333</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>50.2</v>
+        <v>405.3833333333333</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1114.9</v>
+        <v>260.2</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>ENG2 (20cr): Dimitris Kolovos: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h</t>
+          <t>THE2 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 376.0h; Grant Socially-Acceptable and Trustworthy Human-Robot Teaming for Agile Industries (SYMPHONY Resubmission): 5% of 1642h = 82.1h; Grant MOSAICO: 5% of 1642h = 82.1h; Grant SCHEME: 20% of 1642h = 328.4h; Grant Cavecore: Doctoral Network on Continuous, Automated Validation, and Evaluation of Cognitive Robots in Open-Ended Environments: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>EC Officer (on-campus): 15% of 1642h = 246.3h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1680,7 +1676,7 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -1692,37 +1688,37 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Fang Yan</t>
+          <t>Dimitar Kazakov</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>713</v>
+        <v>1510.4</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>373.8</v>
+        <v>386.8</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>164.2</v>
+        <v>620.2</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>SOF2 (20cr): Fang Yan: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; THE3 (20cr): Fang Yan: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Detlef Plump: 2.5x, Simon Foster: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>NLPG (20cr): Dimitar Kazakov: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - 5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 5x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Ethics Committee Member: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1732,7 +1728,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>NLPG: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
@@ -1744,37 +1740,37 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Felix Ulrich-Oltean</t>
+          <t>Dimitris Kolovos</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>458.2</v>
+        <v>1537.14</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>71</v>
+        <v>50.2</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>212.2</v>
+        <v>1114.9</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>175</v>
+        <v>372.04</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>SAIL (20cr): Felix Ulrich-Oltean: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
+          <t>ENG2 (20cr): Dimitris Kolovos: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 376.0h; Grant Socially-Acceptable and Trustworthy Human-Robot Teaming for Agile Industries (SYMPHONY Resubmission): 5% of 1642h = 82.1h; Grant MOSAICO: 5% of 1642h = 82.1h; Grant SCHEME: 20% of 1642h = 328.4h; Grant Cavecore: Doctoral Network on Continuous, Automated Validation, and Evaluation of Cognitive Robots in Open-Ended Environments: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Research Group Leader: 10% of 1642h = 164.2h; Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1784,7 +1780,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -1796,37 +1792,37 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Frank Soboczenski</t>
+          <t>Fang Yan</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2189.02</v>
+        <v>553.5999999999999</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>137.5</v>
+        <v>214.4</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1794.42</v>
+        <v>164.2</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>LLMA (20cr): Frank Soboczenski: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
+          <t>SOF2 (20cr): Fang Yan: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 11% of 1642h = 180.6h; Grant Alan Turing AI Fellowship: 80% of 1642h = 1313.6h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1836,7 +1832,7 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>LLMA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
@@ -1848,33 +1844,37 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Iain Bate</t>
+          <t>Felix Ulrich-Oltean</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2405.6</v>
+        <v>458.2</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>588.6</v>
+        <v>212.2</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1817</v>
-      </c>
-      <c r="G20" s="4" t="inlineStr"/>
+        <v>175</v>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>SAIL (20cr): Felix Ulrich-Oltean: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
+        </is>
+      </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h; Grant SCHEME: 20% of 1642h = 328.4h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Head of Department: 100% of 1642h = 1642.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -1896,37 +1896,37 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Ian Gray</t>
+          <t>Frank Soboczenski</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1444</v>
+        <v>2143.186666666667</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>99.8</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>348.2</v>
+        <v>1794.42</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>996</v>
+        <v>257.1</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>EMBS (20cr): Ian Gray: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
+          <t>LLMA (20cr): Frank Soboczenski: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 11% of 1642h = 180.6h; Grant Alan Turing AI Fellowship: 80% of 1642h = 1313.6h</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Deputy Head of Department (On-campus teaching): 50% of 1642h = 821.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>LLMA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
@@ -1948,37 +1948,37 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Jacob Rigby</t>
+          <t>Iain Bate</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>821.4333333333334</v>
+        <v>2435.6</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>235.9333333333333</v>
+        <v>30</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>246.3</v>
+        <v>588.6</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>339.2</v>
+        <v>1817</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Jacob Rigby: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>; Pastoral: 10 students x 3h = 30.0h</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Grant EPSRC: Addressing environmental injustices through transdisciplinary science and technology: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h; Grant SCHEME: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Taught Project Coordinator: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Head of Department: 100% of 1642h = 1642.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -2000,37 +2000,37 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>James Stovold</t>
+          <t>Ian Gray</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1027.9</v>
+        <v>1444</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>606.6</v>
+        <v>99.8</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>164.2</v>
+        <v>348.2</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>257.1</v>
+        <v>996</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>DEEP (20cr): James Stovold: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, James Stovold: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; LLMA (20cr): James Stovold: New lecturer + new content (7.5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>EMBS (20cr): Ian Gray: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Head of Department (On-campus teaching): 50% of 1642h = 821.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>LLMA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -2052,37 +2052,37 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>James Walker</t>
+          <t>Jacob Rigby</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1485.666666666667</v>
+        <v>828.7333333333333</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>309.8666666666667</v>
+        <v>243.2333333333333</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1000.8</v>
+        <v>246.3</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): James Walker: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HCIN (20cr): Jacob Rigby: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h; Grant Smart Data Donation Service (SDDS): 10% of 1642h = 164.2h; Grant IGGI: 20% of 1642h = 328.4h</t>
+          <t>Grant EPSRC: Addressing environmental injustices through transdisciplinary science and technology: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Taught Project Coordinator: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
@@ -2104,37 +2104,37 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Jen Beeston</t>
+          <t>James Stovold</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>855.5999999999999</v>
+        <v>828.8000000000001</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>348.4</v>
+        <v>407.5</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>332.2</v>
+        <v>164.2</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>QUAL (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; TECC (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>IMLO (20cr): James Stovold: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 168.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Chair of the Department Education Committee: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -2156,37 +2156,37 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Jo Iacovides</t>
+          <t>James Walker</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>985.1</v>
+        <v>1485.666666666667</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>297.7</v>
+        <v>309.8666666666667</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>348.2</v>
+        <v>1000.8</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>PLEI (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; QUAL (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IMLO (20cr): James Walker: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 184.0h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h; Grant Smart Data Donation Service (SDDS): 10% of 1642h = 164.2h; Grant IGGI: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -2208,37 +2208,37 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Joe Cutting</t>
+          <t>Jen Beeston</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>743</v>
+        <v>1355.5</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>339.8</v>
+        <v>355.7</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>228.2</v>
+        <v>332.2</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>175</v>
+        <v>667.5999999999999</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PRAD (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>QUAL (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; TECC (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 168.0h</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>ECR representative: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>DEC Chair: 30% of 1642h = 492.6h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -2260,37 +2260,37 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Katrina Attwood</t>
+          <t>Jo Iacovides</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1162.933333333333</v>
+        <v>985.1</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>447.3333333333334</v>
+        <v>297.7</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>212.2</v>
+        <v>348.2</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>503.4</v>
+        <v>339.2</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; TECC (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>PLEI (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; QUAL (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 184.0h</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Director of Students: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -2312,37 +2312,37 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Kofi Appiah</t>
+          <t>Joe Cutting</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1166</v>
+        <v>750.3</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>388.5</v>
+        <v>347.1</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>356.2</v>
+        <v>228.2</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>421.3</v>
+        <v>175</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>IDEV (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PRAD (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Deputy Director of Admissions (UG Admissions): 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>ECR representative: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -2364,37 +2364,33 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Kostas Barmpis</t>
+          <t>John McDermid</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1170.233333333333</v>
+        <v>1878.9</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>364.5333333333333</v>
+        <v>0</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>548.6</v>
+        <v>1539.7</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>257.1</v>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>ENG1 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Kostas Barmpis: 2.5x, Robbert Jongeling: 5x, Tommy Yuan: 2.5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; ENG2 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
-        </is>
-      </c>
+        <v>339.2</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE = 144.0h; Grant Assessment of DSTA USVs and Continual Assurance of CI/CD for USVs: 5% of 1642h = 82.1h; Grant RAI UK: Safety &amp; Security Network (SSAIN): 20% of 1642h = 328.4h; Grant The Centre for Assuring Autonomy: 50% of 1642h = 821.0h</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>PhD Training Officer: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -2416,37 +2412,37 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Mike Freeman</t>
+          <t>Katrina Attwood</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>894.6333333333333</v>
+        <v>1170.233333333333</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>473.3333333333333</v>
+        <v>454.6333333333333</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>164.2</v>
+        <v>212.2</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>257.1</v>
+        <v>503.4</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>HCIN (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; TECC (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Director of Students: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -2468,37 +2464,37 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Mike O'Dea</t>
+          <t>Kofi Appiah</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>631.9000000000001</v>
+        <v>1173.3</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>210.6</v>
+        <v>395.8</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>164.2</v>
+        <v>356.2</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>257.1</v>
+        <v>421.3</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; GODS (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
+          <t>SOF1 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Director of Admissions (UG Admissions): 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -2520,37 +2516,37 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Nick Pears</t>
+          <t>Kostas Barmpis</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1468.933333333333</v>
+        <v>1234.7</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>208.9333333333333</v>
+        <v>429</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>428.2</v>
+        <v>548.6</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>831.8000000000001</v>
+        <v>257.1</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Nick Pears: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>ENG1 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; ENG2 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 264.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Deputy Head (Research): 40% of 1642h = 656.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>PGR Training Officer: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -2572,37 +2568,37 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Paul Cairns</t>
+          <t>Mark Nicholson</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1626.133333333333</v>
+        <v>734.6039999999999</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>274.3333333333334</v>
+        <v>314.7</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1012.6</v>
+        <v>227.36</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>339.2</v>
+        <v>192.544</v>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>GODS (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HCIN (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>RASS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SSAS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 8 projects x MSc (24h) = 192.0h</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h; Grant BiB Centre for Social Change: 0% of 1642h = 0.0h; Grant IGGI: 20% of 1642h = 328.4h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE = 96.0h</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; REF Lead: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>StAMP committee: 4% of 1314h = 52.5h; Engagement (email/meetings): 80.0h; Personal development: 60.0h (FTE: 0.80)</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -2624,37 +2620,37 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ribeiro</t>
+          <t>Mark Sujan</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1289</v>
+        <v>318.76</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>305.2</v>
+        <v>47.4</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>644.6</v>
+        <v>131.36</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>339.2</v>
+        <v>140</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS1 (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>HUFS (10cr): Mark Sujan: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 20% of 1642h = 328.4h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 80.0h; Personal development: 60.0h (FTE: 0.80)</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
@@ -2664,7 +2660,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -2676,37 +2672,37 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Pengcheng Liu</t>
+          <t>Mike Freeman</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1397.58</v>
+        <v>901.9333333333333</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>226</v>
+        <v>480.6333333333333</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>996.5800000000002</v>
+        <v>164.2</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): Pengcheng Liu: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Pengcheng Liu: 2.5x, Christopher Crispin-Bailey: 2.5x, Da Li: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>SYS1 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Intelligent Dependable Environment Control for Sustainable Aquaculture: 20% of 1642h = 328.4h; Grant Establishing a Safe AI Research Hub: York–UTM–UTB Twin-Lab Initiative: 9% of 1642h = 147.8h; Grant Establishment of Korea–UK Collaboration Platform for Convergent Research in Quantum Photonics and Artificial Intelligence - Yr2: 5% of 1642h = 82.1h; Grant SCHEME: 5% of 1642h = 82.1h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Graduate School Board (GSB) Chair: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -2728,37 +2724,37 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Peter Nightingale</t>
+          <t>Mike O'Dea</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1108.4</v>
+        <v>816.6</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>469</v>
+        <v>395.3</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>300.2</v>
+        <v>164.2</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>ARIA (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; FOAM (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SAIL (20cr): Peter Nightingale: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>CBDA (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; GODS (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ROCS (20cr): Mike O'Dea: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>UG PL: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -2768,7 +2764,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>ARIA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -2780,33 +2776,37 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Phoebe</t>
+          <t>Nick Pears</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>339.2</v>
+        <v>1468.933333333333</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0</v>
+        <v>208.9333333333333</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>164.2</v>
+        <v>428.2</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="G38" s="4" t="inlineStr"/>
+        <v>831.8000000000001</v>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>THE1 (20cr): Nick Pears: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+        </is>
+      </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 264.0h</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Head (Research): 40% of 1642h = 656.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -2828,37 +2828,37 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Poonam Yadav</t>
+          <t>Oleg Lisagor</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1702.933333333333</v>
+        <v>797.3000000000001</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>250.9333333333333</v>
+        <v>376</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1112.8</v>
+        <v>164.2</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Poonam Yadav: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>FSSE (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; HRAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SSAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 8 projects x MSc (24h) = 192.0h</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h; Grant CHEDDAR Funding Apr-Sep 26- PSU296: 5% of 1642h = 82.1h; Grant REMOTE: Resilient and Secure Multi-Access Interoperable Communication Fabric for TinyEdge: 20% of 1642h = 328.4h; Grant Orchestrated mobile Network for Blackpool intelligent transport: 5% of 1642h = 82.1h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -2880,37 +2880,37 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Pourya Shamsolmoali</t>
+          <t>Paul Cairns</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>922.4166666666666</v>
+        <v>1797.633333333334</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>396.0666666666667</v>
+        <v>281.6333333333333</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>228.2</v>
+        <v>1012.6</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>298.15</v>
+        <v>503.4</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Pourya Shamsolmoali: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; IMLO (20cr): Pourya Shamsolmoali: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>GODS (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HCIN (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h; Grant BiB Centre for Social Change: 0% of 1642h = 0.0h; Grant IGGI: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Graduate School Board (Ordinary member): 2% of 1642h = 41.1h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; REF Lead: 5% of 1642h = 82.1h; Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -2932,37 +2932,37 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Radu Calinescu</t>
+          <t>Pedro Ribeiro</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1224.7</v>
+        <v>1296.3</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>131</v>
+        <v>312.5</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>918.7</v>
+        <v>644.6</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>GPIG (40cr): Radu Calinescu: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>AURO (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS1 (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h; Grant ARISE: Accelerating ReIntroduction of EcoSystem-Engineering Ant Colonies with Embodied AI: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h; Grant MammoBot: Robotic Posture Assistance for Universal Breast Screening Access: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -2984,37 +2984,37 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Rob Alexander</t>
+          <t>Pengcheng Liu</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>800</v>
+        <v>1993.32</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>226.7</v>
+        <v>296.3</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>398.3</v>
+        <v>996.5800000000002</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>175</v>
+        <v>700.4400000000001</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS3 (20cr): Pengcheng Liu: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Intelligent Dependable Environment Control for Sustainable Aquaculture: 20% of 1642h = 328.4h; Grant Establishing a Safe AI Research Hub: York–UTM–UTB Twin-Lab Initiative: 9% of 1642h = 147.8h; Grant Establishment of Korea–UK Collaboration Platform for Convergent Research in Quantum Photonics and Artificial Intelligence - Yr2: 5% of 1642h = 82.1h; Grant SCHEME: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Graduate Chair: 20% of 1642h = 328.4h; Research Group Leader: 10% of 1642h = 164.2h; Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -3036,37 +3036,37 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Robbert Jongeling</t>
+          <t>Peter Nightingale</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>832.7</v>
+        <v>1069.866666666667</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>493.5</v>
+        <v>430.4666666666666</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>164.2</v>
+        <v>300.2</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>ELLA (20cr): Robbert Jongeling: New lecturer + new content (7.5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Robbert Jongeling: 7.5x, Antonio Garcia-Dominguez: 5x, Soumya Banerjee: 7.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ENG1 (20cr): Robbert Jongeling: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Kostas Barmpis: 2.5x, Robbert Jongeling: 5x, Tommy Yuan: 2.5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 2 students x 3h = 6.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>ARIA (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; FOAM (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SAIL (20cr): Peter Nightingale: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>UG PL: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned; ELLA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+          <t>ARIA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -3088,37 +3088,37 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Roberto Metere</t>
+          <t>Poonam Yadav</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1047.383333333333</v>
+        <v>1702.933333333333</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>604.1833333333334</v>
+        <v>250.9333333333333</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>268.2</v>
+        <v>1112.8</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Roberto Metere: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; CTAP (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; EHAC (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SOF1 (20cr): Poonam Yadav: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h; Grant CHEDDAR Funding Apr-Sep 26- PSU296: 5% of 1642h = 82.1h; Grant REMOTE: Resilient and Secure Multi-Access Interoperable Communication Fabric for TinyEdge: 20% of 1642h = 328.4h; Grant Orchestrated mobile Network for Blackpool intelligent transport: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
@@ -3140,37 +3140,37 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Sam Braunstein</t>
+          <t>Pourya Shamsolmoali</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>616.4833333333333</v>
+        <v>1010.9</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>277.2833333333333</v>
+        <v>484.55</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>164.2</v>
+        <v>228.2</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>175</v>
+        <v>298.15</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; THE2 (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DATA (20cr): Pourya Shamsolmoali: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; DEEP (20cr): Pourya Shamsolmoali: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Graduate School Board (Ordinary member): 2% of 1642h = 41.1h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -3192,37 +3192,37 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Siamak Shahandashti</t>
+          <t>Radu Calinescu</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1193.866666666667</v>
+        <v>1257.54</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>376.3666666666667</v>
+        <v>131</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>478.3</v>
+        <v>918.7</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>339.2</v>
+        <v>207.84</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE1 (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>GPIG (40cr): Radu Calinescu: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h; Grant Participatory Harm Auditing Workbenches &amp; Methodologies: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h; Grant ARISE: Accelerating ReIntroduction of EcoSystem-Engineering Ant Colonies with Embodied AI: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h; Grant MammoBot: Robotic Posture Assistance for Universal Breast Screening Access: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
@@ -3244,37 +3244,37 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Simon Foster</t>
+          <t>Richard Hawkins</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>799.0333333333333</v>
+        <v>1158</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>347.8333333333333</v>
+        <v>378.4</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>276.2</v>
+        <v>358.3</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>175</v>
+        <v>421.3</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Simon Foster: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Simon Foster: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Detlef Plump: 2.5x, Simon Foster: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>CASA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SCDR (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 23 students x 3h = 69.0h; Projects: 7 projects x MSc (24h) = 168.0h</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Impact: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -3296,37 +3296,37 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Soumya Banerjee</t>
+          <t>Richard Wilson</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>858.3333333333333</v>
+        <v>657.04</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>519.1333333333333</v>
+        <v>3</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>164.2</v>
+        <v>450.52</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>175</v>
+        <v>203.52</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): Soumya Banerjee: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; ELLA (20cr): Soumya Banerjee: New lecturer + new content (7.5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Robbert Jongeling: 7.5x, Antonio Garcia-Dominguez: 5x, Soumya Banerjee: 7.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>; Pastoral: 1 students x 3h = 3.0h; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 352.0h</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>ART staff representative: 0% of 985h = 0.0h; Research Group Leader: 10% of 985h = 98.5h; Engagement (email/meetings): 60.0h; Personal development: 45.0h (FTE: 0.60)</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned; ELLA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
@@ -3348,37 +3348,37 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Stefano Pirandola</t>
+          <t>Rob Alexander</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1216.25</v>
+        <v>1043.88</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>274.55</v>
+        <v>404.9</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>520.4000000000001</v>
+        <v>398.3</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>421.3</v>
+        <v>240.68</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Stefano Pirandola: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HINT (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; RASS (10cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; REMS (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x MSc (24h) = 168.0h</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Integrated Quantum Networks (IQN) Hub: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>StAMP committee: 4% of 1642h = 65.7h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
@@ -3400,37 +3400,37 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Steven Wright</t>
+          <t>Roberto Metere</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>853.9</v>
+        <v>1120.363333333333</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>226.7</v>
+        <v>611.4833333333333</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>452.2</v>
+        <v>268.2</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>175</v>
+        <v>240.68</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>HIPC (20cr): Steven Wright: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>CBDA (20cr): Roberto Metere: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; CTAP (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; EHAC (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>Chair of the Board of Examiners: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>StAMP committee: 4% of 1642h = 65.7h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
@@ -3452,37 +3452,37 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Steven Xiaotian Dai</t>
+          <t>Sam Braunstein</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1183.2</v>
+        <v>623.7833333333333</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>329.5</v>
+        <v>284.5833333333333</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>350.3</v>
+        <v>164.2</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>EMBS (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HIPC (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>QUCO (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; THE2 (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h; Grant SCHEME: 5% of 1642h = 82.1h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>Student Disability Representative: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -3504,37 +3504,37 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Tommy Yuan</t>
+          <t>Sarah Carrington</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1301.733333333333</v>
+        <v>648.66</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>598.3333333333333</v>
+        <v>377.3</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>364.2</v>
+        <v>131.36</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>339.2</v>
+        <v>140</v>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>ARIA (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ENG1 (20cr): Tommy Yuan: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Kostas Barmpis: 2.5x, Robbert Jongeling: 5x, Tommy Yuan: 2.5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; FOAM (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>FSSE (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SCDR (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 10 projects x MSc (24h) = 240.0h</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 200.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>CSCSE SQA Partnership Leader: 0% of 1642h = 0.0h; Deputy CBoEs: 10% of 1642h = 164.2h; StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 80.0h; Personal development: 60.0h (FTE: 0.80)</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>ARIA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
@@ -3556,37 +3556,37 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Vasileios Vasilakis</t>
+          <t>Siamak Shahandashti</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>999</v>
+        <v>1365.366666666667</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>303.6</v>
+        <v>383.6666666666666</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>356.2</v>
+        <v>478.3</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>339.2</v>
+        <v>503.4</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>NETS (20cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CTAP (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE1 (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h; Grant Participatory Harm Auditing Workbenches &amp; Methodologies: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
@@ -3608,37 +3608,37 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>William Smith</t>
+          <t>Simon Burton</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1333.55</v>
+        <v>1020.24</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>359.2</v>
+        <v>53.7</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>676.2</v>
+        <v>791.54</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>298.15</v>
+        <v>175</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>DEEP (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, James Stovold: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; ROCS (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>CASA (10cr): Simon Burton: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h; Grant Verifiable generation of SOTIF requirements: 2% of 1642h = 32.8h; Grant Moving forward explainable AI by combining different assurance metrics: 15% of 1642h = 246.3h; Grant AI safety argumentation review: 5% of 1642h = 82.1h; Grant KTP with DNV Services Ltd - Innovate part: 3% of 1642h = 49.3h; Grant KTP with DNV Services Ltd - Industry part: 2% of 1642h = 32.8h</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
@@ -3660,37 +3660,37 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Xinwei Fang</t>
+          <t>Simon Foster</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>910.5</v>
+        <v>855.1166666666666</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>409.2</v>
+        <v>403.9166666666666</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>244.2</v>
+        <v>276.2</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; GPIG (40cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>THE1 (20cr): Simon Foster: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Simon Foster: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -3712,37 +3712,33 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Yan Jia</t>
+          <t>Simos Gerasimou</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>961.8000000000001</v>
+        <v>1309.68</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>148.1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>638.7</v>
+        <v>1101.84</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>ROCS (20cr): Yan Jia: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
-        </is>
-      </c>
+        <v>207.84</v>
+      </c>
+      <c r="G56" s="4" t="inlineStr"/>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10% of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 248.0h; Grant Human-centric Digital Twin Approaches to Trustworthy AI and Robotics for Improved Working Conditions: 12% of 1642h = 197.0h; Grant Socially-Acceptable and Trustworthy Human-Robot Teaming for Agile Industries (SYMPHONY Resubmission): 10% of 1642h = 164.2h; Grant GuardAI ( Enhancing Robustness and Security of Edge AI Systems for Safety-Critical Applications): 15% of 1642h = 246.3h; Grant MOSAICO: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
@@ -3752,7 +3748,7 @@
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
@@ -3764,50 +3760,518 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>Soumya Banerjee</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>919.8333333333334</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>416.4333333333333</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>164.2</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>339.2</v>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>AURO (20cr): Soumya Banerjee: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; LLMA (20cr): Soumya Banerjee: New lecturer + new content (7.5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>No research activities recorded</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai Campus Partnership Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>LLMA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Stefano Pirandola</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>1380.45</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>274.55</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>520.4000000000001</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>585.5</v>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>QUCO (20cr): Stefano Pirandola: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Integrated Quantum Networks (IQN) Hub: 10% of 1642h = 164.2h</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Steven Wright</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>1353.8</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>452.2</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>667.5999999999999</v>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>HIPC (20cr): Steven Wright: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>CBoE (on-campus): 30% of 1642h = 492.6h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Steven Xiaotian Dai</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>1190.5</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>336.8</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>350.3</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>503.4</v>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>EMBS (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HIPC (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h; Grant SCHEME: 5% of 1642h = 82.1h</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Student Disability Representative: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Tommy Yuan</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>1557.546666666667</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>624.2666666666667</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>364.2</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>569.08</v>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>ARIA (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; ENG1 (20cr): Tommy Yuan: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; FOAM (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 200.0h</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>CSCSE HAP Partnership Leader: 10% of 1642h = 164.2h; Deputy CBoEs: 10% of 1642h = 164.2h; StAMP committee: 4% of 1642h = 65.7h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>ARIA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Vasileios Vasilakis</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>1103.9</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>408.5</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>356.2</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>339.2</v>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>NETS (20cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x MSc (24h) = 168.0h</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>William Smith</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>1490.316666666667</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>351.7666666666667</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>676.2</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>462.35</v>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>DEEP (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; ROCS (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Xinwei Fang</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>925.1</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>423.8</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>244.2</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>257.1</v>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>DATA (20cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; GPIG (40cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Yan Jia</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>1169.1</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>638.7</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>503.4</v>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10% of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>Ethics Committee Member: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
           <t>Yuchen Zhao</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>849.1999999999999</v>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>411.9</v>
-      </c>
-      <c r="E57" s="3" t="n">
+      <c r="B66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>856.5</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>419.2</v>
+      </c>
+      <c r="E66" s="3" t="n">
         <v>180.2</v>
       </c>
-      <c r="F57" s="3" t="n">
+      <c r="F66" s="3" t="n">
         <v>257.1</v>
       </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t>EHAC (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; NETS (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
+      <c r="H66" s="4" t="inlineStr">
         <is>
           <t>PhD supervision: 2x assessor (8h each) = 16.0h</t>
         </is>
       </c>
-      <c r="I57" s="4" t="inlineStr">
+      <c r="I66" s="4" t="inlineStr">
         <is>
           <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L57" s="5" t="inlineStr">
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3838,7 +4302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3902,7 +4366,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>343.7</v>
+        <v>351</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>444.2</v>
@@ -3922,7 +4386,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>204.8666666666667</v>
+        <v>303.8333333333333</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>268.2</v>
@@ -3938,17 +4402,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Andrew Pomfret</t>
+          <t>Ana Cavalcanti</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>452.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>164.2</v>
+        <v>548.2</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="E5" s="7">
         <f>SUM(B5:D5)</f>
@@ -3958,17 +4422,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Antonio Garcia-Dominguez</t>
+          <t>Andrew Pomfret</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>315.2</v>
+        <v>459.6333333333333</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>644.6000000000001</v>
+        <v>164.2</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E6" s="7">
         <f>SUM(B6:D6)</f>
@@ -3978,17 +4442,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Carlo Ottaviani</t>
+          <t>Antonio Garcia-Dominguez</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>416.2333333333333</v>
+        <v>357.3</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>268.2</v>
+        <v>644.6000000000001</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E7" s="7">
         <f>SUM(B7:D7)</f>
@@ -3998,17 +4462,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Christopher Crispin-Bailey</t>
+          <t>Carlo Ottaviani</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>530.1</v>
+        <v>423.5333333333333</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>164.2</v>
+        <v>268.2</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>462.35</v>
+        <v>339.2</v>
       </c>
       <c r="E8" s="7">
         <f>SUM(B8:D8)</f>
@@ -4018,17 +4482,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Claire Ingram</t>
+          <t>Christopher Crispin-Bailey</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>238.7</v>
+        <v>593.1</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>164.2</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>257.1</v>
+        <v>462.35</v>
       </c>
       <c r="E9" s="7">
         <f>SUM(B9:D9)</f>
@@ -4038,17 +4502,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Claudio Guarnera</t>
+          <t>Claire Ingram</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>212.8666666666667</v>
+        <v>399.6</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>276.2</v>
+        <v>164.2</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E10" s="7">
         <f>SUM(B10:D10)</f>
@@ -4058,17 +4522,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Colin Paterson</t>
+          <t>Claudio Guarnera</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>224</v>
+        <v>212.8666666666667</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>579.76</v>
+        <v>177.68</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>175</v>
+        <v>70</v>
       </c>
       <c r="E11" s="7">
         <f>SUM(B11:D11)</f>
@@ -4078,14 +4542,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Da Li</t>
+          <t>Colin Paterson</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>410.8333333333333</v>
+        <v>401.4</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>164.2</v>
+        <v>579.76</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>175</v>
@@ -4098,11 +4562,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dawn H Wood</t>
+          <t>Da Li</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>437.5</v>
+        <v>317.8333333333334</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>164.2</v>
@@ -4118,17 +4582,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Detlef Plump</t>
+          <t>David Pumfrey</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>349.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>260.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>503.4</v>
+        <v>87.5</v>
       </c>
       <c r="E14" s="7">
         <f>SUM(B14:D14)</f>
@@ -4138,17 +4602,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dimitar Kazakov</t>
+          <t>Dawn H Wood</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>379.5</v>
+        <v>444.8</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>620.2</v>
+        <v>164.2</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="E15" s="7">
         <f>SUM(B15:D15)</f>
@@ -4158,17 +4622,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dimitris Kolovos</t>
+          <t>Detlef Plump</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>50.2</v>
+        <v>405.3833333333333</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>1114.9</v>
+        <v>260.2</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="E16" s="7">
         <f>SUM(B16:D16)</f>
@@ -4178,17 +4642,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fang Yan</t>
+          <t>Dimitar Kazakov</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>373.8</v>
+        <v>386.8</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>164.2</v>
+        <v>620.2</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="E17" s="7">
         <f>SUM(B17:D17)</f>
@@ -4198,17 +4662,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Felix Ulrich-Oltean</t>
+          <t>Dimitris Kolovos</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>71</v>
+        <v>50.2</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>212.2</v>
+        <v>1114.9</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>175</v>
+        <v>372.04</v>
       </c>
       <c r="E18" s="7">
         <f>SUM(B18:D18)</f>
@@ -4218,17 +4682,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Frank Soboczenski</t>
+          <t>Fang Yan</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>137.5</v>
+        <v>214.4</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>1794.42</v>
+        <v>164.2</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="E19" s="7">
         <f>SUM(B19:D19)</f>
@@ -4238,17 +4702,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Iain Bate</t>
+          <t>Felix Ulrich-Oltean</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>588.6</v>
+        <v>212.2</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>1817</v>
+        <v>175</v>
       </c>
       <c r="E20" s="7">
         <f>SUM(B20:D20)</f>
@@ -4258,17 +4722,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ian Gray</t>
+          <t>Frank Soboczenski</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>99.8</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>348.2</v>
+        <v>1794.42</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>996</v>
+        <v>257.1</v>
       </c>
       <c r="E21" s="7">
         <f>SUM(B21:D21)</f>
@@ -4278,17 +4742,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jacob Rigby</t>
+          <t>Iain Bate</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>235.9333333333333</v>
+        <v>30</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>246.3</v>
+        <v>588.6</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>339.2</v>
+        <v>1817</v>
       </c>
       <c r="E22" s="7">
         <f>SUM(B22:D22)</f>
@@ -4298,17 +4762,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>James Stovold</t>
+          <t>Ian Gray</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>606.6</v>
+        <v>99.8</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>164.2</v>
+        <v>348.2</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>257.1</v>
+        <v>996</v>
       </c>
       <c r="E23" s="7">
         <f>SUM(B23:D23)</f>
@@ -4318,17 +4782,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>James Walker</t>
+          <t>Jacob Rigby</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>309.8666666666667</v>
+        <v>243.2333333333333</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>1000.8</v>
+        <v>246.3</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E24" s="7">
         <f>SUM(B24:D24)</f>
@@ -4338,17 +4802,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jen Beeston</t>
+          <t>James Stovold</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>348.4</v>
+        <v>407.5</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>332.2</v>
+        <v>164.2</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E25" s="7">
         <f>SUM(B25:D25)</f>
@@ -4358,17 +4822,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jo Iacovides</t>
+          <t>James Walker</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>297.7</v>
+        <v>309.8666666666667</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>348.2</v>
+        <v>1000.8</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E26" s="7">
         <f>SUM(B26:D26)</f>
@@ -4378,17 +4842,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Joe Cutting</t>
+          <t>Jen Beeston</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>339.8</v>
+        <v>355.7</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>228.2</v>
+        <v>332.2</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>175</v>
+        <v>667.5999999999999</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(B27:D27)</f>
@@ -4398,17 +4862,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Katrina Attwood</t>
+          <t>Jo Iacovides</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>447.3333333333334</v>
+        <v>297.7</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>212.2</v>
+        <v>348.2</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>503.4</v>
+        <v>339.2</v>
       </c>
       <c r="E28" s="7">
         <f>SUM(B28:D28)</f>
@@ -4418,17 +4882,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kofi Appiah</t>
+          <t>Joe Cutting</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>388.5</v>
+        <v>347.1</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>356.2</v>
+        <v>228.2</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>421.3</v>
+        <v>175</v>
       </c>
       <c r="E29" s="7">
         <f>SUM(B29:D29)</f>
@@ -4438,17 +4902,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kostas Barmpis</t>
+          <t>John McDermid</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>364.5333333333333</v>
+        <v>0</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>548.6</v>
+        <v>1539.7</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="E30" s="7">
         <f>SUM(B30:D30)</f>
@@ -4458,17 +4922,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mike Freeman</t>
+          <t>Katrina Attwood</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>473.3333333333333</v>
+        <v>454.6333333333333</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>164.2</v>
+        <v>212.2</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>257.1</v>
+        <v>503.4</v>
       </c>
       <c r="E31" s="7">
         <f>SUM(B31:D31)</f>
@@ -4478,17 +4942,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mike O'Dea</t>
+          <t>Kofi Appiah</t>
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>210.6</v>
+        <v>395.8</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>164.2</v>
+        <v>356.2</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>257.1</v>
+        <v>421.3</v>
       </c>
       <c r="E32" s="7">
         <f>SUM(B32:D32)</f>
@@ -4498,17 +4962,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nick Pears</t>
+          <t>Kostas Barmpis</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>208.9333333333333</v>
+        <v>429</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>428.2</v>
+        <v>548.6</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>831.8000000000001</v>
+        <v>257.1</v>
       </c>
       <c r="E33" s="7">
         <f>SUM(B33:D33)</f>
@@ -4518,17 +4982,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Paul Cairns</t>
+          <t>Mark Nicholson</t>
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>274.3333333333334</v>
+        <v>314.7</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>1012.6</v>
+        <v>227.36</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>339.2</v>
+        <v>192.544</v>
       </c>
       <c r="E34" s="7">
         <f>SUM(B34:D34)</f>
@@ -4538,17 +5002,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pedro Ribeiro</t>
+          <t>Mark Sujan</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>305.2</v>
+        <v>47.4</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>644.6</v>
+        <v>131.36</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>339.2</v>
+        <v>140</v>
       </c>
       <c r="E35" s="7">
         <f>SUM(B35:D35)</f>
@@ -4558,17 +5022,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pengcheng Liu</t>
+          <t>Mike Freeman</t>
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>226</v>
+        <v>480.6333333333333</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>996.5800000000002</v>
+        <v>164.2</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E36" s="7">
         <f>SUM(B36:D36)</f>
@@ -4578,17 +5042,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Peter Nightingale</t>
+          <t>Mike O'Dea</t>
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>469</v>
+        <v>395.3</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>300.2</v>
+        <v>164.2</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="E37" s="7">
         <f>SUM(B37:D37)</f>
@@ -4598,17 +5062,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Phoebe</t>
+          <t>Nick Pears</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>0</v>
+        <v>208.9333333333333</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>164.2</v>
+        <v>428.2</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>175</v>
+        <v>831.8000000000001</v>
       </c>
       <c r="E38" s="7">
         <f>SUM(B38:D38)</f>
@@ -4618,17 +5082,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poonam Yadav</t>
+          <t>Oleg Lisagor</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>250.9333333333333</v>
+        <v>376</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>1112.8</v>
+        <v>164.2</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="E39" s="7">
         <f>SUM(B39:D39)</f>
@@ -4638,17 +5102,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pourya Shamsolmoali</t>
+          <t>Paul Cairns</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>396.0666666666667</v>
+        <v>281.6333333333333</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>228.2</v>
+        <v>1012.6</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>298.15</v>
+        <v>503.4</v>
       </c>
       <c r="E40" s="7">
         <f>SUM(B40:D40)</f>
@@ -4658,17 +5122,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Radu Calinescu</t>
+          <t>Pedro Ribeiro</t>
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>131</v>
+        <v>312.5</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>918.7</v>
+        <v>644.6</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E41" s="7">
         <f>SUM(B41:D41)</f>
@@ -4678,17 +5142,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Rob Alexander</t>
+          <t>Pengcheng Liu</t>
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>226.7</v>
+        <v>296.3</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>398.3</v>
+        <v>996.5800000000002</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>175</v>
+        <v>700.4400000000001</v>
       </c>
       <c r="E42" s="7">
         <f>SUM(B42:D42)</f>
@@ -4698,17 +5162,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Robbert Jongeling</t>
+          <t>Peter Nightingale</t>
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>493.5</v>
+        <v>430.4666666666666</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>164.2</v>
+        <v>300.2</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E43" s="7">
         <f>SUM(B43:D43)</f>
@@ -4718,17 +5182,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Roberto Metere</t>
+          <t>Poonam Yadav</t>
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>604.1833333333334</v>
+        <v>250.9333333333333</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>268.2</v>
+        <v>1112.8</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E44" s="7">
         <f>SUM(B44:D44)</f>
@@ -4738,17 +5202,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sam Braunstein</t>
+          <t>Pourya Shamsolmoali</t>
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>277.2833333333333</v>
+        <v>484.55</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>164.2</v>
+        <v>228.2</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>175</v>
+        <v>298.15</v>
       </c>
       <c r="E45" s="7">
         <f>SUM(B45:D45)</f>
@@ -4758,17 +5222,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Siamak Shahandashti</t>
+          <t>Radu Calinescu</t>
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>376.3666666666667</v>
+        <v>131</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>478.3</v>
+        <v>918.7</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>339.2</v>
+        <v>207.84</v>
       </c>
       <c r="E46" s="7">
         <f>SUM(B46:D46)</f>
@@ -4778,17 +5242,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Simon Foster</t>
+          <t>Richard Hawkins</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>347.8333333333333</v>
+        <v>378.4</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>276.2</v>
+        <v>358.3</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>175</v>
+        <v>421.3</v>
       </c>
       <c r="E47" s="7">
         <f>SUM(B47:D47)</f>
@@ -4798,17 +5262,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Soumya Banerjee</t>
+          <t>Richard Wilson</t>
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>519.1333333333333</v>
+        <v>3</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>164.2</v>
+        <v>450.52</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>175</v>
+        <v>203.52</v>
       </c>
       <c r="E48" s="7">
         <f>SUM(B48:D48)</f>
@@ -4818,17 +5282,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Stefano Pirandola</t>
+          <t>Rob Alexander</t>
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>274.55</v>
+        <v>404.9</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>520.4000000000001</v>
+        <v>398.3</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>421.3</v>
+        <v>240.68</v>
       </c>
       <c r="E49" s="7">
         <f>SUM(B49:D49)</f>
@@ -4838,17 +5302,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Steven Wright</t>
+          <t>Roberto Metere</t>
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>226.7</v>
+        <v>611.4833333333333</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>452.2</v>
+        <v>268.2</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>175</v>
+        <v>240.68</v>
       </c>
       <c r="E50" s="7">
         <f>SUM(B50:D50)</f>
@@ -4858,17 +5322,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Steven Xiaotian Dai</t>
+          <t>Sam Braunstein</t>
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>329.5</v>
+        <v>284.5833333333333</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>350.3</v>
+        <v>164.2</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="E51" s="7">
         <f>SUM(B51:D51)</f>
@@ -4878,17 +5342,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tommy Yuan</t>
+          <t>Sarah Carrington</t>
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>598.3333333333333</v>
+        <v>377.3</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>364.2</v>
+        <v>131.36</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>339.2</v>
+        <v>140</v>
       </c>
       <c r="E52" s="7">
         <f>SUM(B52:D52)</f>
@@ -4898,17 +5362,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vasileios Vasilakis</t>
+          <t>Siamak Shahandashti</t>
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>303.6</v>
+        <v>383.6666666666666</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>356.2</v>
+        <v>478.3</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>339.2</v>
+        <v>503.4</v>
       </c>
       <c r="E53" s="7">
         <f>SUM(B53:D53)</f>
@@ -4918,17 +5382,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>William Smith</t>
+          <t>Simon Burton</t>
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>359.2</v>
+        <v>53.7</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>676.2</v>
+        <v>791.54</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>298.15</v>
+        <v>175</v>
       </c>
       <c r="E54" s="7">
         <f>SUM(B54:D54)</f>
@@ -4938,17 +5402,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Xinwei Fang</t>
+          <t>Simon Foster</t>
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>409.2</v>
+        <v>403.9166666666666</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>244.2</v>
+        <v>276.2</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="E55" s="7">
         <f>SUM(B55:D55)</f>
@@ -4958,17 +5422,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Yan Jia</t>
+          <t>Simos Gerasimou</t>
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>148.1</v>
+        <v>0</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>638.7</v>
+        <v>1101.84</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>175</v>
+        <v>207.84</v>
       </c>
       <c r="E56" s="7">
         <f>SUM(B56:D56)</f>
@@ -4978,20 +5442,200 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Yuchen Zhao</t>
+          <t>Soumya Banerjee</t>
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>411.9</v>
+        <v>416.4333333333333</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>180.2</v>
+        <v>164.2</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="E57" s="7">
         <f>SUM(B57:D57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Stefano Pirandola</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>274.55</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>520.4000000000001</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>585.5</v>
+      </c>
+      <c r="E58" s="7">
+        <f>SUM(B58:D58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Steven Wright</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="n">
+        <v>234</v>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>452.2</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>667.5999999999999</v>
+      </c>
+      <c r="E59" s="7">
+        <f>SUM(B59:D59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Steven Xiaotian Dai</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>336.8</v>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>350.3</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>503.4</v>
+      </c>
+      <c r="E60" s="7">
+        <f>SUM(B60:D60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Tommy Yuan</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="n">
+        <v>624.2666666666667</v>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>364.2</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>569.08</v>
+      </c>
+      <c r="E61" s="7">
+        <f>SUM(B61:D61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Vasileios Vasilakis</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="n">
+        <v>408.5</v>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>356.2</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>339.2</v>
+      </c>
+      <c r="E62" s="7">
+        <f>SUM(B62:D62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>William Smith</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="n">
+        <v>351.7666666666667</v>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>676.2</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>462.35</v>
+      </c>
+      <c r="E63" s="7">
+        <f>SUM(B63:D63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Xinwei Fang</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>423.8</v>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>244.2</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>257.1</v>
+      </c>
+      <c r="E64" s="7">
+        <f>SUM(B64:D64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Yan Jia</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>638.7</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>503.4</v>
+      </c>
+      <c r="E65" s="7">
+        <f>SUM(B65:D65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Yuchen Zhao</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>419.2</v>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>257.1</v>
+      </c>
+      <c r="E66" s="7">
+        <f>SUM(B66:D66)</f>
         <v/>
       </c>
     </row>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -195,12 +195,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Staff Workload'!$A$2:$A$66</f>
+              <f>'Staff Workload'!$A$2:$A$67</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Staff Workload'!$D$2:$D$66</f>
+              <f>'Staff Workload'!$D$2:$D$67</f>
             </numRef>
           </val>
         </ser>
@@ -219,12 +219,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Staff Workload'!$A$2:$A$66</f>
+              <f>'Staff Workload'!$A$2:$A$67</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Staff Workload'!$E$2:$E$66</f>
+              <f>'Staff Workload'!$E$2:$E$67</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +243,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Staff Workload'!$A$2:$A$66</f>
+              <f>'Staff Workload'!$A$2:$A$67</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Staff Workload'!$F$2:$F$66</f>
+              <f>'Staff Workload'!$F$2:$F$67</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Detailed Breakdown'!$A$2:$A$66</f>
+              <f>'Detailed Breakdown'!$A$2:$A$67</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Detailed Breakdown'!$B$2:$B$66</f>
+              <f>'Detailed Breakdown'!$B$2:$B$67</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Detailed Breakdown'!$A$2:$A$66</f>
+              <f>'Detailed Breakdown'!$A$2:$A$67</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Detailed Breakdown'!$C$2:$C$66</f>
+              <f>'Detailed Breakdown'!$C$2:$C$67</f>
             </numRef>
           </val>
         </ser>
@@ -408,12 +408,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Detailed Breakdown'!$A$2:$A$66</f>
+              <f>'Detailed Breakdown'!$A$2:$A$67</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Detailed Breakdown'!$D$2:$D$66</f>
+              <f>'Detailed Breakdown'!$D$2:$D$67</f>
             </numRef>
           </val>
         </ser>
@@ -830,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2052,37 +2052,37 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Jacob Rigby</t>
+          <t>Ibrahim Habli</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>828.7333333333333</v>
+        <v>1670.5</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>243.2333333333333</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>246.3</v>
+        <v>1495.5</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Jacob Rigby: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>; Also teaches: Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Grant EPSRC: Addressing environmental injustices through transdisciplinary science and technology: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 264.0h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10% of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10% of 1642h = 164.2h; Grant A STAR TO STEER BY: 5% of 1642h = 82.1h; Grant The Centre for Assuring Autonomy: 40% of 1642h = 656.8h</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Taught Project Coordinator: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
@@ -2104,37 +2104,37 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>James Stovold</t>
+          <t>Jacob Rigby</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>828.8000000000001</v>
+        <v>828.7333333333333</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>407.5</v>
+        <v>243.2333333333333</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>164.2</v>
+        <v>246.3</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): James Stovold: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HCIN (20cr): Jacob Rigby: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>Grant EPSRC: Addressing environmental injustices through transdisciplinary science and technology: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Taught Project Coordinator: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -2156,37 +2156,37 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>James Walker</t>
+          <t>James Stovold</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1485.666666666667</v>
+        <v>828.8000000000001</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>309.8666666666667</v>
+        <v>407.5</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1000.8</v>
+        <v>164.2</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): James Walker: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IMLO (20cr): James Stovold: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h; Grant Smart Data Donation Service (SDDS): 10% of 1642h = 164.2h; Grant IGGI: 20% of 1642h = 328.4h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -2208,37 +2208,37 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Jen Beeston</t>
+          <t>James Walker</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1355.5</v>
+        <v>1485.666666666667</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>355.7</v>
+        <v>309.8666666666667</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>332.2</v>
+        <v>1000.8</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>667.5999999999999</v>
+        <v>175</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>QUAL (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; TECC (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>IMLO (20cr): James Walker: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 168.0h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h; Grant Smart Data Donation Service (SDDS): 10% of 1642h = 164.2h; Grant IGGI: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>DEC Chair: 30% of 1642h = 492.6h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -2260,37 +2260,37 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Jo Iacovides</t>
+          <t>Jen Beeston</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>985.1</v>
+        <v>1355.5</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>297.7</v>
+        <v>355.7</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>348.2</v>
+        <v>332.2</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>339.2</v>
+        <v>667.5999999999999</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>PLEI (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; QUAL (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>QUAL (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; TECC (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 184.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 168.0h</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>DEC Chair: 30% of 1642h = 492.6h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -2312,37 +2312,37 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Joe Cutting</t>
+          <t>Jo Iacovides</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>750.3</v>
+        <v>985.1</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>347.1</v>
+        <v>297.7</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>228.2</v>
+        <v>348.2</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PRAD (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>PLEI (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; QUAL (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 184.0h</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>ECR representative: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -2364,33 +2364,37 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>John McDermid</t>
+          <t>Joe Cutting</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1878.9</v>
+        <v>750.3</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0</v>
+        <v>347.1</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1539.7</v>
+        <v>228.2</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>339.2</v>
-      </c>
-      <c r="G30" s="4" t="inlineStr"/>
+        <v>175</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>IDEV (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PRAD (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+        </is>
+      </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE = 144.0h; Grant Assessment of DSTA USVs and Continual Assurance of CI/CD for USVs: 5% of 1642h = 82.1h; Grant RAI UK: Safety &amp; Security Network (SSAIN): 20% of 1642h = 328.4h; Grant The Centre for Assuring Autonomy: 50% of 1642h = 821.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>ECR representative: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -2412,37 +2416,33 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Katrina Attwood</t>
+          <t>John McDermid</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1170.233333333333</v>
+        <v>1878.9</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>454.6333333333333</v>
+        <v>0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>212.2</v>
+        <v>1539.7</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>503.4</v>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>HCIN (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; TECC (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
-        </is>
-      </c>
+        <v>339.2</v>
+      </c>
+      <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE = 144.0h; Grant Assessment of DSTA USVs and Continual Assurance of CI/CD for USVs: 5% of 1642h = 82.1h; Grant RAI UK: Safety &amp; Security Network (SSAIN): 20% of 1642h = 328.4h; Grant The Centre for Assuring Autonomy: 50% of 1642h = 821.0h</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Director of Students: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -2464,37 +2464,37 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Kofi Appiah</t>
+          <t>Katrina Attwood</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1173.3</v>
+        <v>1170.233333333333</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>395.8</v>
+        <v>454.6333333333333</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>356.2</v>
+        <v>212.2</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>421.3</v>
+        <v>503.4</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>HCIN (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; TECC (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Deputy Director of Admissions (UG Admissions): 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Director of Students: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -2516,37 +2516,37 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Kostas Barmpis</t>
+          <t>Kofi Appiah</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1234.7</v>
+        <v>1173.3</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>429</v>
+        <v>395.8</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>548.6</v>
+        <v>356.2</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>257.1</v>
+        <v>421.3</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; ENG2 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SOF1 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>PGR Training Officer: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Director of Admissions (UG Admissions): 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -2568,37 +2568,37 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Mark Nicholson</t>
+          <t>Kostas Barmpis</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>734.6039999999999</v>
+        <v>1234.7</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>314.7</v>
+        <v>429</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>227.36</v>
+        <v>548.6</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>192.544</v>
+        <v>257.1</v>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>RASS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SSAS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 8 projects x MSc (24h) = 192.0h</t>
+          <t>ENG1 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; ENG2 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE = 96.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>StAMP committee: 4% of 1314h = 52.5h; Engagement (email/meetings): 80.0h; Personal development: 60.0h (FTE: 0.80)</t>
+          <t>PGR Training Officer: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -2620,37 +2620,37 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Mark Sujan</t>
+          <t>Mark Nicholson</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>318.76</v>
+        <v>734.6039999999999</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>47.4</v>
+        <v>314.7</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>131.36</v>
+        <v>227.36</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>140</v>
+        <v>192.544</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>HUFS (10cr): Mark Sujan: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
+          <t>RASS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SSAS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 8 projects x MSc (24h) = 192.0h</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE = 96.0h</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 80.0h; Personal development: 60.0h (FTE: 0.80)</t>
+          <t>StAMP committee: 4% of 1314h = 52.5h; Engagement (email/meetings): 80.0h; Personal development: 60.0h (FTE: 0.80)</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -2672,27 +2672,27 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Mike Freeman</t>
+          <t>Mark Sujan</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>901.9333333333333</v>
+        <v>318.76</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>480.6333333333333</v>
+        <v>47.4</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>164.2</v>
+        <v>131.36</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>257.1</v>
+        <v>140</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>HUFS (10cr): Mark Sujan: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 80.0h; Personal development: 60.0h (FTE: 0.80)</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -2724,17 +2724,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Mike O'Dea</t>
+          <t>Mike Freeman</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>816.6</v>
+        <v>901.9333333333333</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>395.3</v>
+        <v>480.6333333333333</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>164.2</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; GODS (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ROCS (20cr): Mike O'Dea: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h</t>
+          <t>SYS1 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -2776,37 +2776,37 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Nick Pears</t>
+          <t>Mike O'Dea</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1468.933333333333</v>
+        <v>816.6</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>208.9333333333333</v>
+        <v>395.3</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>428.2</v>
+        <v>164.2</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>831.8000000000001</v>
+        <v>257.1</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Nick Pears: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>CBDA (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; GODS (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ROCS (20cr): Mike O'Dea: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 264.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Deputy Head (Research): 40% of 1642h = 656.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
@@ -2828,37 +2828,37 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Oleg Lisagor</t>
+          <t>Nick Pears</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>797.3000000000001</v>
+        <v>1468.933333333333</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>376</v>
+        <v>208.9333333333333</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>164.2</v>
+        <v>428.2</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>257.1</v>
+        <v>831.8000000000001</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>FSSE (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; HRAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SSAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 8 projects x MSc (24h) = 192.0h</t>
+          <t>THE1 (20cr): Nick Pears: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 264.0h</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Head (Research): 40% of 1642h = 656.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -2880,37 +2880,37 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Paul Cairns</t>
+          <t>Oleg Lisagor</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1797.633333333334</v>
+        <v>797.3000000000001</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>281.6333333333333</v>
+        <v>376</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1012.6</v>
+        <v>164.2</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>503.4</v>
+        <v>257.1</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>GODS (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HCIN (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>FSSE (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; HRAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SSAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 8 projects x MSc (24h) = 192.0h</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h; Grant BiB Centre for Social Change: 0% of 1642h = 0.0h; Grant IGGI: 20% of 1642h = 328.4h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; REF Lead: 5% of 1642h = 82.1h; Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -2932,37 +2932,37 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ribeiro</t>
+          <t>Paul Cairns</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1296.3</v>
+        <v>1797.633333333334</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>312.5</v>
+        <v>281.6333333333333</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>644.6</v>
+        <v>1012.6</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>339.2</v>
+        <v>503.4</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS1 (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>GODS (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HCIN (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 20% of 1642h = 328.4h</t>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h; Grant BiB Centre for Social Change: 0% of 1642h = 0.0h; Grant IGGI: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; REF Lead: 5% of 1642h = 82.1h; Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -2984,37 +2984,37 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Pengcheng Liu</t>
+          <t>Pedro Ribeiro</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1993.32</v>
+        <v>1296.3</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>296.3</v>
+        <v>312.5</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>996.5800000000002</v>
+        <v>644.6</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>700.4400000000001</v>
+        <v>339.2</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): Pengcheng Liu: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>AURO (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS1 (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Intelligent Dependable Environment Control for Sustainable Aquaculture: 20% of 1642h = 328.4h; Grant Establishing a Safe AI Research Hub: York–UTM–UTB Twin-Lab Initiative: 9% of 1642h = 147.8h; Grant Establishment of Korea–UK Collaboration Platform for Convergent Research in Quantum Photonics and Artificial Intelligence - Yr2: 5% of 1642h = 82.1h; Grant SCHEME: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Graduate Chair: 20% of 1642h = 328.4h; Research Group Leader: 10% of 1642h = 164.2h; Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -3036,37 +3036,37 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Peter Nightingale</t>
+          <t>Pengcheng Liu</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1069.866666666667</v>
+        <v>1993.32</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>430.4666666666666</v>
+        <v>296.3</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>300.2</v>
+        <v>996.5800000000002</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>339.2</v>
+        <v>700.4400000000001</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>ARIA (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; FOAM (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SAIL (20cr): Peter Nightingale: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>SYS3 (20cr): Pengcheng Liu: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Intelligent Dependable Environment Control for Sustainable Aquaculture: 20% of 1642h = 328.4h; Grant Establishing a Safe AI Research Hub: York–UTM–UTB Twin-Lab Initiative: 9% of 1642h = 147.8h; Grant Establishment of Korea–UK Collaboration Platform for Convergent Research in Quantum Photonics and Artificial Intelligence - Yr2: 5% of 1642h = 82.1h; Grant SCHEME: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>UG PL: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Graduate Chair: 20% of 1642h = 328.4h; Research Group Leader: 10% of 1642h = 164.2h; Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>ARIA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -3088,37 +3088,37 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Poonam Yadav</t>
+          <t>Peter Nightingale</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1702.933333333333</v>
+        <v>1069.866666666667</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>250.9333333333333</v>
+        <v>430.4666666666666</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>1112.8</v>
+        <v>300.2</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>339.2</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Poonam Yadav: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>ARIA (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; FOAM (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SAIL (20cr): Peter Nightingale: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h; Grant CHEDDAR Funding Apr-Sep 26- PSU296: 5% of 1642h = 82.1h; Grant REMOTE: Resilient and Secure Multi-Access Interoperable Communication Fabric for TinyEdge: 20% of 1642h = 328.4h; Grant Orchestrated mobile Network for Blackpool intelligent transport: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>UG PL: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ARIA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
@@ -3140,37 +3140,37 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Pourya Shamsolmoali</t>
+          <t>Poonam Yadav</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1010.9</v>
+        <v>1702.933333333333</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>484.55</v>
+        <v>250.9333333333333</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>228.2</v>
+        <v>1112.8</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>298.15</v>
+        <v>339.2</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Pourya Shamsolmoali: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; DEEP (20cr): Pourya Shamsolmoali: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>SOF1 (20cr): Poonam Yadav: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h; Grant CHEDDAR Funding Apr-Sep 26- PSU296: 5% of 1642h = 82.1h; Grant REMOTE: Resilient and Secure Multi-Access Interoperable Communication Fabric for TinyEdge: 20% of 1642h = 328.4h; Grant Orchestrated mobile Network for Blackpool intelligent transport: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Graduate School Board (Ordinary member): 2% of 1642h = 41.1h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -3192,37 +3192,37 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Radu Calinescu</t>
+          <t>Pourya Shamsolmoali</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1257.54</v>
+        <v>1010.9</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>131</v>
+        <v>484.55</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>918.7</v>
+        <v>228.2</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>207.84</v>
+        <v>298.15</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>GPIG (40cr): Radu Calinescu: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>DATA (20cr): Pourya Shamsolmoali: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; DEEP (20cr): Pourya Shamsolmoali: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h; Grant ARISE: Accelerating ReIntroduction of EcoSystem-Engineering Ant Colonies with Embodied AI: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h; Grant MammoBot: Robotic Posture Assistance for Universal Breast Screening Access: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Graduate School Board (Ordinary member): 2% of 1642h = 41.1h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
@@ -3244,37 +3244,37 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Richard Hawkins</t>
+          <t>Radu Calinescu</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1158</v>
+        <v>1257.54</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>378.4</v>
+        <v>131</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>358.3</v>
+        <v>918.7</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>421.3</v>
+        <v>207.84</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>CASA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SCDR (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 23 students x 3h = 69.0h; Projects: 7 projects x MSc (24h) = 168.0h</t>
+          <t>GPIG (40cr): Radu Calinescu: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h; Grant ARISE: Accelerating ReIntroduction of EcoSystem-Engineering Ant Colonies with Embodied AI: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h; Grant MammoBot: Robotic Posture Assistance for Universal Breast Screening Access: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Impact: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
@@ -3296,37 +3296,37 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Richard Wilson</t>
+          <t>Richard Hawkins</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>657.04</v>
+        <v>1158</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3</v>
+        <v>378.4</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>450.52</v>
+        <v>358.3</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>203.52</v>
+        <v>421.3</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>; Pastoral: 1 students x 3h = 3.0h; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
+          <t>CASA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SCDR (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 23 students x 3h = 69.0h; Projects: 7 projects x MSc (24h) = 168.0h</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 352.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>ART staff representative: 0% of 985h = 0.0h; Research Group Leader: 10% of 985h = 98.5h; Engagement (email/meetings): 60.0h; Personal development: 45.0h (FTE: 0.60)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Impact: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
@@ -3348,37 +3348,37 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Rob Alexander</t>
+          <t>Richard Wilson</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1043.88</v>
+        <v>657.04</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>404.9</v>
+        <v>3</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>398.3</v>
+        <v>450.52</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>240.68</v>
+        <v>203.52</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; RASS (10cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; REMS (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x MSc (24h) = 168.0h</t>
+          <t>; Pastoral: 1 students x 3h = 3.0h; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 352.0h</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>StAMP committee: 4% of 1642h = 65.7h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>ART staff representative: 0% of 985h = 0.0h; Research Group Leader: 10% of 985h = 98.5h; Engagement (email/meetings): 60.0h; Personal development: 45.0h (FTE: 0.60)</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
@@ -3400,32 +3400,32 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Roberto Metere</t>
+          <t>Rob Alexander</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1120.363333333333</v>
+        <v>1043.88</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>611.4833333333333</v>
+        <v>404.9</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>268.2</v>
+        <v>398.3</v>
       </c>
       <c r="F50" s="3" t="n">
         <v>240.68</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Roberto Metere: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; CTAP (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; EHAC (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HINT (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; RASS (10cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; REMS (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x MSc (24h) = 168.0h</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -3452,37 +3452,37 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Sam Braunstein</t>
+          <t>Roberto Metere</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>623.7833333333333</v>
+        <v>1120.363333333333</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>284.5833333333333</v>
+        <v>611.4833333333333</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>164.2</v>
+        <v>268.2</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>175</v>
+        <v>240.68</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; THE2 (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CBDA (20cr): Roberto Metere: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; CTAP (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; EHAC (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>StAMP committee: 4% of 1642h = 65.7h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -3504,27 +3504,27 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Sarah Carrington</t>
+          <t>Sam Braunstein</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>648.66</v>
+        <v>623.7833333333333</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>377.3</v>
+        <v>284.5833333333333</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>131.36</v>
+        <v>164.2</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>FSSE (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SCDR (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 10 projects x MSc (24h) = 240.0h</t>
+          <t>QUCO (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; THE2 (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 80.0h; Personal development: 60.0h (FTE: 0.80)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
@@ -3556,37 +3556,37 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Siamak Shahandashti</t>
+          <t>Sarah Carrington</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>1365.366666666667</v>
+        <v>648.66</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>383.6666666666666</v>
+        <v>377.3</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>478.3</v>
+        <v>131.36</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>503.4</v>
+        <v>140</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE1 (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>FSSE (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SCDR (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 10 projects x MSc (24h) = 240.0h</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h; Grant Participatory Harm Auditing Workbenches &amp; Methodologies: 5% of 1642h = 82.1h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 80.0h; Personal development: 60.0h (FTE: 0.80)</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -3608,37 +3608,37 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Simon Burton</t>
+          <t>Siamak Shahandashti</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1020.24</v>
+        <v>1365.366666666667</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>53.7</v>
+        <v>383.6666666666666</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>791.54</v>
+        <v>478.3</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>CASA (10cr): Simon Burton: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
+          <t>CTAP (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE1 (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h; Grant Verifiable generation of SOTIF requirements: 2% of 1642h = 32.8h; Grant Moving forward explainable AI by combining different assurance metrics: 15% of 1642h = 246.3h; Grant AI safety argumentation review: 5% of 1642h = 82.1h; Grant KTP with DNV Services Ltd - Innovate part: 3% of 1642h = 49.3h; Grant KTP with DNV Services Ltd - Industry part: 2% of 1642h = 32.8h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h; Grant Participatory Harm Auditing Workbenches &amp; Methodologies: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
@@ -3660,32 +3660,32 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Simon Foster</t>
+          <t>Simon Burton</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>855.1166666666666</v>
+        <v>1020.24</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>403.9166666666666</v>
+        <v>53.7</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>276.2</v>
+        <v>791.54</v>
       </c>
       <c r="F55" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Simon Foster: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Simon Foster: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>CASA (10cr): Simon Burton: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h; Grant Verifiable generation of SOTIF requirements: 2% of 1642h = 32.8h; Grant Moving forward explainable AI by combining different assurance metrics: 15% of 1642h = 246.3h; Grant AI safety argumentation review: 5% of 1642h = 82.1h; Grant KTP with DNV Services Ltd - Innovate part: 3% of 1642h = 49.3h; Grant KTP with DNV Services Ltd - Industry part: 2% of 1642h = 32.8h</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -3712,33 +3712,37 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Simos Gerasimou</t>
+          <t>Simon Foster</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>1309.68</v>
+        <v>855.1166666666666</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>403.9166666666666</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>1101.84</v>
+        <v>276.2</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>207.84</v>
-      </c>
-      <c r="G56" s="4" t="inlineStr"/>
+        <v>175</v>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>THE1 (20cr): Simon Foster: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Simon Foster: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+        </is>
+      </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 248.0h; Grant Human-centric Digital Twin Approaches to Trustworthy AI and Robotics for Improved Working Conditions: 12% of 1642h = 197.0h; Grant Socially-Acceptable and Trustworthy Human-Robot Teaming for Agile Industries (SYMPHONY Resubmission): 10% of 1642h = 164.2h; Grant GuardAI ( Enhancing Robustness and Security of Edge AI Systems for Safety-Critical Applications): 15% of 1642h = 246.3h; Grant MOSAICO: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
@@ -3748,7 +3752,7 @@
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
@@ -3760,37 +3764,33 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Soumya Banerjee</t>
+          <t>Simos Gerasimou</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>919.8333333333334</v>
+        <v>1309.68</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>416.4333333333333</v>
+        <v>0</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>164.2</v>
+        <v>1101.84</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>339.2</v>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>AURO (20cr): Soumya Banerjee: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; LLMA (20cr): Soumya Banerjee: New lecturer + new content (7.5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
-        </is>
-      </c>
+        <v>207.84</v>
+      </c>
+      <c r="G57" s="4" t="inlineStr"/>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 248.0h; Grant Human-centric Digital Twin Approaches to Trustworthy AI and Robotics for Improved Working Conditions: 12% of 1642h = 197.0h; Grant Socially-Acceptable and Trustworthy Human-Robot Teaming for Agile Industries (SYMPHONY Resubmission): 10% of 1642h = 164.2h; Grant GuardAI ( Enhancing Robustness and Security of Edge AI Systems for Safety-Critical Applications): 15% of 1642h = 246.3h; Grant MOSAICO: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>Mumbai Campus Partnership Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>LLMA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
@@ -3812,37 +3812,37 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Stefano Pirandola</t>
+          <t>Soumya Banerjee</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>1380.45</v>
+        <v>919.8333333333334</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>274.55</v>
+        <v>416.4333333333333</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>520.4000000000001</v>
+        <v>164.2</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>585.5</v>
+        <v>339.2</v>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Stefano Pirandola: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>AURO (20cr): Soumya Banerjee: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; LLMA (20cr): Soumya Banerjee: New lecturer + new content (7.5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Integrated Quantum Networks (IQN) Hub: 10% of 1642h = 164.2h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Mumbai Campus Partnership Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>LLMA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
@@ -3864,37 +3864,37 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Steven Wright</t>
+          <t>Stefano Pirandola</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>1353.8</v>
+        <v>1380.45</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>234</v>
+        <v>274.55</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>452.2</v>
+        <v>520.4000000000001</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>667.5999999999999</v>
+        <v>585.5</v>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>HIPC (20cr): Steven Wright: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>QUCO (20cr): Stefano Pirandola: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Integrated Quantum Networks (IQN) Hub: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>CBoE (on-campus): 30% of 1642h = 492.6h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
@@ -3916,37 +3916,37 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Steven Xiaotian Dai</t>
+          <t>Steven Wright</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1190.5</v>
+        <v>1353.8</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>336.8</v>
+        <v>234</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>350.3</v>
+        <v>452.2</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>503.4</v>
+        <v>667.5999999999999</v>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>EMBS (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HIPC (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>HIPC (20cr): Steven Wright: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h; Grant SCHEME: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>Student Disability Representative: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>CBoE (on-campus): 30% of 1642h = 492.6h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
@@ -3968,37 +3968,37 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Tommy Yuan</t>
+          <t>Steven Xiaotian Dai</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1557.546666666667</v>
+        <v>1190.5</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>624.2666666666667</v>
+        <v>336.8</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>364.2</v>
+        <v>350.3</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>569.08</v>
+        <v>503.4</v>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>ARIA (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; ENG1 (20cr): Tommy Yuan: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; FOAM (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>EMBS (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HIPC (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 200.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h; Grant SCHEME: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>CSCSE HAP Partnership Leader: 10% of 1642h = 164.2h; Deputy CBoEs: 10% of 1642h = 164.2h; StAMP committee: 4% of 1642h = 65.7h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Student Disability Representative: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>ARIA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
@@ -4020,37 +4020,37 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Vasileios Vasilakis</t>
+          <t>Tommy Yuan</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>1103.9</v>
+        <v>1557.546666666667</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>408.5</v>
+        <v>624.2666666666667</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>356.2</v>
+        <v>364.2</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>339.2</v>
+        <v>569.08</v>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>NETS (20cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x MSc (24h) = 168.0h</t>
+          <t>ARIA (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; ENG1 (20cr): Tommy Yuan: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; FOAM (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 200.0h</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>CSCSE HAP Partnership Leader: 10% of 1642h = 164.2h; Deputy CBoEs: 10% of 1642h = 164.2h; StAMP committee: 4% of 1642h = 65.7h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ARIA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr">
@@ -4072,37 +4072,37 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>William Smith</t>
+          <t>Vasileios Vasilakis</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>1490.316666666667</v>
+        <v>1103.9</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>351.7666666666667</v>
+        <v>408.5</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>676.2</v>
+        <v>356.2</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>462.35</v>
+        <v>339.2</v>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>DEEP (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; ROCS (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>NETS (20cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x MSc (24h) = 168.0h</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
@@ -4124,37 +4124,37 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Xinwei Fang</t>
+          <t>William Smith</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>925.1</v>
+        <v>1490.316666666667</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>423.8</v>
+        <v>351.7666666666667</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>244.2</v>
+        <v>676.2</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>257.1</v>
+        <v>462.35</v>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; GPIG (40cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DEEP (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; ROCS (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h</t>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
@@ -4176,37 +4176,37 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Yan Jia</t>
+          <t>Xinwei Fang</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1169.1</v>
+        <v>925.1</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27</v>
+        <v>423.8</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>638.7</v>
+        <v>244.2</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>503.4</v>
+        <v>257.1</v>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>DATA (20cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; GPIG (40cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10% of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>Ethics Committee Member: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
@@ -4228,50 +4228,102 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>Yan Jia</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>1169.1</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>638.7</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>503.4</v>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10% of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>Ethics Committee Member: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
           <t>Yuchen Zhao</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" s="3" t="n">
+      <c r="B67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="3" t="n">
         <v>856.5</v>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="D67" s="3" t="n">
         <v>419.2</v>
       </c>
-      <c r="E66" s="3" t="n">
+      <c r="E67" s="3" t="n">
         <v>180.2</v>
       </c>
-      <c r="F66" s="3" t="n">
+      <c r="F67" s="3" t="n">
         <v>257.1</v>
       </c>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t>EHAC (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; NETS (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr">
+      <c r="H67" s="4" t="inlineStr">
         <is>
           <t>PhD supervision: 2x assessor (8h each) = 16.0h</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr">
+      <c r="I67" s="4" t="inlineStr">
         <is>
           <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
-      <c r="J66" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="inlineStr">
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -4302,7 +4354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4782,17 +4834,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jacob Rigby</t>
+          <t>Ibrahim Habli</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>243.2333333333333</v>
+        <v>0</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>246.3</v>
+        <v>1495.5</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E24" s="7">
         <f>SUM(B24:D24)</f>
@@ -4802,17 +4854,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>James Stovold</t>
+          <t>Jacob Rigby</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>407.5</v>
+        <v>243.2333333333333</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>164.2</v>
+        <v>246.3</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="E25" s="7">
         <f>SUM(B25:D25)</f>
@@ -4822,17 +4874,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>James Walker</t>
+          <t>James Stovold</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>309.8666666666667</v>
+        <v>407.5</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1000.8</v>
+        <v>164.2</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E26" s="7">
         <f>SUM(B26:D26)</f>
@@ -4842,17 +4894,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jen Beeston</t>
+          <t>James Walker</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>355.7</v>
+        <v>309.8666666666667</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>332.2</v>
+        <v>1000.8</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>667.5999999999999</v>
+        <v>175</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(B27:D27)</f>
@@ -4862,17 +4914,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jo Iacovides</t>
+          <t>Jen Beeston</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>297.7</v>
+        <v>355.7</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>348.2</v>
+        <v>332.2</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>339.2</v>
+        <v>667.5999999999999</v>
       </c>
       <c r="E28" s="7">
         <f>SUM(B28:D28)</f>
@@ -4882,17 +4934,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Joe Cutting</t>
+          <t>Jo Iacovides</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>347.1</v>
+        <v>297.7</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>228.2</v>
+        <v>348.2</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E29" s="7">
         <f>SUM(B29:D29)</f>
@@ -4902,17 +4954,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>John McDermid</t>
+          <t>Joe Cutting</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>0</v>
+        <v>347.1</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>1539.7</v>
+        <v>228.2</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E30" s="7">
         <f>SUM(B30:D30)</f>
@@ -4922,17 +4974,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Katrina Attwood</t>
+          <t>John McDermid</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>454.6333333333333</v>
+        <v>0</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>212.2</v>
+        <v>1539.7</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>503.4</v>
+        <v>339.2</v>
       </c>
       <c r="E31" s="7">
         <f>SUM(B31:D31)</f>
@@ -4942,17 +4994,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kofi Appiah</t>
+          <t>Katrina Attwood</t>
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>395.8</v>
+        <v>454.6333333333333</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>356.2</v>
+        <v>212.2</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>421.3</v>
+        <v>503.4</v>
       </c>
       <c r="E32" s="7">
         <f>SUM(B32:D32)</f>
@@ -4962,17 +5014,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kostas Barmpis</t>
+          <t>Kofi Appiah</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>429</v>
+        <v>395.8</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>548.6</v>
+        <v>356.2</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>257.1</v>
+        <v>421.3</v>
       </c>
       <c r="E33" s="7">
         <f>SUM(B33:D33)</f>
@@ -4982,17 +5034,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mark Nicholson</t>
+          <t>Kostas Barmpis</t>
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>314.7</v>
+        <v>429</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>227.36</v>
+        <v>548.6</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>192.544</v>
+        <v>257.1</v>
       </c>
       <c r="E34" s="7">
         <f>SUM(B34:D34)</f>
@@ -5002,17 +5054,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mark Sujan</t>
+          <t>Mark Nicholson</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>47.4</v>
+        <v>314.7</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>131.36</v>
+        <v>227.36</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>140</v>
+        <v>192.544</v>
       </c>
       <c r="E35" s="7">
         <f>SUM(B35:D35)</f>
@@ -5022,17 +5074,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mike Freeman</t>
+          <t>Mark Sujan</t>
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>480.6333333333333</v>
+        <v>47.4</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>164.2</v>
+        <v>131.36</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>257.1</v>
+        <v>140</v>
       </c>
       <c r="E36" s="7">
         <f>SUM(B36:D36)</f>
@@ -5042,11 +5094,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mike O'Dea</t>
+          <t>Mike Freeman</t>
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>395.3</v>
+        <v>480.6333333333333</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>164.2</v>
@@ -5062,17 +5114,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nick Pears</t>
+          <t>Mike O'Dea</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>208.9333333333333</v>
+        <v>395.3</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>428.2</v>
+        <v>164.2</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>831.8000000000001</v>
+        <v>257.1</v>
       </c>
       <c r="E38" s="7">
         <f>SUM(B38:D38)</f>
@@ -5082,17 +5134,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Oleg Lisagor</t>
+          <t>Nick Pears</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>376</v>
+        <v>208.9333333333333</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>164.2</v>
+        <v>428.2</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>257.1</v>
+        <v>831.8000000000001</v>
       </c>
       <c r="E39" s="7">
         <f>SUM(B39:D39)</f>
@@ -5102,17 +5154,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Paul Cairns</t>
+          <t>Oleg Lisagor</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>281.6333333333333</v>
+        <v>376</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>1012.6</v>
+        <v>164.2</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>503.4</v>
+        <v>257.1</v>
       </c>
       <c r="E40" s="7">
         <f>SUM(B40:D40)</f>
@@ -5122,17 +5174,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pedro Ribeiro</t>
+          <t>Paul Cairns</t>
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>312.5</v>
+        <v>281.6333333333333</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>644.6</v>
+        <v>1012.6</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>339.2</v>
+        <v>503.4</v>
       </c>
       <c r="E41" s="7">
         <f>SUM(B41:D41)</f>
@@ -5142,17 +5194,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Pengcheng Liu</t>
+          <t>Pedro Ribeiro</t>
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>296.3</v>
+        <v>312.5</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>996.5800000000002</v>
+        <v>644.6</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>700.4400000000001</v>
+        <v>339.2</v>
       </c>
       <c r="E42" s="7">
         <f>SUM(B42:D42)</f>
@@ -5162,17 +5214,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Peter Nightingale</t>
+          <t>Pengcheng Liu</t>
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>430.4666666666666</v>
+        <v>296.3</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>300.2</v>
+        <v>996.5800000000002</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>339.2</v>
+        <v>700.4400000000001</v>
       </c>
       <c r="E43" s="7">
         <f>SUM(B43:D43)</f>
@@ -5182,14 +5234,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Poonam Yadav</t>
+          <t>Peter Nightingale</t>
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>250.9333333333333</v>
+        <v>430.4666666666666</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>1112.8</v>
+        <v>300.2</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>339.2</v>
@@ -5202,17 +5254,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pourya Shamsolmoali</t>
+          <t>Poonam Yadav</t>
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>484.55</v>
+        <v>250.9333333333333</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>228.2</v>
+        <v>1112.8</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>298.15</v>
+        <v>339.2</v>
       </c>
       <c r="E45" s="7">
         <f>SUM(B45:D45)</f>
@@ -5222,17 +5274,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Radu Calinescu</t>
+          <t>Pourya Shamsolmoali</t>
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>131</v>
+        <v>484.55</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>918.7</v>
+        <v>228.2</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>207.84</v>
+        <v>298.15</v>
       </c>
       <c r="E46" s="7">
         <f>SUM(B46:D46)</f>
@@ -5242,17 +5294,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Richard Hawkins</t>
+          <t>Radu Calinescu</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>378.4</v>
+        <v>131</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>358.3</v>
+        <v>918.7</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>421.3</v>
+        <v>207.84</v>
       </c>
       <c r="E47" s="7">
         <f>SUM(B47:D47)</f>
@@ -5262,17 +5314,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Richard Wilson</t>
+          <t>Richard Hawkins</t>
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>3</v>
+        <v>378.4</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>450.52</v>
+        <v>358.3</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>203.52</v>
+        <v>421.3</v>
       </c>
       <c r="E48" s="7">
         <f>SUM(B48:D48)</f>
@@ -5282,17 +5334,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Rob Alexander</t>
+          <t>Richard Wilson</t>
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>404.9</v>
+        <v>3</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>398.3</v>
+        <v>450.52</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>240.68</v>
+        <v>203.52</v>
       </c>
       <c r="E49" s="7">
         <f>SUM(B49:D49)</f>
@@ -5302,14 +5354,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Roberto Metere</t>
+          <t>Rob Alexander</t>
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>611.4833333333333</v>
+        <v>404.9</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>268.2</v>
+        <v>398.3</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>240.68</v>
@@ -5322,17 +5374,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sam Braunstein</t>
+          <t>Roberto Metere</t>
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>284.5833333333333</v>
+        <v>611.4833333333333</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>164.2</v>
+        <v>268.2</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>175</v>
+        <v>240.68</v>
       </c>
       <c r="E51" s="7">
         <f>SUM(B51:D51)</f>
@@ -5342,17 +5394,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sarah Carrington</t>
+          <t>Sam Braunstein</t>
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>377.3</v>
+        <v>284.5833333333333</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>131.36</v>
+        <v>164.2</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="E52" s="7">
         <f>SUM(B52:D52)</f>
@@ -5362,17 +5414,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Siamak Shahandashti</t>
+          <t>Sarah Carrington</t>
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>383.6666666666666</v>
+        <v>377.3</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>478.3</v>
+        <v>131.36</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>503.4</v>
+        <v>140</v>
       </c>
       <c r="E53" s="7">
         <f>SUM(B53:D53)</f>
@@ -5382,17 +5434,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Simon Burton</t>
+          <t>Siamak Shahandashti</t>
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>53.7</v>
+        <v>383.6666666666666</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>791.54</v>
+        <v>478.3</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="E54" s="7">
         <f>SUM(B54:D54)</f>
@@ -5402,14 +5454,14 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Simon Foster</t>
+          <t>Simon Burton</t>
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>403.9166666666666</v>
+        <v>53.7</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>276.2</v>
+        <v>791.54</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>175</v>
@@ -5422,17 +5474,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Simos Gerasimou</t>
+          <t>Simon Foster</t>
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>0</v>
+        <v>403.9166666666666</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>1101.84</v>
+        <v>276.2</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>207.84</v>
+        <v>175</v>
       </c>
       <c r="E56" s="7">
         <f>SUM(B56:D56)</f>
@@ -5442,17 +5494,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Soumya Banerjee</t>
+          <t>Simos Gerasimou</t>
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>416.4333333333333</v>
+        <v>0</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>164.2</v>
+        <v>1101.84</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>339.2</v>
+        <v>207.84</v>
       </c>
       <c r="E57" s="7">
         <f>SUM(B57:D57)</f>
@@ -5462,17 +5514,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Stefano Pirandola</t>
+          <t>Soumya Banerjee</t>
         </is>
       </c>
       <c r="B58" s="7" t="n">
-        <v>274.55</v>
+        <v>416.4333333333333</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>520.4000000000001</v>
+        <v>164.2</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>585.5</v>
+        <v>339.2</v>
       </c>
       <c r="E58" s="7">
         <f>SUM(B58:D58)</f>
@@ -5482,17 +5534,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Steven Wright</t>
+          <t>Stefano Pirandola</t>
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>234</v>
+        <v>274.55</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>452.2</v>
+        <v>520.4000000000001</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>667.5999999999999</v>
+        <v>585.5</v>
       </c>
       <c r="E59" s="7">
         <f>SUM(B59:D59)</f>
@@ -5502,17 +5554,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Steven Xiaotian Dai</t>
+          <t>Steven Wright</t>
         </is>
       </c>
       <c r="B60" s="7" t="n">
-        <v>336.8</v>
+        <v>234</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>350.3</v>
+        <v>452.2</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>503.4</v>
+        <v>667.5999999999999</v>
       </c>
       <c r="E60" s="7">
         <f>SUM(B60:D60)</f>
@@ -5522,17 +5574,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tommy Yuan</t>
+          <t>Steven Xiaotian Dai</t>
         </is>
       </c>
       <c r="B61" s="7" t="n">
-        <v>624.2666666666667</v>
+        <v>336.8</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>364.2</v>
+        <v>350.3</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>569.08</v>
+        <v>503.4</v>
       </c>
       <c r="E61" s="7">
         <f>SUM(B61:D61)</f>
@@ -5542,17 +5594,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Vasileios Vasilakis</t>
+          <t>Tommy Yuan</t>
         </is>
       </c>
       <c r="B62" s="7" t="n">
-        <v>408.5</v>
+        <v>624.2666666666667</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>356.2</v>
+        <v>364.2</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>339.2</v>
+        <v>569.08</v>
       </c>
       <c r="E62" s="7">
         <f>SUM(B62:D62)</f>
@@ -5562,17 +5614,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>William Smith</t>
+          <t>Vasileios Vasilakis</t>
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>351.7666666666667</v>
+        <v>408.5</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>676.2</v>
+        <v>356.2</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>462.35</v>
+        <v>339.2</v>
       </c>
       <c r="E63" s="7">
         <f>SUM(B63:D63)</f>
@@ -5582,17 +5634,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Xinwei Fang</t>
+          <t>William Smith</t>
         </is>
       </c>
       <c r="B64" s="7" t="n">
-        <v>423.8</v>
+        <v>351.7666666666667</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>244.2</v>
+        <v>676.2</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>257.1</v>
+        <v>462.35</v>
       </c>
       <c r="E64" s="7">
         <f>SUM(B64:D64)</f>
@@ -5602,17 +5654,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Yan Jia</t>
+          <t>Xinwei Fang</t>
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>27</v>
+        <v>423.8</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>638.7</v>
+        <v>244.2</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>503.4</v>
+        <v>257.1</v>
       </c>
       <c r="E65" s="7">
         <f>SUM(B65:D65)</f>
@@ -5622,20 +5674,40 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Yuchen Zhao</t>
+          <t>Yan Jia</t>
         </is>
       </c>
       <c r="B66" s="7" t="n">
-        <v>419.2</v>
+        <v>27</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>180.2</v>
+        <v>638.7</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>257.1</v>
+        <v>503.4</v>
       </c>
       <c r="E66" s="7">
         <f>SUM(B66:D66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Yuchen Zhao</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>419.2</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>257.1</v>
+      </c>
+      <c r="E67" s="7">
+        <f>SUM(B67:D67)</f>
         <v/>
       </c>
     </row>
